--- a/docs/Chiraath-Summary-Sep26.xlsx
+++ b/docs/Chiraath-Summary-Sep26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11F6FF4-B729-FC4C-973A-404D7FD3DD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EA5CD3-095A-FD41-813C-21E310EFA09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="1394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3535" uniqueCount="1396">
   <si>
     <t>Notes:</t>
   </si>
@@ -2066,9 +2066,6 @@
   </si>
   <si>
     <t>Chanderi silk soft dusty rose/pink kurta suit set with delicate floral prints and light embroiderysalwar 3 piece set</t>
-  </si>
-  <si>
-    <t>Saida (1400), Binija (1560), Shinoob Cousin(1000)</t>
   </si>
   <si>
     <t>Size: M</t>
@@ -2135,12 +2132,6 @@
     <t>Co-ord set short (2 piece) linen blend</t>
   </si>
   <si>
-    <t>Silpa (600) - M</t>
-  </si>
-  <si>
-    <t>Size: L, XL</t>
-  </si>
-  <si>
     <t>CHR-84</t>
   </si>
   <si>
@@ -2154,12 +2145,6 @@
   </si>
   <si>
     <t>Linen Blend cotton Salwar Set- 3 piece (lavender with ajrakh print)</t>
-  </si>
-  <si>
-    <t>Baby Khadeeja - 1400, Rameez Relative(XXL): 900</t>
-  </si>
-  <si>
-    <t>Size: M, L</t>
   </si>
   <si>
     <t>CHR-86</t>
@@ -3576,12 +3561,6 @@
     <t>Niroop</t>
   </si>
   <si>
-    <t>Rust, Purple, Olive Green</t>
-  </si>
-  <si>
-    <t>Dark Grey - returned</t>
-  </si>
-  <si>
     <t>Churi material with pant &amp; shawl</t>
   </si>
   <si>
@@ -3817,9 +3796,6 @@
   </si>
   <si>
     <t>Revathi, Simi Sudhir, Aruna</t>
-  </si>
-  <si>
-    <t>Pink, Black</t>
   </si>
   <si>
     <t>Blue - returned</t>
@@ -3904,9 +3880,6 @@
     <t>Black, Maroon, Violet, Rani Pink, Olive Green</t>
   </si>
   <si>
-    <t>Temple Design, CHR-240 New Kerala Golden Saree with flowers, CHR-242-Kerala Saree, CHR-230 - Jute Silk  (Advance -2800)</t>
-  </si>
-  <si>
     <t>Bank Account</t>
   </si>
   <si>
@@ -4091,9 +4064,6 @@
   </si>
   <si>
     <t>purple - Malini, Olive green - Latha, Navy Blue - Thressiamma</t>
-  </si>
-  <si>
-    <t>Light blue/onion peel, brown/dark maroon, black/light green, rani pink, olive green(2)</t>
   </si>
   <si>
     <t>Latha Ammayi</t>
@@ -4208,27 +4178,9 @@
     <t>Prabha Chidambaram - Green, Wine red returned, Blue - Lakshmi</t>
   </si>
   <si>
-    <t>CHR-229 Blue Modal</t>
-  </si>
-  <si>
-    <t>Shylaja - Purple, Jisha - Blue, Bank staff - Green, Rajna - Yellow/Orange, Ramy - Red, 3 returned</t>
-  </si>
-  <si>
-    <t>2026-0904</t>
-  </si>
-  <si>
-    <t>Ramya (US)</t>
-  </si>
-  <si>
     <t>Red - retruned, Olive green returned</t>
   </si>
   <si>
-    <t>CHR-212 Red &amp; CHR-246 - Kasavu tissue set mund</t>
-  </si>
-  <si>
-    <t>Ramya US</t>
-  </si>
-  <si>
     <t>CHR-79 Indigo Blue Salwar</t>
   </si>
   <si>
@@ -4245,6 +4197,60 @@
   </si>
   <si>
     <t>Tussar Silk Saree Collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temple Design, CHR-240 New Kerala Golden Saree with flowers, CHR-242-Kerala Saree, CHR-230 - Jute Silk </t>
+  </si>
+  <si>
+    <t>Anu Mathew (Canada)</t>
+  </si>
+  <si>
+    <t>Reetha Peethambaran, Anu Mathew (Canada)</t>
+  </si>
+  <si>
+    <t>CHR-255 new chikku green</t>
+  </si>
+  <si>
+    <t>CHR-218 Soft mul purple, CHR-299 Modal blue</t>
+  </si>
+  <si>
+    <t>Dark Grey - returned, Purple - Lakshmi</t>
+  </si>
+  <si>
+    <t>Aparna</t>
+  </si>
+  <si>
+    <t>Size: XL</t>
+  </si>
+  <si>
+    <t>Silpa (600) - L, Aparna (500) - M</t>
+  </si>
+  <si>
+    <t>CHR-83 Coord set-M, CHR-77 Rose Salwar M</t>
+  </si>
+  <si>
+    <t>Saida (1400), Binija (1560), Shinoob Cousin(1000), Aparna (950)</t>
+  </si>
+  <si>
+    <t>Baby Khadeeja - 1400, Rameez Relative(XXL): 900, Aneesha(M)-950</t>
+  </si>
+  <si>
+    <t>Size: L</t>
+  </si>
+  <si>
+    <t>Aneesha</t>
+  </si>
+  <si>
+    <t>CHR-85 Linen Lavender Salwar M</t>
+  </si>
+  <si>
+    <t>Light blue/onion peel, rani pink, olive green(2)</t>
+  </si>
+  <si>
+    <t>Shylaja - Purple, Jisha - Blue, Bank staff - Green, Rajna - Yellow/Orange, 4 returned</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -4609,7 +4615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4864,6 +4870,12 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5152,10 +5164,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>364</c:v>
+                  <c:v>366</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>99</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -5255,10 +5267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>93</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
@@ -5585,10 +5597,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>69573</c:v>
+                  <c:v>67003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-184887.99333333335</c:v>
+                  <c:v>-191178.99333333335</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5927,7 +5939,7 @@
                   <c:v>45848</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>144</c:v>
+                  <c:v>-5678</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6063,31 +6075,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>45448</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>19089</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>16248</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>54177</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>54393</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>72915</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>65156</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>79098</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>6180</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6503,31 +6515,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-47311</c:v>
+                  <c:v>-1863</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-5152</c:v>
+                  <c:v>13937</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-22172</c:v>
+                  <c:v>-5924</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-71002</c:v>
+                  <c:v>-16825</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-4449</c:v>
+                  <c:v>49944</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-99043</c:v>
+                  <c:v>-26128</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-102200</c:v>
+                  <c:v>-37044</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-45848</c:v>
+                  <c:v>33250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-144</c:v>
+                  <c:v>11858</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6985,10 +6997,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>468</c:v>
+                  <c:v>473</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>161</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8180,7 +8192,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>602339</v>
+        <v>596517</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -8195,7 +8207,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>554801</v>
+        <v>565651</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -8212,7 +8224,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>575661</v>
+        <v>578731</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -8229,7 +8241,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-47538</v>
+        <v>-30866</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8264,7 +8276,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>43857.993333333347</v>
+        <v>44178.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -8274,7 +8286,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>64379.003333333341</v>
+        <v>62117.67</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -8284,7 +8296,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-108236.99666666666</v>
+        <v>-106296.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -8323,15 +8335,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>262941</v>
+        <v>261321</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>200779.66666666666</v>
+        <v>198839</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>62161.333333333343</v>
+        <v>62482</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8339,11 +8351,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>43857.993333333347</v>
+        <v>44178.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹43,858</v>
+        <v>Receive ₹44,179</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -8353,15 +8365,15 @@
       </c>
       <c r="B19" s="12">
         <f>PartnerShares!B9</f>
-        <v>306798</v>
+        <v>302596</v>
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>200779.66666666666</v>
+        <v>198839</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>106018.33333333334</v>
+        <v>103757</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8369,11 +8381,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>64379.003333333341</v>
+        <v>62117.67</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹64,379</v>
+        <v>Receive ₹62,118</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -8387,11 +8399,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>200779.66666666666</v>
+        <v>198839</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-168179.66666666666</v>
+        <v>-166239</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8399,11 +8411,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-108236.99666666666</v>
+        <v>-106296.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹108,237</v>
+        <v>Pay ₹106,296</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -8441,15 +8453,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>485198</v>
+        <v>493648</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>184970.65339999998</v>
+        <v>188588.0434</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>300227.34660000005</v>
+        <v>305059.95660000003</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8457,11 +8469,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>162917.32060000004</v>
+        <v>167749.93060000002</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹162,917</v>
+        <v>Pay ₹167,750</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8471,15 +8483,15 @@
       </c>
       <c r="B27" s="12">
         <f>'Cash Pool'!B5</f>
-        <v>56073</v>
+        <v>58473</v>
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>184859.69320000001</v>
+        <v>188474.91320000001</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-128786.69320000001</v>
+        <v>-130001.91320000001</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8487,11 +8499,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-57199.651200000008</v>
+        <v>-58414.871200000009</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹57,200</v>
+        <v>Receive ₹58,415</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8505,11 +8517,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>184970.65339999998</v>
+        <v>188588.0434</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-172440.65339999998</v>
+        <v>-176058.0434</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8517,11 +8529,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-106717.66939999997</v>
+        <v>-110335.05939999998</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹106,718</v>
+        <v>Receive ₹110,335</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8633,7 +8645,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46270</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8642,14 +8654,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>602339</v>
+        <v>596517</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>554801</v>
+        <v>565651</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8658,14 +8670,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-47538</v>
+        <v>-30866</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>-126686.79333333336</v>
+        <v>-135547.79333333333</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8706,18 +8718,18 @@
       </c>
       <c r="C10" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A10)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>45448</v>
       </c>
       <c r="D10" s="21">
         <f t="shared" ref="D10:D21" si="0">C10-B10</f>
-        <v>-47311</v>
+        <v>-1863</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>80</v>
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8730,18 +8742,18 @@
       </c>
       <c r="C11" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>19089</v>
       </c>
       <c r="D11" s="27">
         <f t="shared" si="0"/>
-        <v>-5152</v>
+        <v>13937</v>
       </c>
       <c r="F11" s="26" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8754,11 +8766,11 @@
       </c>
       <c r="C12" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A12)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>16248</v>
       </c>
       <c r="D12" s="21">
         <f t="shared" si="0"/>
-        <v>-22172</v>
+        <v>-5924</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
@@ -8771,11 +8783,11 @@
       </c>
       <c r="C13" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>54177</v>
       </c>
       <c r="D13" s="27">
         <f t="shared" si="0"/>
-        <v>-71002</v>
+        <v>-16825</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
@@ -8788,11 +8800,11 @@
       </c>
       <c r="C14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>54393</v>
       </c>
       <c r="D14" s="21">
         <f t="shared" si="0"/>
-        <v>-4449</v>
+        <v>49944</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
@@ -8805,11 +8817,11 @@
       </c>
       <c r="C15" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>72915</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="0"/>
-        <v>-99043</v>
+        <v>-26128</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -8822,11 +8834,11 @@
       </c>
       <c r="C16" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>65156</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
-        <v>-102200</v>
+        <v>-37044</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -8839,11 +8851,11 @@
       </c>
       <c r="C17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>79098</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>-45848</v>
+        <v>33250</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -8852,15 +8864,15 @@
       </c>
       <c r="B18" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A18)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>144</v>
+        <v>-5678</v>
       </c>
       <c r="C18" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>0</v>
+        <v>6180</v>
       </c>
       <c r="D18" s="21">
         <f t="shared" si="0"/>
-        <v>-144</v>
+        <v>11858</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
@@ -8937,18 +8949,18 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
       </c>
       <c r="K47" s="31">
         <f t="array" ref="K47">SUMPRODUCT((INVENTORY!$C$2:$C$475=J47)*(INVENTORY!$D$2:$D$475)*(INVENTORY!$G$2:$G$475))</f>
-        <v>69573</v>
+        <v>67003</v>
       </c>
     </row>
     <row r="48" spans="6:11" ht="15" customHeight="1">
@@ -8957,18 +8969,18 @@
       </c>
       <c r="G48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!F:F)</f>
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!G:G)</f>
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J48" s="30" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$475=J48)*(INVENTORY!$D$2:$D$475)*(INVENTORY!$G$2:$G$475))</f>
-        <v>-184887.99333333335</v>
+        <v>-191178.99333333335</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10341,7 +10353,7 @@
         <v>28526</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
@@ -10411,7 +10423,7 @@
         <v>70</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
@@ -10425,7 +10437,7 @@
         <v>1375</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
@@ -10439,7 +10451,7 @@
         <v>189</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
@@ -10565,7 +10577,7 @@
         <v>570</v>
       </c>
       <c r="D107" s="39" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
@@ -10593,7 +10605,7 @@
         <v>320</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
@@ -10607,7 +10619,7 @@
         <v>3046</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>1317</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15" customHeight="1">
@@ -10667,16 +10679,32 @@
       </c>
     </row>
     <row r="115" spans="1:4" ht="15" customHeight="1">
-      <c r="A115" s="38"/>
-      <c r="B115" s="39"/>
-      <c r="C115" s="40"/>
-      <c r="D115" s="39"/>
+      <c r="A115" s="38">
+        <v>46276</v>
+      </c>
+      <c r="B115" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" s="40">
+        <v>-4202</v>
+      </c>
+      <c r="D115" s="39" t="s">
+        <v>1395</v>
+      </c>
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
-      <c r="A116" s="35"/>
-      <c r="B116" s="36"/>
-      <c r="C116" s="37"/>
-      <c r="D116" s="36"/>
+      <c r="A116" s="35">
+        <v>46276</v>
+      </c>
+      <c r="B116" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C116" s="37">
+        <v>-1620</v>
+      </c>
+      <c r="D116" s="36" t="s">
+        <v>1395</v>
+      </c>
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
       <c r="A117" s="38"/>
@@ -18006,7 +18034,7 @@
       <c r="F216" s="46"/>
       <c r="G216" s="46"/>
       <c r="H216" s="46" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="I216" s="45" t="s">
         <v>148</v>
@@ -18831,7 +18859,7 @@
       <c r="F249" s="46"/>
       <c r="G249" s="46"/>
       <c r="H249" s="46" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="I249" s="45" t="s">
         <v>148</v>
@@ -18845,17 +18873,21 @@
         <v>164</v>
       </c>
       <c r="C250" s="83">
-        <v>950</v>
-      </c>
-      <c r="D250" s="44"/>
-      <c r="E250" s="44"/>
+        <v>980</v>
+      </c>
+      <c r="D250" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E250" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F250" s="44"/>
       <c r="G250" s="44"/>
       <c r="H250" s="44" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="I250" s="44" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="14">
@@ -18863,7 +18895,7 @@
         <v>46201</v>
       </c>
       <c r="B251" s="45" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="C251" s="85">
         <v>1380</v>
@@ -18888,7 +18920,7 @@
         <v>46201</v>
       </c>
       <c r="B252" s="44" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="C252" s="83">
         <v>699</v>
@@ -18902,7 +18934,7 @@
       <c r="F252" s="44"/>
       <c r="G252" s="44"/>
       <c r="H252" s="44" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="I252" s="44" t="s">
         <v>148</v>
@@ -18913,7 +18945,7 @@
         <v>46201</v>
       </c>
       <c r="B253" s="45" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="C253" s="85">
         <v>699</v>
@@ -18927,7 +18959,7 @@
       <c r="F253" s="46"/>
       <c r="G253" s="46"/>
       <c r="H253" s="46" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="I253" s="45" t="s">
         <v>148</v>
@@ -18938,7 +18970,7 @@
         <v>46201</v>
       </c>
       <c r="B254" s="44" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="C254" s="83">
         <v>699</v>
@@ -18952,7 +18984,7 @@
       <c r="F254" s="44"/>
       <c r="G254" s="44"/>
       <c r="H254" s="44" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="I254" s="44" t="s">
         <v>148</v>
@@ -18977,7 +19009,7 @@
       <c r="F255" s="46"/>
       <c r="G255" s="46"/>
       <c r="H255" s="46" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="I255" s="45" t="s">
         <v>148</v>
@@ -18988,7 +19020,7 @@
         <v>46203</v>
       </c>
       <c r="B256" s="44" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="C256" s="83">
         <v>950</v>
@@ -19002,7 +19034,7 @@
       <c r="F256" s="44"/>
       <c r="G256" s="44"/>
       <c r="H256" s="44" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="I256" s="44" t="s">
         <v>148</v>
@@ -19013,7 +19045,7 @@
         <v>46204</v>
       </c>
       <c r="B257" s="45" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="C257" s="85">
         <v>699</v>
@@ -19027,7 +19059,7 @@
       <c r="F257" s="46"/>
       <c r="G257" s="46"/>
       <c r="H257" s="46" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="I257" s="45" t="s">
         <v>148</v>
@@ -19038,7 +19070,7 @@
         <v>46205</v>
       </c>
       <c r="B258" s="44" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C258" s="83">
         <v>1500</v>
@@ -19052,7 +19084,7 @@
       <c r="F258" s="44"/>
       <c r="G258" s="44"/>
       <c r="H258" s="44" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="I258" s="44" t="s">
         <v>148</v>
@@ -19063,7 +19095,7 @@
         <v>46205</v>
       </c>
       <c r="B259" s="45" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C259" s="85">
         <v>1200</v>
@@ -19077,7 +19109,7 @@
       <c r="F259" s="46"/>
       <c r="G259" s="46"/>
       <c r="H259" s="46" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="I259" s="45" t="s">
         <v>148</v>
@@ -19088,7 +19120,7 @@
         <v>46205</v>
       </c>
       <c r="B260" s="44" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="C260" s="83">
         <v>1500</v>
@@ -19102,7 +19134,7 @@
       <c r="F260" s="44"/>
       <c r="G260" s="44"/>
       <c r="H260" s="44" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="I260" s="44" t="s">
         <v>148</v>
@@ -19113,7 +19145,7 @@
         <v>46205</v>
       </c>
       <c r="B261" s="45" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="C261" s="85">
         <v>2600</v>
@@ -19127,7 +19159,7 @@
       <c r="F261" s="46"/>
       <c r="G261" s="46"/>
       <c r="H261" s="46" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="I261" s="45" t="s">
         <v>148</v>
@@ -19138,7 +19170,7 @@
         <v>46206</v>
       </c>
       <c r="B262" s="44" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="C262" s="83">
         <v>1380</v>
@@ -19163,7 +19195,7 @@
         <v>46206</v>
       </c>
       <c r="B263" s="45" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="C263" s="85">
         <v>1380</v>
@@ -19188,7 +19220,7 @@
         <v>46206</v>
       </c>
       <c r="B264" s="44" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="C264" s="83">
         <v>2500</v>
@@ -19202,7 +19234,7 @@
       <c r="F264" s="44"/>
       <c r="G264" s="44"/>
       <c r="H264" s="44" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="I264" s="44" t="s">
         <v>356</v>
@@ -19213,7 +19245,7 @@
         <v>46206</v>
       </c>
       <c r="B265" s="45" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="C265" s="85">
         <v>1300</v>
@@ -19227,7 +19259,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1389</v>
+        <v>1373</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>148</v>
@@ -19238,7 +19270,7 @@
         <v>46206</v>
       </c>
       <c r="B266" s="44" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="C266" s="83">
         <v>1380</v>
@@ -19252,7 +19284,7 @@
       <c r="F266" s="44"/>
       <c r="G266" s="44"/>
       <c r="H266" s="44" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="I266" s="44" t="s">
         <v>148</v>
@@ -19277,7 +19309,7 @@
       <c r="F267" s="46"/>
       <c r="G267" s="46"/>
       <c r="H267" s="46" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="I267" s="45" t="s">
         <v>148</v>
@@ -19288,7 +19320,7 @@
         <v>46208</v>
       </c>
       <c r="B268" s="44" t="s">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="C268" s="83">
         <v>2350</v>
@@ -19298,7 +19330,7 @@
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1284</v>
+        <v>1275</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>356</v>
@@ -19309,7 +19341,7 @@
         <v>46209</v>
       </c>
       <c r="B269" s="45" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="C269" s="85">
         <v>1100</v>
@@ -19323,7 +19355,7 @@
       <c r="F269" s="46"/>
       <c r="G269" s="46"/>
       <c r="H269" s="46" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="I269" s="45" t="s">
         <v>148</v>
@@ -19334,7 +19366,7 @@
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -19348,7 +19380,7 @@
       <c r="F270" s="44"/>
       <c r="G270" s="44"/>
       <c r="H270" s="44" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="I270" s="44" t="s">
         <v>148</v>
@@ -19359,7 +19391,7 @@
         <v>46211</v>
       </c>
       <c r="B271" s="45" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="C271" s="85">
         <v>1380</v>
@@ -19373,7 +19405,7 @@
       <c r="F271" s="46"/>
       <c r="G271" s="46"/>
       <c r="H271" s="46" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="I271" s="45" t="s">
         <v>148</v>
@@ -19384,7 +19416,7 @@
         <v>46215</v>
       </c>
       <c r="B272" s="44" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="C272" s="83">
         <v>1380</v>
@@ -19409,7 +19441,7 @@
         <v>46215</v>
       </c>
       <c r="B273" s="45" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="C273" s="85">
         <v>699</v>
@@ -19423,7 +19455,7 @@
       <c r="F273" s="46"/>
       <c r="G273" s="46"/>
       <c r="H273" s="46" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="I273" s="45" t="s">
         <v>148</v>
@@ -19448,7 +19480,7 @@
       <c r="F274" s="44"/>
       <c r="G274" s="44"/>
       <c r="H274" s="44" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="I274" s="44" t="s">
         <v>148</v>
@@ -19459,7 +19491,7 @@
         <v>46216</v>
       </c>
       <c r="B275" s="45" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="C275" s="85">
         <v>699</v>
@@ -19473,7 +19505,7 @@
       <c r="F275" s="46"/>
       <c r="G275" s="46"/>
       <c r="H275" s="46" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="I275" s="45" t="s">
         <v>148</v>
@@ -19484,7 +19516,7 @@
         <v>46216</v>
       </c>
       <c r="B276" s="44" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C276" s="83">
         <v>3000</v>
@@ -19498,7 +19530,7 @@
       <c r="F276" s="44"/>
       <c r="G276" s="44"/>
       <c r="H276" s="44" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="I276" s="44" t="s">
         <v>148</v>
@@ -19509,7 +19541,7 @@
         <v>46219</v>
       </c>
       <c r="B277" s="45" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="C277" s="85">
         <v>1380</v>
@@ -19573,7 +19605,7 @@
       <c r="F279" s="46"/>
       <c r="G279" s="46"/>
       <c r="H279" s="46" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="I279" s="45" t="s">
         <v>148</v>
@@ -19598,7 +19630,7 @@
       <c r="F280" s="44"/>
       <c r="G280" s="44"/>
       <c r="H280" s="44" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="I280" s="44" t="s">
         <v>148</v>
@@ -19609,7 +19641,7 @@
         <v>46219</v>
       </c>
       <c r="B281" s="45" t="s">
-        <v>1344</v>
+        <v>1334</v>
       </c>
       <c r="C281" s="85">
         <v>3600</v>
@@ -19623,7 +19655,7 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1346</v>
+        <v>1336</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
@@ -19634,7 +19666,7 @@
         <v>46220</v>
       </c>
       <c r="B282" s="44" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="C282" s="83">
         <v>1500</v>
@@ -19648,7 +19680,7 @@
       <c r="F282" s="44"/>
       <c r="G282" s="44"/>
       <c r="H282" s="44" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="I282" s="44" t="s">
         <v>148</v>
@@ -19659,7 +19691,7 @@
         <v>46221</v>
       </c>
       <c r="B283" s="45" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="C283" s="85">
         <v>1100</v>
@@ -19673,7 +19705,7 @@
       <c r="F283" s="46"/>
       <c r="G283" s="46"/>
       <c r="H283" s="46" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="I283" s="45" t="s">
         <v>148</v>
@@ -19684,7 +19716,7 @@
         <v>46222</v>
       </c>
       <c r="B284" s="44" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="C284" s="83">
         <v>850</v>
@@ -19698,7 +19730,7 @@
       <c r="F284" s="44"/>
       <c r="G284" s="44"/>
       <c r="H284" s="44" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="I284" s="44" t="s">
         <v>148</v>
@@ -19709,7 +19741,7 @@
         <v>46222</v>
       </c>
       <c r="B285" s="45" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="C285" s="85">
         <v>1250</v>
@@ -19723,7 +19755,7 @@
       <c r="F285" s="46"/>
       <c r="G285" s="46"/>
       <c r="H285" s="46" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="I285" s="45" t="s">
         <v>148</v>
@@ -19734,7 +19766,7 @@
         <v>46222</v>
       </c>
       <c r="B286" s="44" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C286" s="83">
         <v>700</v>
@@ -19759,7 +19791,7 @@
         <v>46222</v>
       </c>
       <c r="B287" s="45" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="C287" s="85">
         <v>699</v>
@@ -19784,7 +19816,7 @@
         <v>46223</v>
       </c>
       <c r="B288" s="44" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="C288" s="83">
         <v>1380</v>
@@ -19798,7 +19830,7 @@
       <c r="F288" s="44"/>
       <c r="G288" s="44"/>
       <c r="H288" s="44" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="I288" s="44" t="s">
         <v>148</v>
@@ -19809,7 +19841,7 @@
         <v>46224</v>
       </c>
       <c r="B289" s="45" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="C289" s="85">
         <v>1380</v>
@@ -19823,7 +19855,7 @@
       <c r="F289" s="46"/>
       <c r="G289" s="46"/>
       <c r="H289" s="46" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="I289" s="45" t="s">
         <v>148</v>
@@ -19834,7 +19866,7 @@
         <v>46224</v>
       </c>
       <c r="B290" s="44" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="C290" s="83">
         <v>1380</v>
@@ -19848,7 +19880,7 @@
       <c r="F290" s="44"/>
       <c r="G290" s="44"/>
       <c r="H290" s="44" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="I290" s="44" t="s">
         <v>148</v>
@@ -19873,7 +19905,7 @@
       <c r="F291" s="44"/>
       <c r="G291" s="44"/>
       <c r="H291" s="44" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="I291" s="44" t="s">
         <v>148</v>
@@ -19884,7 +19916,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1391</v>
+        <v>1375</v>
       </c>
       <c r="C292" s="85">
         <v>3600</v>
@@ -19894,7 +19926,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1390</v>
+        <v>1374</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19905,7 +19937,7 @@
         <v>46229</v>
       </c>
       <c r="B293" s="44" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="C293" s="83">
         <v>2230</v>
@@ -19915,7 +19947,7 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1309</v>
+        <v>1300</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
@@ -19926,7 +19958,7 @@
         <v>46229</v>
       </c>
       <c r="B294" s="45" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="C294" s="85">
         <v>2230</v>
@@ -19940,7 +19972,7 @@
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1292</v>
+        <v>1283</v>
       </c>
       <c r="I294" s="45" t="s">
         <v>148</v>
@@ -19951,13 +19983,13 @@
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="C295" s="83">
         <v>3700</v>
       </c>
       <c r="D295" s="44" t="s">
-        <v>1281</v>
+        <v>1272</v>
       </c>
       <c r="E295" s="44" t="s">
         <v>49</v>
@@ -19965,7 +19997,7 @@
       <c r="F295" s="44"/>
       <c r="G295" s="44"/>
       <c r="H295" s="44" t="s">
-        <v>1282</v>
+        <v>1273</v>
       </c>
       <c r="I295" s="44" t="s">
         <v>148</v>
@@ -19976,7 +20008,7 @@
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1210</v>
+        <v>1203</v>
       </c>
       <c r="C296" s="85">
         <v>1450</v>
@@ -19990,7 +20022,7 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
@@ -20001,7 +20033,7 @@
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -20015,7 +20047,7 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1288</v>
+        <v>1279</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
@@ -20026,7 +20058,7 @@
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="C298" s="85">
         <v>1479</v>
@@ -20040,7 +20072,7 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
@@ -20051,7 +20083,7 @@
         <v>46236</v>
       </c>
       <c r="B299" s="44" t="s">
-        <v>1217</v>
+        <v>1210</v>
       </c>
       <c r="C299" s="83">
         <v>2630</v>
@@ -20065,7 +20097,7 @@
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
       <c r="H299" s="44" t="s">
-        <v>1215</v>
+        <v>1208</v>
       </c>
       <c r="I299" s="44" t="s">
         <v>148</v>
@@ -20076,7 +20108,7 @@
         <v>46238</v>
       </c>
       <c r="B300" s="45" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="C300" s="85">
         <v>1380</v>
@@ -20101,7 +20133,7 @@
         <v>46238</v>
       </c>
       <c r="B301" s="44" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C301" s="83">
         <v>12650</v>
@@ -20115,7 +20147,7 @@
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
       <c r="H301" s="44" t="s">
-        <v>1289</v>
+        <v>1280</v>
       </c>
       <c r="I301" s="44" t="s">
         <v>148</v>
@@ -20126,7 +20158,7 @@
         <v>46240</v>
       </c>
       <c r="B302" s="45" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="C302" s="85">
         <v>1000</v>
@@ -20136,13 +20168,13 @@
       <c r="F302" s="46"/>
       <c r="G302" s="46"/>
       <c r="H302" s="46" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="I302" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="42">
+    <row r="303" spans="1:9" ht="28">
       <c r="A303" s="82">
         <v>46241</v>
       </c>
@@ -20152,15 +20184,19 @@
       <c r="C303" s="83">
         <v>4750</v>
       </c>
-      <c r="D303" s="44"/>
-      <c r="E303" s="44"/>
+      <c r="D303" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E303" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="I303" s="44" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="304" spans="1:9" ht="14">
@@ -20168,7 +20204,7 @@
         <v>46243</v>
       </c>
       <c r="B304" s="45" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
       <c r="C304" s="85">
         <v>950</v>
@@ -20182,7 +20218,7 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1388</v>
+        <v>1372</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>148</v>
@@ -20193,7 +20229,7 @@
         <v>46243</v>
       </c>
       <c r="B305" s="44" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
       <c r="C305" s="83">
         <v>1380</v>
@@ -20207,7 +20243,7 @@
       <c r="F305" s="44"/>
       <c r="G305" s="44"/>
       <c r="H305" s="44" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="I305" s="44" t="s">
         <v>148</v>
@@ -20218,7 +20254,7 @@
         <v>46243</v>
       </c>
       <c r="B306" s="45" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="C306" s="85">
         <v>1250</v>
@@ -20232,7 +20268,7 @@
       <c r="F306" s="46"/>
       <c r="G306" s="46"/>
       <c r="H306" s="46" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
       <c r="I306" s="45" t="s">
         <v>148</v>
@@ -20243,7 +20279,7 @@
         <v>46243</v>
       </c>
       <c r="B307" s="44" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C307" s="83">
         <v>5750</v>
@@ -20257,7 +20293,7 @@
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
       <c r="H307" s="44" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="I307" s="44" t="s">
         <v>148</v>
@@ -20268,7 +20304,7 @@
         <v>46248</v>
       </c>
       <c r="B308" s="44" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="C308" s="83">
         <v>1380</v>
@@ -20282,7 +20318,7 @@
       <c r="F308" s="44"/>
       <c r="G308" s="44"/>
       <c r="H308" s="44" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="I308" s="44" t="s">
         <v>148</v>
@@ -20293,7 +20329,7 @@
         <v>46248</v>
       </c>
       <c r="B309" s="45" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="C309" s="85">
         <v>1380</v>
@@ -20307,7 +20343,7 @@
       <c r="F309" s="46"/>
       <c r="G309" s="46"/>
       <c r="H309" s="46" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="I309" s="45" t="s">
         <v>148</v>
@@ -20332,7 +20368,7 @@
       <c r="F310" s="44"/>
       <c r="G310" s="44"/>
       <c r="H310" s="44" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="I310" s="44" t="s">
         <v>148</v>
@@ -20357,7 +20393,7 @@
       <c r="F311" s="46"/>
       <c r="G311" s="46"/>
       <c r="H311" s="46" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="I311" s="45" t="s">
         <v>148</v>
@@ -20368,7 +20404,7 @@
         <v>46250</v>
       </c>
       <c r="B312" s="44" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="C312" s="83">
         <v>2250</v>
@@ -20382,7 +20418,7 @@
       <c r="F312" s="44"/>
       <c r="G312" s="44"/>
       <c r="H312" s="44" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
       <c r="I312" s="44" t="s">
         <v>148</v>
@@ -20393,7 +20429,7 @@
         <v>46252</v>
       </c>
       <c r="B313" s="45" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C313" s="85">
         <v>5750</v>
@@ -20407,7 +20443,7 @@
       <c r="F313" s="46"/>
       <c r="G313" s="46"/>
       <c r="H313" s="46" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="I313" s="45" t="s">
         <v>148</v>
@@ -20418,7 +20454,7 @@
         <v>46252</v>
       </c>
       <c r="B314" s="44" t="s">
-        <v>1290</v>
+        <v>1281</v>
       </c>
       <c r="C314" s="83">
         <v>1380</v>
@@ -20432,7 +20468,7 @@
       <c r="F314" s="44"/>
       <c r="G314" s="44"/>
       <c r="H314" s="44" t="s">
-        <v>1301</v>
+        <v>1292</v>
       </c>
       <c r="I314" s="44" t="s">
         <v>148</v>
@@ -20443,7 +20479,7 @@
         <v>46252</v>
       </c>
       <c r="B315" s="45" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C315" s="85">
         <v>5750</v>
@@ -20457,7 +20493,7 @@
       <c r="F315" s="46"/>
       <c r="G315" s="46"/>
       <c r="H315" s="46" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="I315" s="45" t="s">
         <v>148</v>
@@ -20468,20 +20504,24 @@
         <v>46252</v>
       </c>
       <c r="B316" s="44" t="s">
-        <v>1294</v>
+        <v>1285</v>
       </c>
       <c r="C316" s="83">
-        <v>1380</v>
-      </c>
-      <c r="D316" s="44"/>
-      <c r="E316" s="44"/>
+        <v>1340</v>
+      </c>
+      <c r="D316" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E316" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F316" s="44"/>
       <c r="G316" s="44"/>
       <c r="H316" s="44" t="s">
-        <v>1295</v>
+        <v>1286</v>
       </c>
       <c r="I316" s="44" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="317" spans="1:9" ht="14">
@@ -20489,7 +20529,7 @@
         <v>46252</v>
       </c>
       <c r="B317" s="45" t="s">
-        <v>1297</v>
+        <v>1288</v>
       </c>
       <c r="C317" s="85">
         <v>1250</v>
@@ -20503,7 +20543,7 @@
       <c r="F317" s="46"/>
       <c r="G317" s="46"/>
       <c r="H317" s="46" t="s">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="I317" s="45" t="s">
         <v>148</v>
@@ -20514,7 +20554,7 @@
         <v>46257</v>
       </c>
       <c r="B318" s="44" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C318" s="83">
         <v>1780</v>
@@ -20528,7 +20568,7 @@
       <c r="F318" s="44"/>
       <c r="G318" s="44"/>
       <c r="H318" s="44" t="s">
-        <v>1302</v>
+        <v>1293</v>
       </c>
       <c r="I318" s="44" t="s">
         <v>148</v>
@@ -20553,7 +20593,7 @@
       <c r="F319" s="46"/>
       <c r="G319" s="46"/>
       <c r="H319" s="46" t="s">
-        <v>1305</v>
+        <v>1296</v>
       </c>
       <c r="I319" s="45" t="s">
         <v>148</v>
@@ -20578,7 +20618,7 @@
       <c r="F320" s="44"/>
       <c r="G320" s="44"/>
       <c r="H320" s="44" t="s">
-        <v>1308</v>
+        <v>1299</v>
       </c>
       <c r="I320" s="44" t="s">
         <v>148</v>
@@ -20589,7 +20629,7 @@
         <v>46257</v>
       </c>
       <c r="B321" s="45" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="C321" s="85">
         <v>1500</v>
@@ -20603,7 +20643,7 @@
       <c r="F321" s="46"/>
       <c r="G321" s="46"/>
       <c r="H321" s="46" t="s">
-        <v>1313</v>
+        <v>1304</v>
       </c>
       <c r="I321" s="45" t="s">
         <v>148</v>
@@ -20614,7 +20654,7 @@
         <v>46258</v>
       </c>
       <c r="B322" s="44" t="s">
-        <v>1314</v>
+        <v>1305</v>
       </c>
       <c r="C322" s="83">
         <v>1250</v>
@@ -20628,7 +20668,7 @@
       <c r="F322" s="44"/>
       <c r="G322" s="44"/>
       <c r="H322" s="44" t="s">
-        <v>1315</v>
+        <v>1306</v>
       </c>
       <c r="I322" s="44" t="s">
         <v>148</v>
@@ -20639,7 +20679,7 @@
         <v>46263</v>
       </c>
       <c r="B323" s="45" t="s">
-        <v>1334</v>
+        <v>1325</v>
       </c>
       <c r="C323" s="85">
         <v>1380</v>
@@ -20653,7 +20693,7 @@
       <c r="F323" s="46"/>
       <c r="G323" s="46"/>
       <c r="H323" s="46" t="s">
-        <v>1335</v>
+        <v>1326</v>
       </c>
       <c r="I323" s="45" t="s">
         <v>148</v>
@@ -20664,7 +20704,7 @@
         <v>46263</v>
       </c>
       <c r="B324" s="44" t="s">
-        <v>1337</v>
+        <v>1328</v>
       </c>
       <c r="C324" s="83">
         <v>1380</v>
@@ -20678,7 +20718,7 @@
       <c r="F324" s="44"/>
       <c r="G324" s="44"/>
       <c r="H324" s="44" t="s">
-        <v>1338</v>
+        <v>1329</v>
       </c>
       <c r="I324" s="44" t="s">
         <v>148</v>
@@ -20689,7 +20729,7 @@
         <v>46263</v>
       </c>
       <c r="B325" s="45" t="s">
-        <v>1339</v>
+        <v>1330</v>
       </c>
       <c r="C325" s="85">
         <v>2500</v>
@@ -20703,7 +20743,7 @@
       <c r="F325" s="46"/>
       <c r="G325" s="46"/>
       <c r="H325" s="46" t="s">
-        <v>1350</v>
+        <v>1340</v>
       </c>
       <c r="I325" s="45" t="s">
         <v>148</v>
@@ -20728,7 +20768,7 @@
       <c r="F326" s="44"/>
       <c r="G326" s="44"/>
       <c r="H326" s="44" t="s">
-        <v>1349</v>
+        <v>1339</v>
       </c>
       <c r="I326" s="44" t="s">
         <v>148</v>
@@ -20739,7 +20779,7 @@
         <v>46257</v>
       </c>
       <c r="B327" s="45" t="s">
-        <v>1351</v>
+        <v>1341</v>
       </c>
       <c r="C327" s="85">
         <v>750</v>
@@ -20753,7 +20793,7 @@
       <c r="F327" s="46"/>
       <c r="G327" s="46"/>
       <c r="H327" s="46" t="s">
-        <v>1352</v>
+        <v>1342</v>
       </c>
       <c r="I327" s="45" t="s">
         <v>148</v>
@@ -20761,67 +20801,103 @@
     </row>
     <row r="328" spans="1:9" ht="14">
       <c r="A328" s="82">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="B328" s="44" t="s">
-        <v>414</v>
+        <v>1379</v>
       </c>
       <c r="C328" s="83">
-        <v>1250</v>
-      </c>
-      <c r="D328" s="44"/>
-      <c r="E328" s="44"/>
+        <v>1380</v>
+      </c>
+      <c r="D328" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E328" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F328" s="44"/>
       <c r="G328" s="44"/>
       <c r="H328" s="44" t="s">
         <v>1381</v>
       </c>
       <c r="I328" s="44" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="329" spans="1:9" ht="14">
-      <c r="A329" s="84" t="s">
-        <v>1383</v>
+      <c r="A329" s="84">
+        <v>46272</v>
       </c>
       <c r="B329" s="45" t="s">
-        <v>1384</v>
+        <v>414</v>
       </c>
       <c r="C329" s="85">
-        <v>1850</v>
-      </c>
-      <c r="D329" s="45"/>
-      <c r="E329" s="45"/>
+        <v>2400</v>
+      </c>
+      <c r="D329" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E329" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F329" s="46"/>
       <c r="G329" s="46"/>
       <c r="H329" s="46" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="I329" s="45" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="330" spans="1:9">
-      <c r="A330" s="82"/>
-      <c r="B330" s="44"/>
-      <c r="C330" s="83"/>
-      <c r="D330" s="44"/>
-      <c r="E330" s="44"/>
+    <row r="330" spans="1:9" ht="14">
+      <c r="A330" s="82">
+        <v>46275</v>
+      </c>
+      <c r="B330" s="44" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C330" s="83">
+        <v>1450</v>
+      </c>
+      <c r="D330" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E330" s="44" t="s">
+        <v>50</v>
+      </c>
       <c r="F330" s="44"/>
       <c r="G330" s="44"/>
-      <c r="H330" s="44"/>
-      <c r="I330" s="44"/>
-    </row>
-    <row r="331" spans="1:9">
-      <c r="A331" s="84"/>
-      <c r="B331" s="45"/>
-      <c r="C331" s="85"/>
-      <c r="D331" s="45"/>
-      <c r="E331" s="45"/>
+      <c r="H330" s="44" t="s">
+        <v>1387</v>
+      </c>
+      <c r="I330" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="14">
+      <c r="A331" s="84">
+        <v>46275</v>
+      </c>
+      <c r="B331" s="45" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C331" s="85">
+        <v>950</v>
+      </c>
+      <c r="D331" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="E331" s="45" t="s">
+        <v>50</v>
+      </c>
       <c r="F331" s="46"/>
       <c r="G331" s="46"/>
-      <c r="H331" s="46"/>
-      <c r="I331" s="45"/>
+      <c r="H331" s="46" t="s">
+        <v>1392</v>
+      </c>
+      <c r="I331" s="45" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="82"/>
@@ -27687,7 +27763,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="55" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="M59" s="55"/>
       <c r="N59" s="55" t="s">
@@ -28677,10 +28753,10 @@
         <v>1560</v>
       </c>
       <c r="F78" s="53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" s="53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="52">
         <f t="shared" si="4"/>
@@ -28692,21 +28768,21 @@
       </c>
       <c r="J78" s="52">
         <f t="shared" si="5"/>
-        <v>3225</v>
+        <v>4300</v>
       </c>
       <c r="K78" s="52">
         <f t="shared" si="6"/>
-        <v>1075</v>
+        <v>0</v>
       </c>
       <c r="L78" s="52" t="s">
-        <v>673</v>
+        <v>1388</v>
       </c>
       <c r="M78" s="52"/>
       <c r="N78" s="52" t="s">
-        <v>589</v>
+        <v>504</v>
       </c>
       <c r="O78" s="52" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P78" s="52"/>
       <c r="Q78" s="52"/>
@@ -28716,10 +28792,10 @@
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1">
       <c r="A79" s="55" t="s">
+        <v>674</v>
+      </c>
+      <c r="B79" s="55" t="s">
         <v>675</v>
-      </c>
-      <c r="B79" s="55" t="s">
-        <v>676</v>
       </c>
       <c r="C79" s="55" t="s">
         <v>96</v>
@@ -28753,14 +28829,14 @@
         <v>0</v>
       </c>
       <c r="L79" s="55" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="M79" s="55"/>
       <c r="N79" s="55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O79" s="55" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P79" s="55"/>
       <c r="Q79" s="55"/>
@@ -28770,10 +28846,10 @@
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1">
       <c r="A80" s="52" t="s">
+        <v>678</v>
+      </c>
+      <c r="B80" s="52" t="s">
         <v>679</v>
-      </c>
-      <c r="B80" s="52" t="s">
-        <v>680</v>
       </c>
       <c r="C80" s="52" t="s">
         <v>96</v>
@@ -28807,14 +28883,14 @@
         <v>1230</v>
       </c>
       <c r="L80" s="52" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="M80" s="52"/>
       <c r="N80" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O80" s="52" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P80" s="52"/>
       <c r="Q80" s="52"/>
@@ -28824,10 +28900,10 @@
     </row>
     <row r="81" spans="1:20" ht="30" customHeight="1">
       <c r="A81" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="B81" s="55" t="s">
         <v>683</v>
-      </c>
-      <c r="B81" s="55" t="s">
-        <v>684</v>
       </c>
       <c r="C81" s="55" t="s">
         <v>96</v>
@@ -28861,7 +28937,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="55" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="M81" s="55"/>
       <c r="N81" s="55" t="s">
@@ -28876,10 +28952,10 @@
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1">
       <c r="A82" s="52" t="s">
+        <v>685</v>
+      </c>
+      <c r="B82" s="52" t="s">
         <v>686</v>
-      </c>
-      <c r="B82" s="52" t="s">
-        <v>687</v>
       </c>
       <c r="C82" s="52" t="s">
         <v>96</v>
@@ -28913,7 +28989,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="52" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="M82" s="52"/>
       <c r="N82" s="52" t="s">
@@ -28928,10 +29004,10 @@
     </row>
     <row r="83" spans="1:20" ht="30" customHeight="1">
       <c r="A83" s="55" t="s">
+        <v>688</v>
+      </c>
+      <c r="B83" s="55" t="s">
         <v>689</v>
-      </c>
-      <c r="B83" s="55" t="s">
-        <v>690</v>
       </c>
       <c r="C83" s="55" t="s">
         <v>96</v>
@@ -28965,14 +29041,14 @@
         <v>0</v>
       </c>
       <c r="L83" s="55" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M83" s="55"/>
       <c r="N83" s="55" t="s">
         <v>504</v>
       </c>
       <c r="O83" s="55" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="P83" s="55"/>
       <c r="Q83" s="55"/>
@@ -28982,10 +29058,10 @@
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1">
       <c r="A84" s="52" t="s">
+        <v>692</v>
+      </c>
+      <c r="B84" s="52" t="s">
         <v>693</v>
-      </c>
-      <c r="B84" s="52" t="s">
-        <v>694</v>
       </c>
       <c r="C84" s="52" t="s">
         <v>96</v>
@@ -28997,10 +29073,10 @@
         <v>650</v>
       </c>
       <c r="F84" s="53">
+        <v>2</v>
+      </c>
+      <c r="G84" s="53">
         <v>1</v>
-      </c>
-      <c r="G84" s="53">
-        <v>2</v>
       </c>
       <c r="H84" s="52">
         <f t="shared" si="4"/>
@@ -29012,21 +29088,21 @@
       </c>
       <c r="J84" s="52">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="K84" s="52">
         <f t="shared" si="6"/>
-        <v>900</v>
+        <v>450</v>
       </c>
       <c r="L84" s="52" t="s">
-        <v>695</v>
+        <v>1386</v>
       </c>
       <c r="M84" s="52"/>
       <c r="N84" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O84" s="52" t="s">
-        <v>696</v>
+        <v>1385</v>
       </c>
       <c r="P84" s="52"/>
       <c r="Q84" s="52"/>
@@ -29036,10 +29112,10 @@
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1">
       <c r="A85" s="55" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B85" s="55" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C85" s="55" t="s">
         <v>96</v>
@@ -29073,7 +29149,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="55" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="M85" s="55"/>
       <c r="N85" s="55" t="s">
@@ -29088,10 +29164,10 @@
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1">
       <c r="A86" s="52" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B86" s="52" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C86" s="52" t="s">
         <v>96</v>
@@ -29103,10 +29179,10 @@
         <v>1495</v>
       </c>
       <c r="F86" s="53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" s="53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" s="52">
         <f t="shared" si="4"/>
@@ -29118,21 +29194,21 @@
       </c>
       <c r="J86" s="52">
         <f t="shared" si="5"/>
-        <v>2090</v>
+        <v>3135</v>
       </c>
       <c r="K86" s="52">
         <f t="shared" si="6"/>
-        <v>2090</v>
+        <v>1045</v>
       </c>
       <c r="L86" s="52" t="s">
-        <v>702</v>
+        <v>1389</v>
       </c>
       <c r="M86" s="52"/>
       <c r="N86" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O86" s="52" t="s">
-        <v>703</v>
+        <v>1390</v>
       </c>
       <c r="P86" s="52"/>
       <c r="Q86" s="52"/>
@@ -29142,10 +29218,10 @@
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1">
       <c r="A87" s="55" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="B87" s="55" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C87" s="55" t="s">
         <v>96</v>
@@ -29181,10 +29257,10 @@
       <c r="L87" s="55"/>
       <c r="M87" s="55"/>
       <c r="N87" s="55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O87" s="55" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="P87" s="55"/>
       <c r="Q87" s="55"/>
@@ -29194,10 +29270,10 @@
     </row>
     <row r="88" spans="1:20" ht="30" customHeight="1">
       <c r="A88" s="52" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B88" s="52" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="C88" s="52" t="s">
         <v>96</v>
@@ -29231,7 +29307,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="52" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="M88" s="52"/>
       <c r="N88" s="52" t="s">
@@ -29246,10 +29322,10 @@
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1">
       <c r="A89" s="55" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="B89" s="55" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="C89" s="55" t="s">
         <v>95</v>
@@ -29283,7 +29359,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="55" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="M89" s="55"/>
       <c r="N89" s="55" t="s">
@@ -29298,10 +29374,10 @@
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1">
       <c r="A90" s="52" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="B90" s="52" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="C90" s="52" t="s">
         <v>95</v>
@@ -29350,13 +29426,13 @@
     </row>
     <row r="91" spans="1:20" ht="15" customHeight="1">
       <c r="A91" s="55" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="D91" s="56">
         <v>389</v>
@@ -29387,7 +29463,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="55" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="M91" s="55"/>
       <c r="N91" s="55" t="s">
@@ -29402,13 +29478,13 @@
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1">
       <c r="A92" s="52" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B92" s="52" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C92" s="52" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="D92" s="53">
         <v>489</v>
@@ -29439,7 +29515,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="52" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="M92" s="52"/>
       <c r="N92" s="52" t="s">
@@ -29454,10 +29530,10 @@
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1">
       <c r="A93" s="55" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C93" s="55" t="s">
         <v>97</v>
@@ -29491,7 +29567,7 @@
         <v>472</v>
       </c>
       <c r="L93" s="55" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="M93" s="55"/>
       <c r="N93" s="52" t="s">
@@ -29508,10 +29584,10 @@
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1">
       <c r="A94" s="52" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B94" s="52" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C94" s="52" t="s">
         <v>95</v>
@@ -29560,10 +29636,10 @@
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1">
       <c r="A95" s="55" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="B95" s="55" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C95" s="55" t="s">
         <v>95</v>
@@ -29597,7 +29673,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="55" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="M95" s="55"/>
       <c r="N95" s="55" t="s">
@@ -29612,10 +29688,10 @@
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1">
       <c r="A96" s="52" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B96" s="52" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C96" s="52" t="s">
         <v>95</v>
@@ -29662,10 +29738,10 @@
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1">
       <c r="A97" s="55" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="C97" s="55" t="s">
         <v>95</v>
@@ -29714,10 +29790,10 @@
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1">
       <c r="A98" s="52" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B98" s="52" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C98" s="52" t="s">
         <v>96</v>
@@ -29768,10 +29844,10 @@
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1">
       <c r="A99" s="55" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="B99" s="55" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C99" s="55" t="s">
         <v>96</v>
@@ -29822,10 +29898,10 @@
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1">
       <c r="A100" s="52" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="B100" s="52" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="C100" s="52" t="s">
         <v>96</v>
@@ -29876,10 +29952,10 @@
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1">
       <c r="A101" s="55" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="C101" s="55" t="s">
         <v>96</v>
@@ -29930,10 +30006,10 @@
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1">
       <c r="A102" s="52" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="B102" s="52" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C102" s="52" t="s">
         <v>96</v>
@@ -29984,10 +30060,10 @@
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1">
       <c r="A103" s="55" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C103" s="55" t="s">
         <v>96</v>
@@ -30038,10 +30114,10 @@
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1">
       <c r="A104" s="52" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B104" s="52" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C104" s="52" t="s">
         <v>96</v>
@@ -30092,10 +30168,10 @@
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1">
       <c r="A105" s="55" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="B105" s="55" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C105" s="55" t="s">
         <v>96</v>
@@ -30146,10 +30222,10 @@
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1">
       <c r="A106" s="52" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B106" s="52" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C106" s="52" t="s">
         <v>96</v>
@@ -30200,10 +30276,10 @@
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1">
       <c r="A107" s="55" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B107" s="55" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C107" s="55" t="s">
         <v>96</v>
@@ -30254,10 +30330,10 @@
     </row>
     <row r="108" spans="1:20" ht="15" customHeight="1">
       <c r="A108" s="52" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B108" s="52" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C108" s="52" t="s">
         <v>96</v>
@@ -30308,10 +30384,10 @@
     </row>
     <row r="109" spans="1:20" ht="15" customHeight="1">
       <c r="A109" s="55" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B109" s="55" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C109" s="55" t="s">
         <v>96</v>
@@ -30362,10 +30438,10 @@
     </row>
     <row r="110" spans="1:20" ht="15" customHeight="1">
       <c r="A110" s="52" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B110" s="52" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C110" s="52" t="s">
         <v>96</v>
@@ -30416,10 +30492,10 @@
     </row>
     <row r="111" spans="1:20" ht="15" customHeight="1">
       <c r="A111" s="55" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B111" s="55" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C111" s="55" t="s">
         <v>96</v>
@@ -30470,10 +30546,10 @@
     </row>
     <row r="112" spans="1:20" ht="15" customHeight="1">
       <c r="A112" s="52" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B112" s="52" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="C112" s="52" t="s">
         <v>96</v>
@@ -30507,7 +30583,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="52" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="M112" s="52"/>
       <c r="N112" s="52" t="s">
@@ -30524,10 +30600,10 @@
     </row>
     <row r="113" spans="1:246" ht="15" customHeight="1">
       <c r="A113" s="55" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B113" s="55" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C113" s="55" t="s">
         <v>96</v>
@@ -30578,10 +30654,10 @@
     </row>
     <row r="114" spans="1:246" ht="15" customHeight="1">
       <c r="A114" s="52" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B114" s="52" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C114" s="52" t="s">
         <v>95</v>
@@ -30630,10 +30706,10 @@
     </row>
     <row r="115" spans="1:246" ht="30" customHeight="1">
       <c r="A115" s="55" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="B115" s="55" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="C115" s="55" t="s">
         <v>95</v>
@@ -30667,7 +30743,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="55" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="M115" s="55"/>
       <c r="N115" s="55" t="s">
@@ -30682,10 +30758,10 @@
     </row>
     <row r="116" spans="1:246" ht="150" customHeight="1">
       <c r="A116" s="52" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="B116" s="52" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C116" s="52" t="s">
         <v>95</v>
@@ -30719,7 +30795,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="52" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="M116" s="52"/>
       <c r="N116" s="52" t="s">
@@ -30734,10 +30810,10 @@
     </row>
     <row r="117" spans="1:246" ht="15" customHeight="1">
       <c r="A117" s="55" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="B117" s="55" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C117" s="55" t="s">
         <v>95</v>
@@ -30786,10 +30862,10 @@
     </row>
     <row r="118" spans="1:246" ht="15" customHeight="1">
       <c r="A118" s="52" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B118" s="52" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C118" s="52" t="s">
         <v>95</v>
@@ -30823,7 +30899,7 @@
         <v>2095.8000000000002</v>
       </c>
       <c r="L118" s="52" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="M118" s="52"/>
       <c r="N118" s="52" t="s">
@@ -30831,7 +30907,7 @@
       </c>
       <c r="O118" s="52"/>
       <c r="P118" s="52" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="Q118" s="52"/>
       <c r="R118" s="52"/>
@@ -30840,10 +30916,10 @@
     </row>
     <row r="119" spans="1:246" ht="15" customHeight="1">
       <c r="A119" s="55" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B119" s="55" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="C119" s="55" t="s">
         <v>95</v>
@@ -30892,10 +30968,10 @@
     </row>
     <row r="120" spans="1:246" ht="181.5" customHeight="1">
       <c r="A120" s="52" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B120" s="52" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="C120" s="52" t="s">
         <v>95</v>
@@ -30929,7 +31005,7 @@
         <v>4608.486666666663</v>
       </c>
       <c r="L120" s="52" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="M120" s="52" t="s">
         <v>49</v>
@@ -30939,7 +31015,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1361</v>
+        <v>1351</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -30948,10 +31024,10 @@
     </row>
     <row r="121" spans="1:246" ht="15" customHeight="1">
       <c r="A121" s="55" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="B121" s="55" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="C121" s="55" t="s">
         <v>95</v>
@@ -30985,7 +31061,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="55" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="M121" s="55"/>
       <c r="N121" s="55" t="s">
@@ -30993,7 +31069,7 @@
       </c>
       <c r="O121" s="55"/>
       <c r="P121" s="55" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="Q121" s="55"/>
       <c r="R121" s="55"/>
@@ -31002,10 +31078,10 @@
     </row>
     <row r="122" spans="1:246" ht="15" customHeight="1">
       <c r="A122" s="52" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B122" s="52" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C122" s="52" t="s">
         <v>96</v>
@@ -31039,7 +31115,7 @@
         <v>4700</v>
       </c>
       <c r="L122" s="52" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="M122" s="52"/>
       <c r="N122" s="52" t="s">
@@ -31054,10 +31130,10 @@
     </row>
     <row r="123" spans="1:246" s="58" customFormat="1" ht="75" customHeight="1">
       <c r="A123" s="63" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B123" s="63" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C123" s="63" t="s">
         <v>95</v>
@@ -31091,7 +31167,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="63" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="M123" s="63"/>
       <c r="N123" s="63" t="s">
@@ -31332,10 +31408,10 @@
     </row>
     <row r="124" spans="1:246" s="68" customFormat="1" ht="30" customHeight="1">
       <c r="A124" s="65" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B124" s="65" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C124" s="65" t="s">
         <v>95</v>
@@ -31369,7 +31445,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="65" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="M124" s="65"/>
       <c r="N124" s="65" t="s">
@@ -31612,10 +31688,10 @@
     </row>
     <row r="125" spans="1:246" s="58" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="63" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B125" s="63" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="C125" s="63" t="s">
         <v>95</v>
@@ -31649,7 +31725,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="63" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="M125" s="63"/>
       <c r="N125" s="63" t="s">
@@ -31657,7 +31733,7 @@
       </c>
       <c r="O125" s="63"/>
       <c r="P125" s="63" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="Q125" s="63"/>
       <c r="R125" s="63"/>
@@ -31892,10 +31968,10 @@
     </row>
     <row r="126" spans="1:246" ht="15" customHeight="1">
       <c r="A126" s="65" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="B126" s="52" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C126" s="52" t="s">
         <v>96</v>
@@ -31929,14 +32005,14 @@
         <v>0</v>
       </c>
       <c r="L126" s="52" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="M126" s="52"/>
       <c r="N126" s="52" t="s">
         <v>504</v>
       </c>
       <c r="O126" s="52" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="P126" s="52"/>
       <c r="Q126" s="52"/>
@@ -31946,10 +32022,10 @@
     </row>
     <row r="127" spans="1:246" ht="15" customHeight="1">
       <c r="A127" s="63" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="B127" s="55" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C127" s="55" t="s">
         <v>96</v>
@@ -32000,10 +32076,10 @@
     </row>
     <row r="128" spans="1:246" ht="15" customHeight="1">
       <c r="A128" s="65" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="B128" s="52" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="C128" s="52" t="s">
         <v>95</v>
@@ -32037,7 +32113,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="52" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="M128" s="52"/>
       <c r="N128" s="52" t="s">
@@ -32052,10 +32128,10 @@
     </row>
     <row r="129" spans="1:20" ht="15" customHeight="1">
       <c r="A129" s="63" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B129" s="55" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C129" s="55" t="s">
         <v>95</v>
@@ -32089,7 +32165,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="55" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="M129" s="55"/>
       <c r="N129" s="55" t="s">
@@ -32104,10 +32180,10 @@
     </row>
     <row r="130" spans="1:20" ht="15" customHeight="1">
       <c r="A130" s="65" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="B130" s="52" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C130" s="52" t="s">
         <v>95</v>
@@ -32141,7 +32217,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="52" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="M130" s="52"/>
       <c r="N130" s="52" t="s">
@@ -32156,10 +32232,10 @@
     </row>
     <row r="131" spans="1:20" ht="15" customHeight="1">
       <c r="A131" s="63" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="B131" s="55" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C131" s="55" t="s">
         <v>95</v>
@@ -32195,7 +32271,7 @@
       <c r="L131" s="55"/>
       <c r="M131" s="55"/>
       <c r="N131" s="55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O131" s="55"/>
       <c r="P131" s="55"/>
@@ -32206,10 +32282,10 @@
     </row>
     <row r="132" spans="1:20" ht="15" customHeight="1">
       <c r="A132" s="65" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="B132" s="52" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="C132" s="52" t="s">
         <v>95</v>
@@ -32243,7 +32319,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="52" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="M132" s="52"/>
       <c r="N132" s="52" t="s">
@@ -32258,10 +32334,10 @@
     </row>
     <row r="133" spans="1:20" ht="15" customHeight="1">
       <c r="A133" s="63" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B133" s="55" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C133" s="55" t="s">
         <v>95</v>
@@ -32297,7 +32373,7 @@
       <c r="L133" s="55"/>
       <c r="M133" s="55"/>
       <c r="N133" s="55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O133" s="55"/>
       <c r="P133" s="55"/>
@@ -32308,10 +32384,10 @@
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1">
       <c r="A134" s="65" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="B134" s="52" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="C134" s="52" t="s">
         <v>95</v>
@@ -32347,7 +32423,7 @@
       <c r="L134" s="52"/>
       <c r="M134" s="52"/>
       <c r="N134" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O134" s="52"/>
       <c r="P134" s="52"/>
@@ -32358,10 +32434,10 @@
     </row>
     <row r="135" spans="1:20" ht="15" customHeight="1">
       <c r="A135" s="63" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B135" s="55" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C135" s="55" t="s">
         <v>95</v>
@@ -32395,7 +32471,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="55" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="M135" s="55"/>
       <c r="N135" s="55" t="s">
@@ -32410,10 +32486,10 @@
     </row>
     <row r="136" spans="1:20" ht="15" customHeight="1">
       <c r="A136" s="65" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B136" s="52" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C136" s="52" t="s">
         <v>95</v>
@@ -32447,7 +32523,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="52" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="M136" s="52"/>
       <c r="N136" s="52" t="s">
@@ -32455,7 +32531,7 @@
       </c>
       <c r="O136" s="52"/>
       <c r="P136" s="52" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="Q136" s="52"/>
       <c r="R136" s="52"/>
@@ -32464,10 +32540,10 @@
     </row>
     <row r="137" spans="1:20" ht="15" customHeight="1">
       <c r="A137" s="63" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B137" s="55" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="C137" s="55" t="s">
         <v>95</v>
@@ -32516,10 +32592,10 @@
     </row>
     <row r="138" spans="1:20" ht="15" customHeight="1">
       <c r="A138" s="65" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="B138" s="52" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C138" s="52" t="s">
         <v>95</v>
@@ -32553,7 +32629,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="52" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="M138" s="52"/>
       <c r="N138" s="52" t="s">
@@ -32568,10 +32644,10 @@
     </row>
     <row r="139" spans="1:20" ht="15" customHeight="1">
       <c r="A139" s="63" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B139" s="55" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C139" s="55" t="s">
         <v>95</v>
@@ -32620,10 +32696,10 @@
     </row>
     <row r="140" spans="1:20" ht="15" customHeight="1">
       <c r="A140" s="65" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="B140" s="52" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C140" s="52" t="s">
         <v>95</v>
@@ -32657,7 +32733,7 @@
         <v>699</v>
       </c>
       <c r="L140" s="52" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="M140" s="52"/>
       <c r="N140" s="52" t="s">
@@ -32672,10 +32748,10 @@
     </row>
     <row r="141" spans="1:20" ht="15" customHeight="1">
       <c r="A141" s="63" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B141" s="55" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="C141" s="55" t="s">
         <v>95</v>
@@ -32709,7 +32785,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="55" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="M141" s="55"/>
       <c r="N141" s="55" t="s">
@@ -32724,10 +32800,10 @@
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1">
       <c r="A142" s="52" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B142" s="52" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="C142" s="52" t="s">
         <v>95</v>
@@ -32761,7 +32837,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="52" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="M142" s="52"/>
       <c r="N142" s="52" t="s">
@@ -32776,10 +32852,10 @@
     </row>
     <row r="143" spans="1:20" ht="15" customHeight="1">
       <c r="A143" s="55" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="B143" s="55" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C143" s="55" t="s">
         <v>95</v>
@@ -32815,7 +32891,7 @@
       <c r="L143" s="55"/>
       <c r="M143" s="55"/>
       <c r="N143" s="55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O143" s="55"/>
       <c r="P143" s="55"/>
@@ -32826,10 +32902,10 @@
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1">
       <c r="A144" s="52" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B144" s="52" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="C144" s="52" t="s">
         <v>95</v>
@@ -32865,7 +32941,7 @@
       <c r="L144" s="52"/>
       <c r="M144" s="52"/>
       <c r="N144" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O144" s="52"/>
       <c r="P144" s="52"/>
@@ -32876,7 +32952,7 @@
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1">
       <c r="A145" s="55" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B145" s="55" t="s">
         <v>302</v>
@@ -32928,10 +33004,10 @@
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1">
       <c r="A146" s="52" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="B146" s="52" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="C146" s="52" t="s">
         <v>95</v>
@@ -32965,7 +33041,7 @@
         <v>761</v>
       </c>
       <c r="L146" s="52" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="M146" s="52"/>
       <c r="N146" s="52" t="s">
@@ -32973,7 +33049,7 @@
       </c>
       <c r="O146" s="52"/>
       <c r="P146" s="52" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="Q146" s="52"/>
       <c r="R146" s="52"/>
@@ -32982,10 +33058,10 @@
     </row>
     <row r="147" spans="1:20" ht="63.75" customHeight="1">
       <c r="A147" s="55" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="B147" s="55" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C147" s="55" t="s">
         <v>95</v>
@@ -33019,7 +33095,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="55" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="M147" s="55"/>
       <c r="N147" s="55" t="s">
@@ -33034,10 +33110,10 @@
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1">
       <c r="A148" s="52" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="B148" s="52" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C148" s="52" t="s">
         <v>95</v>
@@ -33071,7 +33147,7 @@
         <v>1004</v>
       </c>
       <c r="L148" s="52" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="M148" s="52"/>
       <c r="N148" s="52" t="s">
@@ -33086,10 +33162,10 @@
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1">
       <c r="A149" s="55" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B149" s="55" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C149" s="55" t="s">
         <v>95</v>
@@ -33123,7 +33199,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="55" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="M149" s="55"/>
       <c r="N149" s="55" t="s">
@@ -33138,10 +33214,10 @@
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1">
       <c r="A150" s="52" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="B150" s="52" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="C150" s="52" t="s">
         <v>95</v>
@@ -33177,7 +33253,7 @@
       <c r="L150" s="52"/>
       <c r="M150" s="52"/>
       <c r="N150" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O150" s="52"/>
       <c r="P150" s="52"/>
@@ -33188,10 +33264,10 @@
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1">
       <c r="A151" s="55" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="B151" s="55" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C151" s="55" t="s">
         <v>96</v>
@@ -33225,7 +33301,7 @@
         <v>645</v>
       </c>
       <c r="L151" s="55" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="M151" s="55"/>
       <c r="N151" s="55" t="s">
@@ -33235,7 +33311,7 @@
         <v>216</v>
       </c>
       <c r="P151" s="55" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="Q151" s="55"/>
       <c r="R151" s="55"/>
@@ -33244,10 +33320,10 @@
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1">
       <c r="A152" s="52" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="B152" s="52" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="C152" s="52" t="s">
         <v>97</v>
@@ -33281,17 +33357,17 @@
         <v>590</v>
       </c>
       <c r="L152" s="52" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="M152" s="52"/>
       <c r="N152" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O152" s="52" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="P152" s="52" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="Q152" s="52"/>
       <c r="R152" s="52"/>
@@ -33300,10 +33376,10 @@
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1">
       <c r="A153" s="55" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="B153" s="55" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C153" s="55" t="s">
         <v>95</v>
@@ -33337,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="55" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="M153" s="55"/>
       <c r="N153" s="55" t="s">
@@ -33345,7 +33421,7 @@
       </c>
       <c r="O153" s="55"/>
       <c r="P153" s="55" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="Q153" s="55"/>
       <c r="R153" s="55"/>
@@ -33354,10 +33430,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="52" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="B154" s="52" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C154" s="52" t="s">
         <v>96</v>
@@ -33391,14 +33467,14 @@
         <v>949</v>
       </c>
       <c r="L154" s="52" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="M154" s="52"/>
       <c r="N154" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O154" s="52" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="P154" s="52"/>
       <c r="Q154" s="52"/>
@@ -33408,10 +33484,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="55" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="B155" s="55" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="C155" s="55" t="s">
         <v>96</v>
@@ -33445,14 +33521,14 @@
         <v>949</v>
       </c>
       <c r="L155" s="55" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="M155" s="55"/>
       <c r="N155" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O155" s="55" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="P155" s="55"/>
       <c r="Q155" s="55"/>
@@ -33462,10 +33538,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="52" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="B156" s="52" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C156" s="52" t="s">
         <v>96</v>
@@ -33499,7 +33575,7 @@
         <v>1900</v>
       </c>
       <c r="L156" s="52" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="M156" s="52"/>
       <c r="N156" s="52" t="s">
@@ -33516,10 +33592,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="55" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="B157" s="55" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="C157" s="55" t="s">
         <v>96</v>
@@ -33553,7 +33629,7 @@
         <v>1050</v>
       </c>
       <c r="L157" s="55" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="M157" s="55"/>
       <c r="N157" s="55" t="s">
@@ -33570,10 +33646,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="52" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="B158" s="52" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="C158" s="52" t="s">
         <v>96</v>
@@ -33607,14 +33683,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="52" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="M158" s="52"/>
       <c r="N158" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O158" s="52" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="P158" s="52"/>
       <c r="Q158" s="52"/>
@@ -33624,10 +33700,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="55" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B159" s="55" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C159" s="55" t="s">
         <v>96</v>
@@ -33661,14 +33737,14 @@
         <v>2517</v>
       </c>
       <c r="L159" s="55" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="M159" s="55"/>
       <c r="N159" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O159" s="55" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="P159" s="55"/>
       <c r="Q159" s="55"/>
@@ -33678,10 +33754,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="52" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="B160" s="52" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C160" s="52" t="s">
         <v>95</v>
@@ -33730,10 +33806,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="55" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B161" s="55" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C161" s="55" t="s">
         <v>95</v>
@@ -33782,10 +33858,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="52" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="B162" s="52" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C162" s="52" t="s">
         <v>95</v>
@@ -33834,10 +33910,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="55" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="B163" s="55" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="C163" s="55" t="s">
         <v>95</v>
@@ -33873,7 +33949,7 @@
       <c r="L163" s="55"/>
       <c r="M163" s="55"/>
       <c r="N163" s="55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O163" s="55"/>
       <c r="P163" s="55"/>
@@ -33884,10 +33960,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="52" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="B164" s="52" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C164" s="52" t="s">
         <v>95</v>
@@ -33921,7 +33997,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="52" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="M164" s="52"/>
       <c r="N164" s="52" t="s">
@@ -33936,10 +34012,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="55" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="B165" s="55" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C165" s="55" t="s">
         <v>95</v>
@@ -33981,7 +34057,7 @@
       </c>
       <c r="O165" s="55"/>
       <c r="P165" s="55" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="Q165" s="55"/>
       <c r="R165" s="55"/>
@@ -33990,10 +34066,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="52" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="B166" s="52" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C166" s="52" t="s">
         <v>95</v>
@@ -34027,7 +34103,7 @@
         <v>606</v>
       </c>
       <c r="L166" s="52" t="s">
-        <v>1303</v>
+        <v>1294</v>
       </c>
       <c r="M166" s="52"/>
       <c r="N166" s="52" t="s">
@@ -34035,7 +34111,7 @@
       </c>
       <c r="O166" s="52"/>
       <c r="P166" s="52" t="s">
-        <v>1304</v>
+        <v>1295</v>
       </c>
       <c r="Q166" s="52"/>
       <c r="R166" s="52"/>
@@ -34044,10 +34120,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="55" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="B167" s="55" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C167" s="55" t="s">
         <v>95</v>
@@ -34081,7 +34157,7 @@
         <v>2220</v>
       </c>
       <c r="L167" s="55" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="M167" s="55"/>
       <c r="N167" s="55" t="s">
@@ -34089,7 +34165,7 @@
       </c>
       <c r="O167" s="55"/>
       <c r="P167" s="55" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="Q167" s="55"/>
       <c r="R167" s="55"/>
@@ -34098,10 +34174,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="52" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="B168" s="52" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="C168" s="52" t="s">
         <v>95</v>
@@ -34135,7 +34211,7 @@
         <v>1216</v>
       </c>
       <c r="L168" s="52" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="M168" s="52"/>
       <c r="N168" s="52" t="s">
@@ -34143,7 +34219,7 @@
       </c>
       <c r="O168" s="52"/>
       <c r="P168" s="52" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="Q168" s="52"/>
       <c r="R168" s="52"/>
@@ -34152,10 +34228,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="55" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="B169" s="55" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="C169" s="55" t="s">
         <v>95</v>
@@ -34191,11 +34267,11 @@
       <c r="L169" s="55"/>
       <c r="M169" s="55"/>
       <c r="N169" s="55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O169" s="55"/>
       <c r="P169" s="55" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="Q169" s="55"/>
       <c r="R169" s="55"/>
@@ -34204,10 +34280,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="52" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B170" s="52" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="C170" s="52" t="s">
         <v>95</v>
@@ -34241,7 +34317,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="52" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="M170" s="52"/>
       <c r="N170" s="52" t="s">
@@ -34249,7 +34325,7 @@
       </c>
       <c r="O170" s="52"/>
       <c r="P170" s="52" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="Q170" s="52"/>
       <c r="R170" s="52"/>
@@ -34258,10 +34334,10 @@
     </row>
     <row r="171" spans="1:20" ht="31.5" customHeight="1">
       <c r="A171" s="55" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B171" s="52" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="C171" s="55" t="s">
         <v>95</v>
@@ -34295,7 +34371,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="55" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="M171" s="55"/>
       <c r="N171" s="55" t="s">
@@ -34310,10 +34386,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="52" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="B172" s="52" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C172" s="52" t="s">
         <v>95</v>
@@ -34347,7 +34423,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="52" t="s">
-        <v>1251</v>
+        <v>1244</v>
       </c>
       <c r="M172" s="52"/>
       <c r="N172" s="52" t="s">
@@ -34362,10 +34438,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="55" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="B173" s="55" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="C173" s="55" t="s">
         <v>95</v>
@@ -34414,10 +34490,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="52" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B174" s="52" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="C174" s="52" t="s">
         <v>95</v>
@@ -34451,7 +34527,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="52" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="M174" s="52"/>
       <c r="N174" s="52" t="s">
@@ -34466,10 +34542,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="55" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="B175" s="55" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="C175" s="55" t="s">
         <v>95</v>
@@ -34503,7 +34579,7 @@
         <v>2793</v>
       </c>
       <c r="L175" s="55" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="M175" s="55"/>
       <c r="N175" s="55" t="s">
@@ -34511,7 +34587,7 @@
       </c>
       <c r="O175" s="55"/>
       <c r="P175" s="55" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="Q175" s="55"/>
       <c r="R175" s="55"/>
@@ -34520,10 +34596,10 @@
     </row>
     <row r="176" spans="1:20" ht="24" customHeight="1">
       <c r="A176" s="52" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B176" s="52" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="C176" s="52" t="s">
         <v>95</v>
@@ -34557,7 +34633,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="52" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="M176" s="52"/>
       <c r="N176" s="52" t="s">
@@ -34572,10 +34648,10 @@
     </row>
     <row r="177" spans="1:20" ht="33.75" customHeight="1">
       <c r="A177" s="55" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B177" s="55" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="C177" s="55" t="s">
         <v>95</v>
@@ -34609,7 +34685,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="55" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="M177" s="55"/>
       <c r="N177" s="55" t="s">
@@ -34617,7 +34693,7 @@
       </c>
       <c r="O177" s="55"/>
       <c r="P177" s="55" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="Q177" s="55"/>
       <c r="R177" s="55"/>
@@ -34626,10 +34702,10 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1">
       <c r="A178" s="52" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B178" s="52" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="C178" s="52" t="s">
         <v>95</v>
@@ -34663,7 +34739,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="52" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="M178" s="52"/>
       <c r="N178" s="52" t="s">
@@ -34671,7 +34747,7 @@
       </c>
       <c r="O178" s="52"/>
       <c r="P178" s="52" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="Q178" s="52"/>
       <c r="R178" s="52"/>
@@ -34680,10 +34756,10 @@
     </row>
     <row r="179" spans="1:20" ht="30" customHeight="1">
       <c r="A179" s="55" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="B179" s="55" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="C179" s="55" t="s">
         <v>95</v>
@@ -34717,7 +34793,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="55" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="M179" s="55"/>
       <c r="N179" s="55" t="s">
@@ -34725,7 +34801,7 @@
       </c>
       <c r="O179" s="55"/>
       <c r="P179" s="55" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="Q179" s="55"/>
       <c r="R179" s="55"/>
@@ -34734,10 +34810,10 @@
     </row>
     <row r="180" spans="1:20" ht="33.75" customHeight="1">
       <c r="A180" s="52" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B180" s="52" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="C180" s="52" t="s">
         <v>95</v>
@@ -34771,7 +34847,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="52" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="M180" s="52"/>
       <c r="N180" s="52" t="s">
@@ -34786,10 +34862,10 @@
     </row>
     <row r="181" spans="1:20" ht="15" customHeight="1">
       <c r="A181" s="55" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B181" s="55" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C181" s="55" t="s">
         <v>96</v>
@@ -34823,17 +34899,17 @@
         <v>1019</v>
       </c>
       <c r="L181" s="55" t="s">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="M181" s="55"/>
       <c r="N181" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O181" s="55" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="P181" s="55" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="Q181" s="55"/>
       <c r="R181" s="55"/>
@@ -34842,10 +34918,10 @@
     </row>
     <row r="182" spans="1:20" ht="15" customHeight="1">
       <c r="A182" s="52" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B182" s="52" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="C182" s="52" t="s">
         <v>95</v>
@@ -34881,11 +34957,11 @@
       <c r="L182" s="52"/>
       <c r="M182" s="52"/>
       <c r="N182" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O182" s="52"/>
       <c r="P182" s="52" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="Q182" s="52"/>
       <c r="R182" s="52"/>
@@ -34894,10 +34970,10 @@
     </row>
     <row r="183" spans="1:20" ht="15" customHeight="1">
       <c r="A183" s="55" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B183" s="55" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C183" s="55" t="s">
         <v>95</v>
@@ -34930,7 +35006,7 @@
         <v>1676</v>
       </c>
       <c r="L183" s="55" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="M183" s="55"/>
       <c r="N183" s="55" t="s">
@@ -34945,10 +35021,10 @@
     </row>
     <row r="184" spans="1:20" ht="52" customHeight="1">
       <c r="A184" s="52" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B184" s="52" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="C184" s="52" t="s">
         <v>95</v>
@@ -34982,7 +35058,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="52" t="s">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="M184" s="52"/>
       <c r="N184" s="52" t="s">
@@ -34997,10 +35073,10 @@
     </row>
     <row r="185" spans="1:20" ht="15" customHeight="1">
       <c r="A185" s="55" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B185" s="55" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C185" s="55" t="s">
         <v>95</v>
@@ -35034,7 +35110,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="55" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="M185" s="55"/>
       <c r="N185" s="55" t="s">
@@ -35049,10 +35125,10 @@
     </row>
     <row r="186" spans="1:20" ht="15" customHeight="1">
       <c r="A186" s="52" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="B186" s="52" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C186" s="52" t="s">
         <v>95</v>
@@ -35088,7 +35164,7 @@
       <c r="L186" s="52"/>
       <c r="M186" s="52"/>
       <c r="N186" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O186" s="52"/>
       <c r="P186" s="52"/>
@@ -35099,10 +35175,10 @@
     </row>
     <row r="187" spans="1:20" ht="15" customHeight="1">
       <c r="A187" s="55" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="B187" s="55" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="C187" s="55" t="s">
         <v>95</v>
@@ -35136,7 +35212,7 @@
         <v>891</v>
       </c>
       <c r="L187" s="55" t="s">
-        <v>1290</v>
+        <v>1281</v>
       </c>
       <c r="M187" s="55"/>
       <c r="N187" s="55" t="s">
@@ -35151,10 +35227,10 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1">
       <c r="A188" s="52" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="B188" s="52" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="C188" s="52" t="s">
         <v>95</v>
@@ -35188,7 +35264,7 @@
         <v>891</v>
       </c>
       <c r="L188" s="52" t="s">
-        <v>1219</v>
+        <v>1212</v>
       </c>
       <c r="M188" s="52"/>
       <c r="N188" s="52" t="s">
@@ -35203,10 +35279,10 @@
     </row>
     <row r="189" spans="1:20" ht="63" customHeight="1">
       <c r="A189" s="55" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B189" s="52" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="C189" s="52" t="s">
         <v>95</v>
@@ -35240,7 +35316,7 @@
         <v>891</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1293</v>
+        <v>1284</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -35248,7 +35324,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1296</v>
+        <v>1287</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -35257,10 +35333,10 @@
     </row>
     <row r="190" spans="1:20" ht="15" customHeight="1">
       <c r="A190" s="52" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="B190" s="55" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="C190" s="55" t="s">
         <v>95</v>
@@ -35294,7 +35370,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="52" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="M190" s="52"/>
       <c r="N190" s="47" t="s">
@@ -35305,10 +35381,10 @@
     </row>
     <row r="191" spans="1:20" ht="30" customHeight="1">
       <c r="A191" s="55" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B191" s="52" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="C191" s="52" t="s">
         <v>95</v>
@@ -35344,20 +35420,20 @@
       <c r="L191" s="55"/>
       <c r="M191" s="55"/>
       <c r="N191" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P191" s="47" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="S191" s="47"/>
       <c r="T191" s="47"/>
     </row>
     <row r="192" spans="1:20" ht="15" customHeight="1">
       <c r="A192" s="52" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="B192" s="55" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="C192" s="55" t="s">
         <v>95</v>
@@ -35391,24 +35467,24 @@
         <v>1616</v>
       </c>
       <c r="L192" s="52" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="M192" s="52"/>
       <c r="N192" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P192" s="47" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="S192" s="47"/>
       <c r="T192" s="47"/>
     </row>
     <row r="193" spans="1:20" ht="15" customHeight="1">
       <c r="A193" s="55" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="B193" s="52" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="C193" s="52" t="s">
         <v>95</v>
@@ -35444,20 +35520,20 @@
       <c r="L193" s="55"/>
       <c r="M193" s="55"/>
       <c r="N193" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P193" s="47" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="S193" s="47"/>
       <c r="T193" s="47"/>
     </row>
     <row r="194" spans="1:20" ht="35" customHeight="1">
       <c r="A194" s="52" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="B194" s="52" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
       <c r="C194" s="52" t="s">
         <v>95</v>
@@ -35472,11 +35548,11 @@
         <v>3</v>
       </c>
       <c r="G194" s="66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H194" s="65">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I194" s="65">
         <f>IF(D194&lt;&gt;"",D194,IFERROR(E194/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -35488,27 +35564,27 @@
       </c>
       <c r="K194" s="65">
         <f t="shared" ref="K194:K224" si="14">IF(LEN(G194)=0,0,G194)*I194</f>
-        <v>5530</v>
+        <v>3950</v>
       </c>
       <c r="L194" s="52" t="s">
-        <v>1342</v>
+        <v>1333</v>
       </c>
       <c r="M194" s="52"/>
       <c r="N194" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1343</v>
+        <v>1393</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
     </row>
     <row r="195" spans="1:20" ht="12" customHeight="1">
       <c r="A195" s="55" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="B195" s="55" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="C195" s="55" t="s">
         <v>95</v>
@@ -35542,24 +35618,24 @@
         <v>5467</v>
       </c>
       <c r="L195" s="55" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="M195" s="55"/>
       <c r="N195" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P195" s="47" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="S195" s="47"/>
       <c r="T195" s="47"/>
     </row>
     <row r="196" spans="1:20" ht="15" customHeight="1">
       <c r="A196" s="55" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B196" s="55" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="C196" s="55" t="s">
         <v>95</v>
@@ -35595,20 +35671,20 @@
       <c r="L196" s="55"/>
       <c r="M196" s="55"/>
       <c r="N196" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P196" s="47" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="S196" s="47"/>
       <c r="T196" s="47"/>
     </row>
     <row r="197" spans="1:20" ht="15" customHeight="1">
       <c r="A197" s="52" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B197" s="52" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="C197" s="52" t="s">
         <v>95</v>
@@ -35644,20 +35720,20 @@
       <c r="L197" s="52"/>
       <c r="M197" s="52"/>
       <c r="N197" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P197" s="47" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="S197" s="47"/>
       <c r="T197" s="47"/>
     </row>
     <row r="198" spans="1:20" ht="15" customHeight="1">
       <c r="A198" s="55" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="B198" s="52" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C198" s="52" t="s">
         <v>95</v>
@@ -35691,24 +35767,24 @@
         <v>1401</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
     </row>
     <row r="199" spans="1:20" ht="30" customHeight="1">
       <c r="A199" s="52" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B199" s="55" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="C199" s="55" t="s">
         <v>95</v>
@@ -35742,24 +35818,24 @@
         <v>1732</v>
       </c>
       <c r="L199" s="52" t="s">
-        <v>1299</v>
+        <v>1290</v>
       </c>
       <c r="M199" s="52"/>
       <c r="N199" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P199" s="47" t="s">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="S199" s="47"/>
       <c r="T199" s="47"/>
     </row>
     <row r="200" spans="1:20" ht="15" customHeight="1">
       <c r="A200" s="55" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B200" s="52" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="C200" s="52" t="s">
         <v>95</v>
@@ -35793,24 +35869,24 @@
         <v>724</v>
       </c>
       <c r="L200" s="55" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="M200" s="55"/>
       <c r="N200" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P200" s="47" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="S200" s="47"/>
       <c r="T200" s="47"/>
     </row>
     <row r="201" spans="1:20" ht="15" customHeight="1">
       <c r="A201" s="52" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="B201" s="55" t="s">
-        <v>1393</v>
+        <v>1377</v>
       </c>
       <c r="C201" s="55" t="s">
         <v>95</v>
@@ -35844,24 +35920,24 @@
         <v>2820</v>
       </c>
       <c r="L201" s="52" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="M201" s="52"/>
       <c r="N201" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1392</v>
+        <v>1376</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
     </row>
     <row r="202" spans="1:20" ht="15" customHeight="1">
       <c r="A202" s="55" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B202" s="52" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="C202" s="52" t="s">
         <v>95</v>
@@ -35895,24 +35971,24 @@
         <v>0</v>
       </c>
       <c r="L202" s="55" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="M202" s="55"/>
       <c r="N202" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P202" s="47" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="S202" s="47"/>
       <c r="T202" s="47"/>
     </row>
     <row r="203" spans="1:20" ht="15" customHeight="1">
       <c r="A203" s="52" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B203" s="52" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="C203" s="52" t="s">
         <v>95</v>
@@ -35946,24 +36022,24 @@
         <v>880</v>
       </c>
       <c r="L203" s="52" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="M203" s="52"/>
       <c r="N203" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P203" s="47" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="S203" s="47"/>
       <c r="T203" s="47"/>
     </row>
     <row r="204" spans="1:20" ht="15" customHeight="1">
       <c r="A204" s="55" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="B204" s="55" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="C204" s="55" t="s">
         <v>95</v>
@@ -35997,24 +36073,24 @@
         <v>761</v>
       </c>
       <c r="L204" s="55" t="s">
-        <v>1306</v>
+        <v>1297</v>
       </c>
       <c r="M204" s="55"/>
       <c r="N204" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P204" s="47" t="s">
-        <v>1307</v>
+        <v>1298</v>
       </c>
       <c r="S204" s="47"/>
       <c r="T204" s="47"/>
     </row>
     <row r="205" spans="1:20" ht="15" customHeight="1">
       <c r="A205" s="52" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="B205" s="52" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="C205" s="52" t="s">
         <v>95</v>
@@ -36055,17 +36131,17 @@
         <v>504</v>
       </c>
       <c r="P205" s="47" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="S205" s="47"/>
       <c r="T205" s="47"/>
     </row>
     <row r="206" spans="1:20" ht="15" customHeight="1">
       <c r="A206" s="55" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="B206" s="55" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="C206" s="55" t="s">
         <v>95</v>
@@ -36099,24 +36175,24 @@
         <v>3312</v>
       </c>
       <c r="L206" s="55" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="M206" s="55"/>
       <c r="N206" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P206" s="47" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="S206" s="47"/>
       <c r="T206" s="47"/>
     </row>
     <row r="207" spans="1:20" ht="30" customHeight="1">
       <c r="A207" s="52" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="B207" s="52" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="C207" s="52" t="s">
         <v>95</v>
@@ -36150,24 +36226,24 @@
         <v>2346</v>
       </c>
       <c r="L207" s="52" t="s">
-        <v>1341</v>
+        <v>1332</v>
       </c>
       <c r="M207" s="52"/>
       <c r="N207" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P207" s="47" t="s">
-        <v>1340</v>
+        <v>1331</v>
       </c>
       <c r="S207" s="47"/>
       <c r="T207" s="47"/>
     </row>
     <row r="208" spans="1:20" ht="15" customHeight="1">
       <c r="A208" s="55" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B208" s="52" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="C208" s="52" t="s">
         <v>95</v>
@@ -36201,24 +36277,24 @@
         <v>982</v>
       </c>
       <c r="L208" s="55" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="M208" s="55"/>
       <c r="N208" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P208" s="47" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="S208" s="47"/>
       <c r="T208" s="47"/>
     </row>
     <row r="209" spans="1:20" ht="15" customHeight="1">
       <c r="A209" s="52" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="B209" s="55" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C209" s="55" t="s">
         <v>95</v>
@@ -36254,20 +36330,20 @@
       <c r="L209" s="52"/>
       <c r="M209" s="52"/>
       <c r="N209" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P209" s="47" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="S209" s="47"/>
       <c r="T209" s="47"/>
     </row>
     <row r="210" spans="1:20" ht="15" customHeight="1">
       <c r="A210" s="55" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B210" s="52" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C210" s="52" t="s">
         <v>95</v>
@@ -36301,24 +36377,24 @@
         <v>0</v>
       </c>
       <c r="L210" s="55" t="s">
-        <v>1347</v>
+        <v>1337</v>
       </c>
       <c r="M210" s="55"/>
       <c r="N210" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P210" s="47" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="S210" s="47"/>
       <c r="T210" s="47"/>
     </row>
     <row r="211" spans="1:20" ht="15" customHeight="1">
       <c r="A211" s="52" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B211" s="55" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C211" s="55" t="s">
         <v>95</v>
@@ -36352,7 +36428,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="52" t="s">
-        <v>1291</v>
+        <v>1282</v>
       </c>
       <c r="M211" s="52"/>
       <c r="N211" s="47" t="s">
@@ -36363,10 +36439,10 @@
     </row>
     <row r="212" spans="1:20" ht="26" customHeight="1">
       <c r="A212" s="55" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="B212" s="52" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="C212" s="52" t="s">
         <v>95</v>
@@ -36400,24 +36476,24 @@
         <v>2775</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1382</v>
+        <v>1394</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P212" s="47" t="s">
-        <v>1345</v>
+        <v>1335</v>
       </c>
       <c r="S212" s="47"/>
       <c r="T212" s="47"/>
     </row>
     <row r="213" spans="1:20" ht="15" customHeight="1">
       <c r="A213" s="52" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="B213" s="52" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="C213" s="52" t="s">
         <v>95</v>
@@ -36451,24 +36527,24 @@
         <v>3340</v>
       </c>
       <c r="L213" s="52" t="s">
-        <v>1316</v>
+        <v>1307</v>
       </c>
       <c r="M213" s="52"/>
       <c r="N213" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P213" s="47" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="S213" s="47"/>
       <c r="T213" s="47"/>
     </row>
     <row r="214" spans="1:20" ht="15" customHeight="1">
       <c r="A214" s="55" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B214" s="55" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="C214" s="55" t="s">
         <v>95</v>
@@ -36483,11 +36559,11 @@
         <v>2</v>
       </c>
       <c r="G214" s="64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H214" s="63">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I214" s="63">
         <f>IF(D214&lt;&gt;"",D214,IFERROR(E214/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -36499,27 +36575,27 @@
       </c>
       <c r="K214" s="63">
         <f t="shared" si="14"/>
-        <v>2976</v>
+        <v>1984</v>
       </c>
       <c r="L214" s="55" t="s">
-        <v>1211</v>
+        <v>1204</v>
       </c>
       <c r="M214" s="55"/>
       <c r="N214" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P214" s="47" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="S214" s="47"/>
       <c r="T214" s="47"/>
     </row>
     <row r="215" spans="1:20" ht="30">
       <c r="A215" s="52" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B215" s="52" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C215" s="52" t="s">
         <v>95</v>
@@ -36555,20 +36631,20 @@
       <c r="L215" s="52"/>
       <c r="M215" s="52"/>
       <c r="N215" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P215" s="47" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="S215" s="47"/>
       <c r="T215" s="47"/>
     </row>
     <row r="216" spans="1:20" ht="15" customHeight="1">
       <c r="A216" s="55" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B216" s="55" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="C216" s="55" t="s">
         <v>95</v>
@@ -36602,24 +36678,24 @@
         <v>0</v>
       </c>
       <c r="L216" s="55" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="M216" s="55"/>
       <c r="N216" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P216" s="47" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="S216" s="47"/>
       <c r="T216" s="47"/>
     </row>
     <row r="217" spans="1:20" ht="15">
       <c r="A217" s="52" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B217" s="52" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="C217" s="52" t="s">
         <v>95</v>
@@ -36653,24 +36729,24 @@
         <v>828</v>
       </c>
       <c r="L217" s="52" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="M217" s="52"/>
       <c r="N217" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P217" s="47" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="S217" s="47"/>
       <c r="T217" s="47"/>
     </row>
     <row r="218" spans="1:20" ht="15" customHeight="1">
       <c r="A218" s="55" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="B218" s="55" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="C218" s="55" t="s">
         <v>95</v>
@@ -36682,14 +36758,14 @@
         <v>1150</v>
       </c>
       <c r="F218" s="64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" s="64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H218" s="63">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I218" s="63">
         <f>IF(D218&lt;&gt;"",D218,IFERROR(E218/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -36697,31 +36773,31 @@
       </c>
       <c r="J218" s="63">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="K218" s="63">
         <f t="shared" si="14"/>
-        <v>2283</v>
+        <v>761</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1172</v>
+        <v>1383</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
-        <v>678</v>
+        <v>589</v>
       </c>
       <c r="P218" s="47" t="s">
-        <v>1171</v>
+        <v>848</v>
       </c>
       <c r="S218" s="47"/>
       <c r="T218" s="47"/>
     </row>
     <row r="219" spans="1:20" ht="15">
       <c r="A219" s="52" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="B219" s="52" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="C219" s="52" t="s">
         <v>95</v>
@@ -36755,24 +36831,24 @@
         <v>3805</v>
       </c>
       <c r="L219" s="52" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="M219" s="52"/>
       <c r="N219" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P219" s="47" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="S219" s="47"/>
       <c r="T219" s="47"/>
     </row>
     <row r="220" spans="1:20" ht="15" customHeight="1">
       <c r="A220" s="55" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="B220" s="55" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="C220" s="55" t="s">
         <v>95</v>
@@ -36787,11 +36863,11 @@
         <v>0</v>
       </c>
       <c r="G220" s="64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H220" s="63">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I220" s="63">
         <f>IF(D220&lt;&gt;"",D220,IFERROR(E220/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -36803,25 +36879,25 @@
       </c>
       <c r="K220" s="63">
         <f t="shared" si="14"/>
-        <v>4350</v>
+        <v>3480</v>
       </c>
       <c r="L220" s="55"/>
       <c r="M220" s="55"/>
       <c r="N220" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P220" s="47" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="S220" s="47"/>
       <c r="T220" s="47"/>
     </row>
     <row r="221" spans="1:20" ht="17">
       <c r="A221" s="52" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="B221" s="52" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
       <c r="C221" s="52" t="s">
         <v>96</v>
@@ -36857,20 +36933,20 @@
       <c r="L221" s="52"/>
       <c r="M221" s="52"/>
       <c r="N221" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P221" s="86" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="S221" s="47"/>
       <c r="T221" s="47"/>
     </row>
     <row r="222" spans="1:20" ht="15" customHeight="1">
       <c r="A222" s="55" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="B222" s="55" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
       <c r="C222" s="55" t="s">
         <v>95</v>
@@ -36906,20 +36982,20 @@
       <c r="L222" s="55"/>
       <c r="M222" s="55"/>
       <c r="N222" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P222" s="86" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="S222" s="47"/>
       <c r="T222" s="47"/>
     </row>
     <row r="223" spans="1:20" ht="15" customHeight="1">
       <c r="A223" s="52" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B223" s="52" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="C223" s="52" t="s">
         <v>95</v>
@@ -36953,24 +37029,24 @@
         <v>942</v>
       </c>
       <c r="L223" s="52" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="M223" s="52"/>
       <c r="N223" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P223" s="86" t="s">
-        <v>1216</v>
+        <v>1209</v>
       </c>
       <c r="S223" s="47"/>
       <c r="T223" s="47"/>
     </row>
     <row r="224" spans="1:20" ht="15" customHeight="1">
       <c r="A224" s="55" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B224" s="55" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="C224" s="55" t="s">
         <v>95</v>
@@ -37011,17 +37087,17 @@
         <v>504</v>
       </c>
       <c r="P224" s="86" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
     </row>
     <row r="225" spans="1:20" ht="17">
       <c r="A225" s="52" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="B225" s="55" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
       <c r="C225" s="55" t="s">
         <v>95</v>
@@ -37055,24 +37131,24 @@
         <v>1338</v>
       </c>
       <c r="L225" s="55" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="M225" s="55"/>
       <c r="N225" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P225" s="86" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
     </row>
     <row r="226" spans="1:20" ht="17">
       <c r="A226" s="55" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
       <c r="B226" s="52" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
       <c r="C226" s="52" t="s">
         <v>95</v>
@@ -37108,20 +37184,20 @@
       <c r="L226" s="52"/>
       <c r="M226" s="52"/>
       <c r="N226" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P226" s="86" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
     </row>
     <row r="227" spans="1:20" ht="17">
       <c r="A227" s="52" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="B227" s="55" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="C227" s="55" t="s">
         <v>95</v>
@@ -37155,24 +37231,24 @@
         <v>2775</v>
       </c>
       <c r="L227" s="55" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
       <c r="M227" s="55"/>
       <c r="N227" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P227" s="86" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
     </row>
     <row r="228" spans="1:20" ht="16">
       <c r="A228" s="55" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
       <c r="B228" s="52" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="C228" s="52" t="s">
         <v>95</v>
@@ -37184,14 +37260,14 @@
         <v>1250</v>
       </c>
       <c r="F228" s="66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G228" s="66">
         <v>0</v>
       </c>
       <c r="H228" s="65">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I228" s="65">
         <f>IF(D228&lt;&gt;"",D228,IFERROR(E228/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -37199,14 +37275,14 @@
       </c>
       <c r="J228" s="65">
         <f t="shared" si="16"/>
-        <v>782</v>
+        <v>1564</v>
       </c>
       <c r="K228" s="65">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L228" s="52" t="s">
-        <v>1380</v>
+        <v>1370</v>
       </c>
       <c r="M228" s="52"/>
       <c r="N228" s="47" t="s">
@@ -37218,10 +37294,10 @@
     </row>
     <row r="229" spans="1:20" ht="17">
       <c r="A229" s="52" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="B229" s="55" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="C229" s="55" t="s">
         <v>95</v>
@@ -37262,17 +37338,17 @@
         <v>589</v>
       </c>
       <c r="P229" s="86" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
     </row>
     <row r="230" spans="1:20" ht="17">
       <c r="A230" s="52" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="B230" s="52" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="C230" s="52" t="s">
         <v>95</v>
@@ -37308,20 +37384,20 @@
       <c r="L230" s="52"/>
       <c r="M230" s="52"/>
       <c r="N230" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P230" s="86" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="S230" s="47"/>
       <c r="T230" s="47"/>
     </row>
     <row r="231" spans="1:20" ht="17">
       <c r="A231" s="55" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="B231" s="55" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="C231" s="55" t="s">
         <v>95</v>
@@ -37355,24 +37431,24 @@
         <v>0</v>
       </c>
       <c r="L231" s="55" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="M231" s="55"/>
       <c r="N231" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P231" s="86" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
     </row>
     <row r="232" spans="1:20" ht="17">
       <c r="A232" s="52" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="B232" s="52" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="C232" s="52" t="s">
         <v>95</v>
@@ -37406,24 +37482,24 @@
         <v>1048</v>
       </c>
       <c r="L232" s="52" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
       <c r="M232" s="52"/>
       <c r="N232" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P232" s="86" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="S232" s="47"/>
       <c r="T232" s="47"/>
     </row>
     <row r="233" spans="1:20" ht="17">
       <c r="A233" s="55" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="B233" s="55" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="C233" s="55" t="s">
         <v>95</v>
@@ -37457,21 +37533,21 @@
         <v>891</v>
       </c>
       <c r="L233" s="55" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="M233" s="55"/>
       <c r="N233" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P233" s="86" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
     </row>
     <row r="234" spans="1:20" ht="17">
       <c r="A234" s="52" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="B234" s="52" t="s">
         <v>510</v>
@@ -37508,24 +37584,24 @@
         <v>1824</v>
       </c>
       <c r="L234" s="52" t="s">
-        <v>1310</v>
+        <v>1301</v>
       </c>
       <c r="M234" s="52"/>
       <c r="N234" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1311</v>
+        <v>1302</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
     </row>
     <row r="235" spans="1:20" ht="17">
       <c r="A235" s="52" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="C235" s="55" t="s">
         <v>95</v>
@@ -37559,11 +37635,11 @@
         <v>734</v>
       </c>
       <c r="L235" s="55" t="s">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="M235" s="55"/>
       <c r="N235" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P235" s="86" t="s">
         <v>657</v>
@@ -37573,10 +37649,10 @@
     </row>
     <row r="236" spans="1:20" ht="17">
       <c r="A236" s="55" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="B236" s="52" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="C236" s="52" t="s">
         <v>95</v>
@@ -37591,11 +37667,11 @@
         <v>0</v>
       </c>
       <c r="G236" s="66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H236" s="65">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I236" s="65">
         <f>IF(D236&lt;&gt;"",D236,IFERROR(E236/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -37607,27 +37683,27 @@
       </c>
       <c r="K236" s="65">
         <f t="shared" si="17"/>
-        <v>872</v>
+        <v>436</v>
       </c>
       <c r="L236" s="52" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="M236" s="52"/>
       <c r="N236" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P236" s="86" t="s">
-        <v>1252</v>
+        <v>594</v>
       </c>
       <c r="S236" s="47"/>
       <c r="T236" s="47"/>
     </row>
     <row r="237" spans="1:20" ht="16">
       <c r="A237" s="55" t="s">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="B237" s="55" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="C237" s="55" t="s">
         <v>95</v>
@@ -37661,7 +37737,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="55" t="s">
-        <v>1221</v>
+        <v>1214</v>
       </c>
       <c r="M237" s="55"/>
       <c r="N237" s="47" t="s">
@@ -37673,10 +37749,10 @@
     </row>
     <row r="238" spans="1:20" ht="17">
       <c r="A238" s="52" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="B238" s="52" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="C238" s="52" t="s">
         <v>95</v>
@@ -37712,20 +37788,20 @@
       <c r="L238" s="52"/>
       <c r="M238" s="52"/>
       <c r="N238" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P238" s="86" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
     </row>
     <row r="239" spans="1:20" ht="17">
       <c r="A239" s="55" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="B239" s="55" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="C239" s="55" t="s">
         <v>95</v>
@@ -37759,7 +37835,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="55" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="M239" s="55"/>
       <c r="N239" s="47" t="s">
@@ -37773,10 +37849,10 @@
     </row>
     <row r="240" spans="1:20" ht="17">
       <c r="A240" s="52" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
       <c r="B240" s="52" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
       <c r="C240" s="52" t="s">
         <v>95</v>
@@ -37810,24 +37886,24 @@
         <v>1124</v>
       </c>
       <c r="L240" s="52" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="M240" s="52"/>
       <c r="N240" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P240" s="86" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="S240" s="47"/>
       <c r="T240" s="47"/>
     </row>
     <row r="241" spans="1:246" ht="17">
       <c r="A241" s="55" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="B241" s="55" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="C241" s="55" t="s">
         <v>95</v>
@@ -37865,20 +37941,20 @@
       </c>
       <c r="M241" s="55"/>
       <c r="N241" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P241" s="86" t="s">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="S241" s="47"/>
       <c r="T241" s="47"/>
     </row>
     <row r="242" spans="1:246" ht="17">
       <c r="A242" s="52" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
       <c r="B242" s="52" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="C242" s="52" t="s">
         <v>95</v>
@@ -37912,24 +37988,24 @@
         <v>0</v>
       </c>
       <c r="L242" s="52" t="s">
-        <v>1348</v>
+        <v>1338</v>
       </c>
       <c r="M242" s="52"/>
       <c r="N242" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P242" s="86" t="s">
-        <v>1247</v>
+        <v>1240</v>
       </c>
       <c r="S242" s="47"/>
       <c r="T242" s="47"/>
     </row>
     <row r="243" spans="1:246" ht="17">
       <c r="A243" s="55" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="B243" s="55" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="C243" s="55" t="s">
         <v>95</v>
@@ -37965,20 +38041,20 @@
       <c r="L243" s="55"/>
       <c r="M243" s="55"/>
       <c r="N243" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P243" s="86" t="s">
-        <v>1248</v>
+        <v>1241</v>
       </c>
       <c r="S243" s="47"/>
       <c r="T243" s="47"/>
     </row>
     <row r="244" spans="1:246" ht="16">
       <c r="A244" s="52" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
       <c r="B244" s="52" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="C244" s="52" t="s">
         <v>95</v>
@@ -38014,7 +38090,7 @@
       <c r="L244" s="52"/>
       <c r="M244" s="52"/>
       <c r="N244" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P244" s="86"/>
       <c r="S244" s="47"/>
@@ -38022,10 +38098,10 @@
     </row>
     <row r="245" spans="1:246" s="62" customFormat="1" ht="17">
       <c r="A245" s="87" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="B245" s="87" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="C245" s="87" t="s">
         <v>95</v>
@@ -38064,7 +38140,7 @@
         <v>504</v>
       </c>
       <c r="P245" s="91" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
       <c r="U245" s="61"/>
       <c r="V245" s="61"/>
@@ -38293,61 +38369,285 @@
       <c r="IK245" s="61"/>
       <c r="IL245" s="61"/>
     </row>
-    <row r="246" spans="1:246" ht="16">
-      <c r="A246" s="52" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B246" s="52" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C246" s="52" t="s">
+    <row r="246" spans="1:246" s="62" customFormat="1" ht="16">
+      <c r="A246" s="59" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B246" s="59" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C246" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="D246" s="53">
+      <c r="D246" s="60">
         <v>628</v>
       </c>
-      <c r="E246" s="53">
+      <c r="E246" s="60">
         <v>999</v>
       </c>
-      <c r="F246" s="66">
-        <v>1</v>
-      </c>
-      <c r="G246" s="66">
+      <c r="F246" s="95">
         <v>0</v>
       </c>
-      <c r="H246" s="65">
+      <c r="G246" s="95">
+        <v>0</v>
+      </c>
+      <c r="H246" s="96">
         <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="I246" s="65">
+        <v>0</v>
+      </c>
+      <c r="I246" s="96">
         <f>IF(D246&lt;&gt;"",D246,IFERROR(E246/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
         <v>628</v>
       </c>
-      <c r="J246" s="65">
+      <c r="J246" s="96">
         <f t="shared" si="19"/>
-        <v>628</v>
-      </c>
-      <c r="K246" s="65">
+        <v>0</v>
+      </c>
+      <c r="K246" s="96">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="L246" s="52" t="s">
-        <v>1387</v>
-      </c>
-      <c r="M246" s="52"/>
-      <c r="N246" s="47" t="s">
+      <c r="L246" s="59" t="s">
+        <v>608</v>
+      </c>
+      <c r="M246" s="59"/>
+      <c r="N246" s="62" t="s">
         <v>504</v>
       </c>
-      <c r="P246" s="86"/>
-      <c r="S246" s="47"/>
-      <c r="T246" s="47"/>
+      <c r="P246" s="91"/>
+      <c r="U246" s="61"/>
+      <c r="V246" s="61"/>
+      <c r="W246" s="61"/>
+      <c r="X246" s="61"/>
+      <c r="Y246" s="61"/>
+      <c r="Z246" s="61"/>
+      <c r="AA246" s="61"/>
+      <c r="AB246" s="61"/>
+      <c r="AC246" s="61"/>
+      <c r="AD246" s="61"/>
+      <c r="AE246" s="61"/>
+      <c r="AF246" s="61"/>
+      <c r="AG246" s="61"/>
+      <c r="AH246" s="61"/>
+      <c r="AI246" s="61"/>
+      <c r="AJ246" s="61"/>
+      <c r="AK246" s="61"/>
+      <c r="AL246" s="61"/>
+      <c r="AM246" s="61"/>
+      <c r="AN246" s="61"/>
+      <c r="AO246" s="61"/>
+      <c r="AP246" s="61"/>
+      <c r="AQ246" s="61"/>
+      <c r="AR246" s="61"/>
+      <c r="AS246" s="61"/>
+      <c r="AT246" s="61"/>
+      <c r="AU246" s="61"/>
+      <c r="AV246" s="61"/>
+      <c r="AW246" s="61"/>
+      <c r="AX246" s="61"/>
+      <c r="AY246" s="61"/>
+      <c r="AZ246" s="61"/>
+      <c r="BA246" s="61"/>
+      <c r="BB246" s="61"/>
+      <c r="BC246" s="61"/>
+      <c r="BD246" s="61"/>
+      <c r="BE246" s="61"/>
+      <c r="BF246" s="61"/>
+      <c r="BG246" s="61"/>
+      <c r="BH246" s="61"/>
+      <c r="BI246" s="61"/>
+      <c r="BJ246" s="61"/>
+      <c r="BK246" s="61"/>
+      <c r="BL246" s="61"/>
+      <c r="BM246" s="61"/>
+      <c r="BN246" s="61"/>
+      <c r="BO246" s="61"/>
+      <c r="BP246" s="61"/>
+      <c r="BQ246" s="61"/>
+      <c r="BR246" s="61"/>
+      <c r="BS246" s="61"/>
+      <c r="BT246" s="61"/>
+      <c r="BU246" s="61"/>
+      <c r="BV246" s="61"/>
+      <c r="BW246" s="61"/>
+      <c r="BX246" s="61"/>
+      <c r="BY246" s="61"/>
+      <c r="BZ246" s="61"/>
+      <c r="CA246" s="61"/>
+      <c r="CB246" s="61"/>
+      <c r="CC246" s="61"/>
+      <c r="CD246" s="61"/>
+      <c r="CE246" s="61"/>
+      <c r="CF246" s="61"/>
+      <c r="CG246" s="61"/>
+      <c r="CH246" s="61"/>
+      <c r="CI246" s="61"/>
+      <c r="CJ246" s="61"/>
+      <c r="CK246" s="61"/>
+      <c r="CL246" s="61"/>
+      <c r="CM246" s="61"/>
+      <c r="CN246" s="61"/>
+      <c r="CO246" s="61"/>
+      <c r="CP246" s="61"/>
+      <c r="CQ246" s="61"/>
+      <c r="CR246" s="61"/>
+      <c r="CS246" s="61"/>
+      <c r="CT246" s="61"/>
+      <c r="CU246" s="61"/>
+      <c r="CV246" s="61"/>
+      <c r="CW246" s="61"/>
+      <c r="CX246" s="61"/>
+      <c r="CY246" s="61"/>
+      <c r="CZ246" s="61"/>
+      <c r="DA246" s="61"/>
+      <c r="DB246" s="61"/>
+      <c r="DC246" s="61"/>
+      <c r="DD246" s="61"/>
+      <c r="DE246" s="61"/>
+      <c r="DF246" s="61"/>
+      <c r="DG246" s="61"/>
+      <c r="DH246" s="61"/>
+      <c r="DI246" s="61"/>
+      <c r="DJ246" s="61"/>
+      <c r="DK246" s="61"/>
+      <c r="DL246" s="61"/>
+      <c r="DM246" s="61"/>
+      <c r="DN246" s="61"/>
+      <c r="DO246" s="61"/>
+      <c r="DP246" s="61"/>
+      <c r="DQ246" s="61"/>
+      <c r="DR246" s="61"/>
+      <c r="DS246" s="61"/>
+      <c r="DT246" s="61"/>
+      <c r="DU246" s="61"/>
+      <c r="DV246" s="61"/>
+      <c r="DW246" s="61"/>
+      <c r="DX246" s="61"/>
+      <c r="DY246" s="61"/>
+      <c r="DZ246" s="61"/>
+      <c r="EA246" s="61"/>
+      <c r="EB246" s="61"/>
+      <c r="EC246" s="61"/>
+      <c r="ED246" s="61"/>
+      <c r="EE246" s="61"/>
+      <c r="EF246" s="61"/>
+      <c r="EG246" s="61"/>
+      <c r="EH246" s="61"/>
+      <c r="EI246" s="61"/>
+      <c r="EJ246" s="61"/>
+      <c r="EK246" s="61"/>
+      <c r="EL246" s="61"/>
+      <c r="EM246" s="61"/>
+      <c r="EN246" s="61"/>
+      <c r="EO246" s="61"/>
+      <c r="EP246" s="61"/>
+      <c r="EQ246" s="61"/>
+      <c r="ER246" s="61"/>
+      <c r="ES246" s="61"/>
+      <c r="ET246" s="61"/>
+      <c r="EU246" s="61"/>
+      <c r="EV246" s="61"/>
+      <c r="EW246" s="61"/>
+      <c r="EX246" s="61"/>
+      <c r="EY246" s="61"/>
+      <c r="EZ246" s="61"/>
+      <c r="FA246" s="61"/>
+      <c r="FB246" s="61"/>
+      <c r="FC246" s="61"/>
+      <c r="FD246" s="61"/>
+      <c r="FE246" s="61"/>
+      <c r="FF246" s="61"/>
+      <c r="FG246" s="61"/>
+      <c r="FH246" s="61"/>
+      <c r="FI246" s="61"/>
+      <c r="FJ246" s="61"/>
+      <c r="FK246" s="61"/>
+      <c r="FL246" s="61"/>
+      <c r="FM246" s="61"/>
+      <c r="FN246" s="61"/>
+      <c r="FO246" s="61"/>
+      <c r="FP246" s="61"/>
+      <c r="FQ246" s="61"/>
+      <c r="FR246" s="61"/>
+      <c r="FS246" s="61"/>
+      <c r="FT246" s="61"/>
+      <c r="FU246" s="61"/>
+      <c r="FV246" s="61"/>
+      <c r="FW246" s="61"/>
+      <c r="FX246" s="61"/>
+      <c r="FY246" s="61"/>
+      <c r="FZ246" s="61"/>
+      <c r="GA246" s="61"/>
+      <c r="GB246" s="61"/>
+      <c r="GC246" s="61"/>
+      <c r="GD246" s="61"/>
+      <c r="GE246" s="61"/>
+      <c r="GF246" s="61"/>
+      <c r="GG246" s="61"/>
+      <c r="GH246" s="61"/>
+      <c r="GI246" s="61"/>
+      <c r="GJ246" s="61"/>
+      <c r="GK246" s="61"/>
+      <c r="GL246" s="61"/>
+      <c r="GM246" s="61"/>
+      <c r="GN246" s="61"/>
+      <c r="GO246" s="61"/>
+      <c r="GP246" s="61"/>
+      <c r="GQ246" s="61"/>
+      <c r="GR246" s="61"/>
+      <c r="GS246" s="61"/>
+      <c r="GT246" s="61"/>
+      <c r="GU246" s="61"/>
+      <c r="GV246" s="61"/>
+      <c r="GW246" s="61"/>
+      <c r="GX246" s="61"/>
+      <c r="GY246" s="61"/>
+      <c r="GZ246" s="61"/>
+      <c r="HA246" s="61"/>
+      <c r="HB246" s="61"/>
+      <c r="HC246" s="61"/>
+      <c r="HD246" s="61"/>
+      <c r="HE246" s="61"/>
+      <c r="HF246" s="61"/>
+      <c r="HG246" s="61"/>
+      <c r="HH246" s="61"/>
+      <c r="HI246" s="61"/>
+      <c r="HJ246" s="61"/>
+      <c r="HK246" s="61"/>
+      <c r="HL246" s="61"/>
+      <c r="HM246" s="61"/>
+      <c r="HN246" s="61"/>
+      <c r="HO246" s="61"/>
+      <c r="HP246" s="61"/>
+      <c r="HQ246" s="61"/>
+      <c r="HR246" s="61"/>
+      <c r="HS246" s="61"/>
+      <c r="HT246" s="61"/>
+      <c r="HU246" s="61"/>
+      <c r="HV246" s="61"/>
+      <c r="HW246" s="61"/>
+      <c r="HX246" s="61"/>
+      <c r="HY246" s="61"/>
+      <c r="HZ246" s="61"/>
+      <c r="IA246" s="61"/>
+      <c r="IB246" s="61"/>
+      <c r="IC246" s="61"/>
+      <c r="ID246" s="61"/>
+      <c r="IE246" s="61"/>
+      <c r="IF246" s="61"/>
+      <c r="IG246" s="61"/>
+      <c r="IH246" s="61"/>
+      <c r="II246" s="61"/>
+      <c r="IJ246" s="61"/>
+      <c r="IK246" s="61"/>
+      <c r="IL246" s="61"/>
     </row>
     <row r="247" spans="1:246" ht="17">
       <c r="A247" s="55" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="B247" s="55" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="C247" s="55" t="s">
         <v>95</v>
@@ -38383,20 +38683,20 @@
       <c r="L247" s="55"/>
       <c r="M247" s="55"/>
       <c r="N247" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P247" s="86" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
       <c r="S247" s="47"/>
       <c r="T247" s="47"/>
     </row>
     <row r="248" spans="1:246" ht="17">
       <c r="A248" s="52" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="B248" s="52" t="s">
-        <v>1331</v>
+        <v>1322</v>
       </c>
       <c r="C248" s="52" t="s">
         <v>95</v>
@@ -38432,20 +38732,20 @@
       <c r="L248" s="52"/>
       <c r="M248" s="52"/>
       <c r="N248" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P248" s="86" t="s">
-        <v>1321</v>
+        <v>1312</v>
       </c>
       <c r="S248" s="47"/>
       <c r="T248" s="47"/>
     </row>
     <row r="249" spans="1:246" ht="17">
       <c r="A249" s="55" t="s">
-        <v>1318</v>
+        <v>1309</v>
       </c>
       <c r="B249" s="55" t="s">
-        <v>1332</v>
+        <v>1323</v>
       </c>
       <c r="C249" s="55" t="s">
         <v>95</v>
@@ -38481,20 +38781,20 @@
       <c r="L249" s="55"/>
       <c r="M249" s="55"/>
       <c r="N249" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P249" s="86" t="s">
-        <v>1320</v>
+        <v>1311</v>
       </c>
       <c r="S249" s="47"/>
       <c r="T249" s="47"/>
     </row>
     <row r="250" spans="1:246" ht="16">
       <c r="A250" s="52" t="s">
-        <v>1319</v>
+        <v>1310</v>
       </c>
       <c r="B250" s="52" t="s">
-        <v>1322</v>
+        <v>1313</v>
       </c>
       <c r="C250" s="52" t="s">
         <v>96</v>
@@ -38528,10 +38828,10 @@
       <c r="L250" s="52"/>
       <c r="M250" s="52"/>
       <c r="N250" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O250" s="47" t="s">
-        <v>1323</v>
+        <v>1314</v>
       </c>
       <c r="P250" s="86"/>
       <c r="S250" s="47"/>
@@ -38539,10 +38839,10 @@
     </row>
     <row r="251" spans="1:246" ht="16">
       <c r="A251" s="55" t="s">
-        <v>1324</v>
+        <v>1315</v>
       </c>
       <c r="B251" s="55" t="s">
-        <v>1325</v>
+        <v>1316</v>
       </c>
       <c r="C251" s="55" t="s">
         <v>96</v>
@@ -38576,10 +38876,10 @@
       <c r="L251" s="55"/>
       <c r="M251" s="55"/>
       <c r="N251" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O251" s="47" t="s">
-        <v>1326</v>
+        <v>1317</v>
       </c>
       <c r="P251" s="86"/>
       <c r="S251" s="47"/>
@@ -38587,10 +38887,10 @@
     </row>
     <row r="252" spans="1:246" ht="16">
       <c r="A252" s="52" t="s">
-        <v>1327</v>
+        <v>1318</v>
       </c>
       <c r="B252" s="52" t="s">
-        <v>1328</v>
+        <v>1319</v>
       </c>
       <c r="C252" s="52" t="s">
         <v>96</v>
@@ -38624,10 +38924,10 @@
       <c r="L252" s="52"/>
       <c r="M252" s="52"/>
       <c r="N252" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O252" s="47" t="s">
-        <v>1326</v>
+        <v>1317</v>
       </c>
       <c r="P252" s="86"/>
       <c r="S252" s="47"/>
@@ -38635,10 +38935,10 @@
     </row>
     <row r="253" spans="1:246" ht="16">
       <c r="A253" s="55" t="s">
-        <v>1329</v>
+        <v>1320</v>
       </c>
       <c r="B253" s="55" t="s">
-        <v>1330</v>
+        <v>1321</v>
       </c>
       <c r="C253" s="55" t="s">
         <v>96</v>
@@ -38672,10 +38972,10 @@
       <c r="L253" s="55"/>
       <c r="M253" s="55"/>
       <c r="N253" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O253" s="47" t="s">
-        <v>1323</v>
+        <v>1314</v>
       </c>
       <c r="P253" s="86"/>
       <c r="S253" s="47"/>
@@ -38683,10 +38983,10 @@
     </row>
     <row r="254" spans="1:246" ht="16">
       <c r="A254" s="52" t="s">
-        <v>1333</v>
+        <v>1324</v>
       </c>
       <c r="B254" s="52" t="s">
-        <v>1356</v>
+        <v>1346</v>
       </c>
       <c r="C254" s="52" t="s">
         <v>95</v>
@@ -38720,7 +39020,7 @@
         <v>3564</v>
       </c>
       <c r="L254" s="52" t="s">
-        <v>1334</v>
+        <v>1325</v>
       </c>
       <c r="M254" s="52"/>
       <c r="N254" s="47" t="s">
@@ -38732,10 +39032,10 @@
     </row>
     <row r="255" spans="1:246" ht="16">
       <c r="A255" s="55" t="s">
-        <v>1336</v>
+        <v>1327</v>
       </c>
       <c r="B255" s="55" t="s">
-        <v>1357</v>
+        <v>1347</v>
       </c>
       <c r="C255" s="55" t="s">
         <v>95</v>
@@ -38747,10 +39047,10 @@
         <v>1380</v>
       </c>
       <c r="F255" s="64">
+        <v>2</v>
+      </c>
+      <c r="G255" s="64">
         <v>1</v>
-      </c>
-      <c r="G255" s="64">
-        <v>2</v>
       </c>
       <c r="H255" s="63">
         <f t="shared" si="18"/>
@@ -38762,14 +39062,14 @@
       </c>
       <c r="J255" s="63">
         <f t="shared" si="19"/>
-        <v>891</v>
+        <v>1782</v>
       </c>
       <c r="K255" s="63">
         <f t="shared" si="20"/>
-        <v>1782</v>
+        <v>891</v>
       </c>
       <c r="L255" s="55" t="s">
-        <v>1337</v>
+        <v>1380</v>
       </c>
       <c r="M255" s="55"/>
       <c r="N255" s="47" t="s">
@@ -38781,10 +39081,10 @@
     </row>
     <row r="256" spans="1:246" ht="16">
       <c r="A256" s="52" t="s">
-        <v>1353</v>
+        <v>1343</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>1358</v>
+        <v>1348</v>
       </c>
       <c r="C256" s="52" t="s">
         <v>95</v>
@@ -38820,7 +39120,7 @@
       <c r="L256" s="52"/>
       <c r="M256" s="52"/>
       <c r="N256" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P256" s="86"/>
       <c r="S256" s="47"/>
@@ -38828,10 +39128,10 @@
     </row>
     <row r="257" spans="1:20" ht="16">
       <c r="A257" s="55" t="s">
-        <v>1354</v>
+        <v>1344</v>
       </c>
       <c r="B257" s="55" t="s">
-        <v>1359</v>
+        <v>1349</v>
       </c>
       <c r="C257" s="55" t="s">
         <v>95</v>
@@ -38867,7 +39167,7 @@
       <c r="L257" s="55"/>
       <c r="M257" s="55"/>
       <c r="N257" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P257" s="86"/>
       <c r="S257" s="47"/>
@@ -38875,10 +39175,10 @@
     </row>
     <row r="258" spans="1:20" ht="16">
       <c r="A258" s="52" t="s">
-        <v>1355</v>
+        <v>1345</v>
       </c>
       <c r="B258" s="52" t="s">
-        <v>1360</v>
+        <v>1350</v>
       </c>
       <c r="C258" s="52" t="s">
         <v>95</v>
@@ -38914,7 +39214,7 @@
       <c r="L258" s="52"/>
       <c r="M258" s="52"/>
       <c r="N258" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P258" s="86"/>
       <c r="S258" s="47"/>
@@ -38922,10 +39222,10 @@
     </row>
     <row r="259" spans="1:20" ht="17">
       <c r="A259" s="55" t="s">
-        <v>1362</v>
+        <v>1352</v>
       </c>
       <c r="B259" s="55" t="s">
-        <v>1374</v>
+        <v>1364</v>
       </c>
       <c r="C259" s="55" t="s">
         <v>95</v>
@@ -38961,20 +39261,20 @@
       <c r="L259" s="55"/>
       <c r="M259" s="55"/>
       <c r="N259" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P259" s="86" t="s">
-        <v>1375</v>
+        <v>1365</v>
       </c>
       <c r="S259" s="47"/>
       <c r="T259" s="47"/>
     </row>
     <row r="260" spans="1:20" ht="17">
       <c r="A260" s="52" t="s">
-        <v>1363</v>
+        <v>1353</v>
       </c>
       <c r="B260" s="52" t="s">
-        <v>1376</v>
+        <v>1366</v>
       </c>
       <c r="C260" s="52" t="s">
         <v>95</v>
@@ -39010,20 +39310,20 @@
       <c r="L260" s="52"/>
       <c r="M260" s="52"/>
       <c r="N260" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P260" s="86" t="s">
-        <v>1379</v>
+        <v>1369</v>
       </c>
       <c r="S260" s="47"/>
       <c r="T260" s="47"/>
     </row>
     <row r="261" spans="1:20" ht="17">
       <c r="A261" s="55" t="s">
-        <v>1364</v>
+        <v>1354</v>
       </c>
       <c r="B261" s="55" t="s">
-        <v>1370</v>
+        <v>1360</v>
       </c>
       <c r="C261" s="55" t="s">
         <v>95</v>
@@ -39059,20 +39359,20 @@
       <c r="L261" s="55"/>
       <c r="M261" s="55"/>
       <c r="N261" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P261" s="86" t="s">
-        <v>1371</v>
+        <v>1361</v>
       </c>
       <c r="S261" s="47"/>
       <c r="T261" s="47"/>
     </row>
     <row r="262" spans="1:20" ht="17">
       <c r="A262" s="52" t="s">
-        <v>1365</v>
+        <v>1355</v>
       </c>
       <c r="B262" s="52" t="s">
-        <v>1368</v>
+        <v>1358</v>
       </c>
       <c r="C262" s="52" t="s">
         <v>95</v>
@@ -39108,20 +39408,20 @@
       <c r="L262" s="52"/>
       <c r="M262" s="52"/>
       <c r="N262" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P262" s="86" t="s">
-        <v>1369</v>
+        <v>1359</v>
       </c>
       <c r="S262" s="47"/>
       <c r="T262" s="47"/>
     </row>
     <row r="263" spans="1:20" ht="17">
       <c r="A263" s="55" t="s">
-        <v>1366</v>
+        <v>1356</v>
       </c>
       <c r="B263" s="55" t="s">
-        <v>1372</v>
+        <v>1362</v>
       </c>
       <c r="C263" s="55" t="s">
         <v>95</v>
@@ -39157,20 +39457,20 @@
       <c r="L263" s="55"/>
       <c r="M263" s="55"/>
       <c r="N263" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P263" s="86" t="s">
-        <v>1373</v>
+        <v>1363</v>
       </c>
       <c r="S263" s="47"/>
       <c r="T263" s="47"/>
     </row>
     <row r="264" spans="1:20" ht="34">
       <c r="A264" s="52" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B264" s="52" t="s">
         <v>1367</v>
-      </c>
-      <c r="B264" s="52" t="s">
-        <v>1377</v>
       </c>
       <c r="C264" s="52" t="s">
         <v>95</v>
@@ -39206,10 +39506,10 @@
       <c r="L264" s="52"/>
       <c r="M264" s="52"/>
       <c r="N264" s="47" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P264" s="86" t="s">
-        <v>1378</v>
+        <v>1368</v>
       </c>
       <c r="S264" s="47"/>
       <c r="T264" s="47"/>
@@ -45032,7 +45332,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B1" s="93"/>
     </row>
@@ -45041,7 +45341,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -45073,25 +45373,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="71" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D7" s="71" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E7" s="71" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F7" s="71" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G7" s="71" t="s">
         <v>1042</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="H7" s="71" t="s">
         <v>1043</v>
-      </c>
-      <c r="D7" s="71" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E7" s="71" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F7" s="71" t="s">
-        <v>1046</v>
-      </c>
-      <c r="G7" s="71" t="s">
-        <v>1047</v>
-      </c>
-      <c r="H7" s="71" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -45100,15 +45400,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>262941</v>
+        <v>261321</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>200779.66666666666</v>
+        <v>198839</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>62161.333333333343</v>
+        <v>62482</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45116,7 +45416,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>62161.333333333343</v>
+        <v>62482</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -45124,7 +45424,7 @@
       </c>
       <c r="H8" s="73">
         <f>F8-G8</f>
-        <v>43857.993333333347</v>
+        <v>44178.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -45133,15 +45433,15 @@
       </c>
       <c r="B9" s="11">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A9,Purchases!$C:$C),0)</f>
-        <v>306798</v>
+        <v>302596</v>
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>200779.66666666666</v>
+        <v>198839</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>106018.33333333334</v>
+        <v>103757</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45149,7 +45449,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>106018.33333333334</v>
+        <v>103757</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -45157,7 +45457,7 @@
       </c>
       <c r="H9" s="74">
         <f>F9-G9</f>
-        <v>64379.003333333341</v>
+        <v>62117.67</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -45170,11 +45470,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>200779.66666666666</v>
+        <v>198839</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-168179.66666666666</v>
+        <v>-166239</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45182,7 +45482,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-168179.66666666666</v>
+        <v>-166239</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -45190,12 +45490,12 @@
       </c>
       <c r="H10" s="73">
         <f>F10-G10</f>
-        <v>-108236.99666666666</v>
+        <v>-106296.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="94" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="B12" s="94"/>
       <c r="C12" s="94"/>
@@ -45208,13 +45508,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C13" s="71" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="E13" s="71" t="s">
         <v>99</v>
@@ -45228,7 +45528,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -45246,7 +45546,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -45300,7 +45600,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -45318,7 +45618,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -45336,7 +45636,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -45354,7 +45654,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -45372,7 +45672,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -45408,7 +45708,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -45444,7 +45744,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -45462,7 +45762,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -45545,7 +45845,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
     </row>
   </sheetData>
@@ -45575,7 +45875,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="78" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="72" customFormat="1" ht="13.5" customHeight="1">
@@ -45583,22 +45883,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="C3" s="71" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="F3" s="71" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="G3" s="71" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -45607,7 +45907,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>485198</v>
+        <v>493648</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -45615,11 +45915,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>184970.65339999998</v>
+        <v>188588.0434</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>300227.34660000005</v>
+        <v>305059.95660000003</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -45627,7 +45927,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>162917.32060000004</v>
+        <v>167749.93060000002</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -45636,7 +45936,7 @@
       </c>
       <c r="B5" s="11">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A5,Sales!$I:$I,"Completed"),0)</f>
-        <v>56073</v>
+        <v>58473</v>
       </c>
       <c r="C5" s="11">
         <f>VLOOKUP($A5,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -45644,11 +45944,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>184859.69320000001</v>
+        <v>188474.91320000001</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-128786.69320000001</v>
+        <v>-130001.91320000001</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -45656,7 +45956,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-57199.651200000008</v>
+        <v>-58414.871200000009</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -45673,11 +45973,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>184970.65339999998</v>
+        <v>188588.0434</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-172440.65339999998</v>
+        <v>-176058.0434</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -45685,7 +45985,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-106717.66939999997</v>
+        <v>-110335.05939999998</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -45695,27 +45995,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Chiraath-Summary-Sep26.xlsx
+++ b/docs/Chiraath-Summary-Sep26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EA5CD3-095A-FD41-813C-21E310EFA09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9AF3DB-1A9F-7344-B49D-5F111706D3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3535" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3551" uniqueCount="1398">
   <si>
     <t>Notes:</t>
   </si>
@@ -3552,12 +3552,6 @@
     <t>CHR-111 white cotton salwar, Banarasi golden yellow blue</t>
   </si>
   <si>
-    <t>Teena mathew - Paeach</t>
-  </si>
-  <si>
-    <t>pink, light green, light blue</t>
-  </si>
-  <si>
     <t>Niroop</t>
   </si>
   <si>
@@ -3772,9 +3766,6 @@
   </si>
   <si>
     <t>Aruna - 1400</t>
-  </si>
-  <si>
-    <t>Golden &amp; yellow with temple design, Golden &amp; Green with temple design</t>
   </si>
   <si>
     <t>Dark biege with floral digital print</t>
@@ -3955,12 +3946,6 @@
     <t>CHR-165 - Checked Green, CHR-204 - Black/Pink</t>
   </si>
   <si>
-    <t>Navya - Black Orange, Saida - Black Pink</t>
-  </si>
-  <si>
-    <t>Violet/bottle green</t>
-  </si>
-  <si>
     <t>CHR-212 Yellow/Orange</t>
   </si>
   <si>
@@ -4205,9 +4190,6 @@
     <t>Anu Mathew (Canada)</t>
   </si>
   <si>
-    <t>Reetha Peethambaran, Anu Mathew (Canada)</t>
-  </si>
-  <si>
     <t>CHR-255 new chikku green</t>
   </si>
   <si>
@@ -4251,6 +4233,30 @@
   </si>
   <si>
     <t>Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden &amp; yellow with temple design, </t>
+  </si>
+  <si>
+    <t>pink, light green</t>
+  </si>
+  <si>
+    <t>Teena mathew - Paeach, Susmi - light blue (500)</t>
+  </si>
+  <si>
+    <t>Navya - Black Orange, Saida - Black Pink, Susmi - Violet/bottle green (800)</t>
+  </si>
+  <si>
+    <t>CHR-198 Semi Silk Blue</t>
+  </si>
+  <si>
+    <t>CHR-204 Violet Matka</t>
+  </si>
+  <si>
+    <t>Gpau</t>
+  </si>
+  <si>
+    <t>Reetha Peethambaran, Anu Mathew (Canada), Komallavali</t>
   </si>
 </sst>
 </file>
@@ -4862,6 +4868,12 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4870,12 +4882,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5164,7 +5170,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>366</c:v>
+                  <c:v>369</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>102</c:v>
@@ -5267,7 +5273,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>85</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>62</c:v>
@@ -5600,7 +5606,7 @@
                   <c:v>67003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-191178.99333333335</c:v>
+                  <c:v>-193900.99333333335</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5939,7 +5945,7 @@
                   <c:v>45848</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-5678</c:v>
+                  <c:v>-7168</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6099,7 +6105,7 @@
                   <c:v>79098</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6180</c:v>
+                  <c:v>8860</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6539,7 +6545,7 @@
                   <c:v>33250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11858</c:v>
+                  <c:v>16028</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6997,10 +7003,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>473</c:v>
+                  <c:v>476</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8192,7 +8198,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>596517</v>
+        <v>595027</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -8207,7 +8213,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>565651</v>
+        <v>568331</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -8224,7 +8230,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>578731</v>
+        <v>581411</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -8241,7 +8247,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-30866</v>
+        <v>-26696</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8276,7 +8282,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>44178.66</v>
+        <v>44072.32666666666</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -8286,7 +8292,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>62117.67</v>
+        <v>61727.336666666655</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -8296,7 +8302,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-106296.33</v>
+        <v>-105799.66333333334</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -8335,15 +8341,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>261321</v>
+        <v>260718</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>198839</v>
+        <v>198342.33333333334</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>62482</v>
+        <v>62375.666666666657</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8351,11 +8357,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>44178.66</v>
+        <v>44072.32666666666</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹44,179</v>
+        <v>Receive ₹44,072</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -8365,15 +8371,15 @@
       </c>
       <c r="B19" s="12">
         <f>PartnerShares!B9</f>
-        <v>302596</v>
+        <v>301709</v>
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>198839</v>
+        <v>198342.33333333334</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>103757</v>
+        <v>103366.66666666666</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8381,11 +8387,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>62117.67</v>
+        <v>61727.336666666655</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹62,118</v>
+        <v>Receive ₹61,727</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -8399,11 +8405,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>198839</v>
+        <v>198342.33333333334</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-166239</v>
+        <v>-165742.33333333334</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8411,11 +8417,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-106296.33</v>
+        <v>-105799.66333333334</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹106,296</v>
+        <v>Pay ₹105,800</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -8453,15 +8459,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>493648</v>
+        <v>495678</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>188588.0434</v>
+        <v>189481.55539999998</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>305059.95660000003</v>
+        <v>306196.44460000005</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8469,11 +8475,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>167749.93060000002</v>
+        <v>168886.41860000003</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹167,750</v>
+        <v>Pay ₹168,886</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8483,15 +8489,15 @@
       </c>
       <c r="B27" s="12">
         <f>'Cash Pool'!B5</f>
-        <v>58473</v>
+        <v>59123</v>
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>188474.91320000001</v>
+        <v>189367.88920000001</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-130001.91320000001</v>
+        <v>-130244.88920000001</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8499,11 +8505,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-58414.871200000009</v>
+        <v>-58657.847200000004</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹58,415</v>
+        <v>Receive ₹58,658</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8517,11 +8523,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>188588.0434</v>
+        <v>189481.55539999998</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-176058.0434</v>
+        <v>-176951.55539999998</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8529,11 +8535,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-110335.05939999998</v>
+        <v>-111228.57139999997</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹110,335</v>
+        <v>Receive ₹111,229</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8628,16 +8634,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -8645,7 +8651,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8654,14 +8660,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>596517</v>
+        <v>595027</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>565651</v>
+        <v>568331</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8670,14 +8676,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-30866</v>
+        <v>-26696</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>-135547.79333333333</v>
+        <v>-138269.79333333333</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8729,7 +8735,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8753,7 +8759,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8864,15 +8870,15 @@
       </c>
       <c r="B18" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A18)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>-5678</v>
+        <v>-7168</v>
       </c>
       <c r="C18" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>6180</v>
+        <v>8860</v>
       </c>
       <c r="D18" s="21">
         <f t="shared" si="0"/>
-        <v>11858</v>
+        <v>16028</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
@@ -8949,11 +8955,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8980,7 +8986,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$475=J48)*(INVENTORY!$D$2:$D$475)*(INVENTORY!$G$2:$G$475))</f>
-        <v>-191178.99333333335</v>
+        <v>-193900.99333333335</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10577,7 +10583,7 @@
         <v>570</v>
       </c>
       <c r="D107" s="39" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
@@ -10605,7 +10611,7 @@
         <v>320</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
@@ -10619,7 +10625,7 @@
         <v>3046</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15" customHeight="1">
@@ -10689,7 +10695,7 @@
         <v>-4202</v>
       </c>
       <c r="D115" s="39" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
@@ -10703,20 +10709,36 @@
         <v>-1620</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
-      <c r="A117" s="38"/>
-      <c r="B117" s="39"/>
-      <c r="C117" s="40"/>
-      <c r="D117" s="39"/>
+      <c r="A117" s="38">
+        <v>46277</v>
+      </c>
+      <c r="B117" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C117" s="40">
+        <v>-603</v>
+      </c>
+      <c r="D117" s="39" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="118" spans="1:4" ht="15" customHeight="1">
-      <c r="A118" s="35"/>
-      <c r="B118" s="36"/>
-      <c r="C118" s="37"/>
-      <c r="D118" s="36"/>
+      <c r="A118" s="35">
+        <v>46277</v>
+      </c>
+      <c r="B118" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C118" s="37">
+        <v>-887</v>
+      </c>
+      <c r="D118" s="36" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="119" spans="1:4" ht="15" customHeight="1">
       <c r="A119" s="38"/>
@@ -19234,7 +19256,7 @@
       <c r="F264" s="44"/>
       <c r="G264" s="44"/>
       <c r="H264" s="44" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="I264" s="44" t="s">
         <v>356</v>
@@ -19259,7 +19281,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>148</v>
@@ -19320,7 +19342,7 @@
         <v>46208</v>
       </c>
       <c r="B268" s="44" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C268" s="83">
         <v>2350</v>
@@ -19330,7 +19352,7 @@
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>356</v>
@@ -19366,7 +19388,7 @@
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -19641,7 +19663,7 @@
         <v>46219</v>
       </c>
       <c r="B281" s="45" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="C281" s="85">
         <v>3600</v>
@@ -19655,7 +19677,7 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
@@ -19916,7 +19938,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="C292" s="85">
         <v>3600</v>
@@ -19926,7 +19948,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19947,7 +19969,7 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
@@ -19972,7 +19994,7 @@
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="I294" s="45" t="s">
         <v>148</v>
@@ -19983,13 +20005,13 @@
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C295" s="83">
         <v>3700</v>
       </c>
       <c r="D295" s="44" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="E295" s="44" t="s">
         <v>49</v>
@@ -19997,7 +20019,7 @@
       <c r="F295" s="44"/>
       <c r="G295" s="44"/>
       <c r="H295" s="44" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="I295" s="44" t="s">
         <v>148</v>
@@ -20008,7 +20030,7 @@
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C296" s="85">
         <v>1450</v>
@@ -20022,7 +20044,7 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
@@ -20033,7 +20055,7 @@
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -20047,7 +20069,7 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
@@ -20058,7 +20080,7 @@
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C298" s="85">
         <v>1479</v>
@@ -20072,7 +20094,7 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
@@ -20083,7 +20105,7 @@
         <v>46236</v>
       </c>
       <c r="B299" s="44" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C299" s="83">
         <v>2630</v>
@@ -20097,7 +20119,7 @@
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
       <c r="H299" s="44" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="I299" s="44" t="s">
         <v>148</v>
@@ -20133,7 +20155,7 @@
         <v>46238</v>
       </c>
       <c r="B301" s="44" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C301" s="83">
         <v>12650</v>
@@ -20147,7 +20169,7 @@
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
       <c r="H301" s="44" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="I301" s="44" t="s">
         <v>148</v>
@@ -20158,7 +20180,7 @@
         <v>46240</v>
       </c>
       <c r="B302" s="45" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C302" s="85">
         <v>1000</v>
@@ -20168,7 +20190,7 @@
       <c r="F302" s="46"/>
       <c r="G302" s="46"/>
       <c r="H302" s="46" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="I302" s="45" t="s">
         <v>148</v>
@@ -20193,7 +20215,7 @@
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="I303" s="44" t="s">
         <v>148</v>
@@ -20204,7 +20226,7 @@
         <v>46243</v>
       </c>
       <c r="B304" s="45" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="C304" s="85">
         <v>950</v>
@@ -20218,7 +20240,7 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>148</v>
@@ -20229,7 +20251,7 @@
         <v>46243</v>
       </c>
       <c r="B305" s="44" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C305" s="83">
         <v>1380</v>
@@ -20243,7 +20265,7 @@
       <c r="F305" s="44"/>
       <c r="G305" s="44"/>
       <c r="H305" s="44" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="I305" s="44" t="s">
         <v>148</v>
@@ -20254,7 +20276,7 @@
         <v>46243</v>
       </c>
       <c r="B306" s="45" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C306" s="85">
         <v>1250</v>
@@ -20268,7 +20290,7 @@
       <c r="F306" s="46"/>
       <c r="G306" s="46"/>
       <c r="H306" s="46" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="I306" s="45" t="s">
         <v>148</v>
@@ -20279,7 +20301,7 @@
         <v>46243</v>
       </c>
       <c r="B307" s="44" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C307" s="83">
         <v>5750</v>
@@ -20293,7 +20315,7 @@
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
       <c r="H307" s="44" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="I307" s="44" t="s">
         <v>148</v>
@@ -20304,7 +20326,7 @@
         <v>46248</v>
       </c>
       <c r="B308" s="44" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C308" s="83">
         <v>1380</v>
@@ -20318,7 +20340,7 @@
       <c r="F308" s="44"/>
       <c r="G308" s="44"/>
       <c r="H308" s="44" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="I308" s="44" t="s">
         <v>148</v>
@@ -20329,7 +20351,7 @@
         <v>46248</v>
       </c>
       <c r="B309" s="45" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C309" s="85">
         <v>1380</v>
@@ -20343,7 +20365,7 @@
       <c r="F309" s="46"/>
       <c r="G309" s="46"/>
       <c r="H309" s="46" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="I309" s="45" t="s">
         <v>148</v>
@@ -20368,7 +20390,7 @@
       <c r="F310" s="44"/>
       <c r="G310" s="44"/>
       <c r="H310" s="44" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="I310" s="44" t="s">
         <v>148</v>
@@ -20393,7 +20415,7 @@
       <c r="F311" s="46"/>
       <c r="G311" s="46"/>
       <c r="H311" s="46" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="I311" s="45" t="s">
         <v>148</v>
@@ -20404,7 +20426,7 @@
         <v>46250</v>
       </c>
       <c r="B312" s="44" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C312" s="83">
         <v>2250</v>
@@ -20418,7 +20440,7 @@
       <c r="F312" s="44"/>
       <c r="G312" s="44"/>
       <c r="H312" s="44" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="I312" s="44" t="s">
         <v>148</v>
@@ -20429,7 +20451,7 @@
         <v>46252</v>
       </c>
       <c r="B313" s="45" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C313" s="85">
         <v>5750</v>
@@ -20443,7 +20465,7 @@
       <c r="F313" s="46"/>
       <c r="G313" s="46"/>
       <c r="H313" s="46" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="I313" s="45" t="s">
         <v>148</v>
@@ -20454,7 +20476,7 @@
         <v>46252</v>
       </c>
       <c r="B314" s="44" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C314" s="83">
         <v>1380</v>
@@ -20468,7 +20490,7 @@
       <c r="F314" s="44"/>
       <c r="G314" s="44"/>
       <c r="H314" s="44" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="I314" s="44" t="s">
         <v>148</v>
@@ -20479,7 +20501,7 @@
         <v>46252</v>
       </c>
       <c r="B315" s="45" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C315" s="85">
         <v>5750</v>
@@ -20493,7 +20515,7 @@
       <c r="F315" s="46"/>
       <c r="G315" s="46"/>
       <c r="H315" s="46" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="I315" s="45" t="s">
         <v>148</v>
@@ -20504,7 +20526,7 @@
         <v>46252</v>
       </c>
       <c r="B316" s="44" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="C316" s="83">
         <v>1340</v>
@@ -20518,7 +20540,7 @@
       <c r="F316" s="44"/>
       <c r="G316" s="44"/>
       <c r="H316" s="44" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="I316" s="44" t="s">
         <v>148</v>
@@ -20529,7 +20551,7 @@
         <v>46252</v>
       </c>
       <c r="B317" s="45" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="C317" s="85">
         <v>1250</v>
@@ -20543,7 +20565,7 @@
       <c r="F317" s="46"/>
       <c r="G317" s="46"/>
       <c r="H317" s="46" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="I317" s="45" t="s">
         <v>148</v>
@@ -20554,7 +20576,7 @@
         <v>46257</v>
       </c>
       <c r="B318" s="44" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C318" s="83">
         <v>1780</v>
@@ -20568,7 +20590,7 @@
       <c r="F318" s="44"/>
       <c r="G318" s="44"/>
       <c r="H318" s="44" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="I318" s="44" t="s">
         <v>148</v>
@@ -20593,7 +20615,7 @@
       <c r="F319" s="46"/>
       <c r="G319" s="46"/>
       <c r="H319" s="46" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="I319" s="45" t="s">
         <v>148</v>
@@ -20618,7 +20640,7 @@
       <c r="F320" s="44"/>
       <c r="G320" s="44"/>
       <c r="H320" s="44" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="I320" s="44" t="s">
         <v>148</v>
@@ -20629,7 +20651,7 @@
         <v>46257</v>
       </c>
       <c r="B321" s="45" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="C321" s="85">
         <v>1500</v>
@@ -20643,7 +20665,7 @@
       <c r="F321" s="46"/>
       <c r="G321" s="46"/>
       <c r="H321" s="46" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="I321" s="45" t="s">
         <v>148</v>
@@ -20654,7 +20676,7 @@
         <v>46258</v>
       </c>
       <c r="B322" s="44" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="C322" s="83">
         <v>1250</v>
@@ -20668,7 +20690,7 @@
       <c r="F322" s="44"/>
       <c r="G322" s="44"/>
       <c r="H322" s="44" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="I322" s="44" t="s">
         <v>148</v>
@@ -20679,7 +20701,7 @@
         <v>46263</v>
       </c>
       <c r="B323" s="45" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="C323" s="85">
         <v>1380</v>
@@ -20693,7 +20715,7 @@
       <c r="F323" s="46"/>
       <c r="G323" s="46"/>
       <c r="H323" s="46" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="I323" s="45" t="s">
         <v>148</v>
@@ -20704,7 +20726,7 @@
         <v>46263</v>
       </c>
       <c r="B324" s="44" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="C324" s="83">
         <v>1380</v>
@@ -20718,7 +20740,7 @@
       <c r="F324" s="44"/>
       <c r="G324" s="44"/>
       <c r="H324" s="44" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="I324" s="44" t="s">
         <v>148</v>
@@ -20729,7 +20751,7 @@
         <v>46263</v>
       </c>
       <c r="B325" s="45" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="C325" s="85">
         <v>2500</v>
@@ -20743,7 +20765,7 @@
       <c r="F325" s="46"/>
       <c r="G325" s="46"/>
       <c r="H325" s="46" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="I325" s="45" t="s">
         <v>148</v>
@@ -20768,7 +20790,7 @@
       <c r="F326" s="44"/>
       <c r="G326" s="44"/>
       <c r="H326" s="44" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="I326" s="44" t="s">
         <v>148</v>
@@ -20779,7 +20801,7 @@
         <v>46257</v>
       </c>
       <c r="B327" s="45" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="C327" s="85">
         <v>750</v>
@@ -20793,7 +20815,7 @@
       <c r="F327" s="46"/>
       <c r="G327" s="46"/>
       <c r="H327" s="46" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="I327" s="45" t="s">
         <v>148</v>
@@ -20804,7 +20826,7 @@
         <v>46275</v>
       </c>
       <c r="B328" s="44" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="C328" s="83">
         <v>1380</v>
@@ -20818,7 +20840,7 @@
       <c r="F328" s="44"/>
       <c r="G328" s="44"/>
       <c r="H328" s="44" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="I328" s="44" t="s">
         <v>148</v>
@@ -20834,16 +20856,12 @@
       <c r="C329" s="85">
         <v>2400</v>
       </c>
-      <c r="D329" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="E329" s="45" t="s">
-        <v>49</v>
-      </c>
+      <c r="D329" s="45"/>
+      <c r="E329" s="45"/>
       <c r="F329" s="46"/>
       <c r="G329" s="46"/>
       <c r="H329" s="46" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="I329" s="45" t="s">
         <v>356</v>
@@ -20854,7 +20872,7 @@
         <v>46275</v>
       </c>
       <c r="B330" s="44" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="C330" s="83">
         <v>1450</v>
@@ -20868,7 +20886,7 @@
       <c r="F330" s="44"/>
       <c r="G330" s="44"/>
       <c r="H330" s="44" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="I330" s="44" t="s">
         <v>148</v>
@@ -20879,7 +20897,7 @@
         <v>46275</v>
       </c>
       <c r="B331" s="45" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="C331" s="85">
         <v>950</v>
@@ -20893,44 +20911,86 @@
       <c r="F331" s="46"/>
       <c r="G331" s="46"/>
       <c r="H331" s="46" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="I331" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="332" spans="1:9">
-      <c r="A332" s="82"/>
-      <c r="B332" s="44"/>
-      <c r="C332" s="83"/>
-      <c r="D332" s="44"/>
-      <c r="E332" s="44"/>
+    <row r="332" spans="1:9" ht="14">
+      <c r="A332" s="82">
+        <v>46277</v>
+      </c>
+      <c r="B332" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="C332" s="83">
+        <v>650</v>
+      </c>
+      <c r="D332" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E332" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F332" s="44"/>
       <c r="G332" s="44"/>
-      <c r="H332" s="44"/>
-      <c r="I332" s="44"/>
-    </row>
-    <row r="333" spans="1:9">
-      <c r="A333" s="84"/>
-      <c r="B333" s="45"/>
-      <c r="C333" s="85"/>
-      <c r="D333" s="45"/>
-      <c r="E333" s="45"/>
+      <c r="H332" s="44" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I332" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="14">
+      <c r="A333" s="84">
+        <v>46277</v>
+      </c>
+      <c r="B333" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="C333" s="85">
+        <v>650</v>
+      </c>
+      <c r="D333" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="E333" s="45" t="s">
+        <v>50</v>
+      </c>
       <c r="F333" s="46"/>
       <c r="G333" s="46"/>
-      <c r="H333" s="46"/>
-      <c r="I333" s="45"/>
-    </row>
-    <row r="334" spans="1:9">
-      <c r="A334" s="82"/>
-      <c r="B334" s="44"/>
-      <c r="C334" s="83"/>
-      <c r="D334" s="44"/>
-      <c r="E334" s="44"/>
+      <c r="H333" s="46" t="s">
+        <v>1395</v>
+      </c>
+      <c r="I333" s="45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" ht="14">
+      <c r="A334" s="82">
+        <v>46277</v>
+      </c>
+      <c r="B334" s="44" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C334" s="83">
+        <v>1380</v>
+      </c>
+      <c r="D334" s="44" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E334" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F334" s="44"/>
       <c r="G334" s="44"/>
-      <c r="H334" s="44"/>
-      <c r="I334" s="44"/>
+      <c r="H334" s="44" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I334" s="44" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="84"/>
@@ -27763,7 +27823,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="55" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="M59" s="55"/>
       <c r="N59" s="55" t="s">
@@ -28775,7 +28835,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="52" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
       <c r="M78" s="52"/>
       <c r="N78" s="52" t="s">
@@ -29095,14 +29155,14 @@
         <v>450</v>
       </c>
       <c r="L84" s="52" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="M84" s="52"/>
       <c r="N84" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O84" s="52" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="P84" s="52"/>
       <c r="Q84" s="52"/>
@@ -29201,14 +29261,14 @@
         <v>1045</v>
       </c>
       <c r="L86" s="52" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
       <c r="M86" s="52"/>
       <c r="N86" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O86" s="52" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="P86" s="52"/>
       <c r="Q86" s="52"/>
@@ -31015,7 +31075,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -34103,7 +34163,7 @@
         <v>606</v>
       </c>
       <c r="L166" s="52" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="M166" s="52"/>
       <c r="N166" s="52" t="s">
@@ -34111,7 +34171,7 @@
       </c>
       <c r="O166" s="52"/>
       <c r="P166" s="52" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="Q166" s="52"/>
       <c r="R166" s="52"/>
@@ -34423,7 +34483,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="52" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="M172" s="52"/>
       <c r="N172" s="52" t="s">
@@ -34579,7 +34639,7 @@
         <v>2793</v>
       </c>
       <c r="L175" s="55" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="M175" s="55"/>
       <c r="N175" s="55" t="s">
@@ -34587,7 +34647,7 @@
       </c>
       <c r="O175" s="55"/>
       <c r="P175" s="55" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="Q175" s="55"/>
       <c r="R175" s="55"/>
@@ -34899,14 +34959,14 @@
         <v>1019</v>
       </c>
       <c r="L181" s="55" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="M181" s="55"/>
       <c r="N181" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O181" s="55" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="P181" s="55" t="s">
         <v>949</v>
@@ -35058,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="52" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="M184" s="52"/>
       <c r="N184" s="52" t="s">
@@ -35212,7 +35272,7 @@
         <v>891</v>
       </c>
       <c r="L187" s="55" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="M187" s="55"/>
       <c r="N187" s="55" t="s">
@@ -35264,7 +35324,7 @@
         <v>891</v>
       </c>
       <c r="L188" s="52" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="M188" s="52"/>
       <c r="N188" s="52" t="s">
@@ -35316,7 +35376,7 @@
         <v>891</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -35324,7 +35384,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -35533,7 +35593,7 @@
         <v>977</v>
       </c>
       <c r="B194" s="52" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="C194" s="52" t="s">
         <v>95</v>
@@ -35567,14 +35627,14 @@
         <v>3950</v>
       </c>
       <c r="L194" s="52" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="M194" s="52"/>
       <c r="N194" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
@@ -35745,10 +35805,10 @@
         <v>850</v>
       </c>
       <c r="F198" s="64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G198" s="64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H198" s="63">
         <f t="shared" si="12"/>
@@ -35760,21 +35820,21 @@
       </c>
       <c r="J198" s="63">
         <f t="shared" si="13"/>
-        <v>467</v>
+        <v>934</v>
       </c>
       <c r="K198" s="63">
         <f t="shared" si="14"/>
-        <v>1401</v>
+        <v>934</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1163</v>
+        <v>1392</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1164</v>
+        <v>1391</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
@@ -35818,14 +35878,14 @@
         <v>1732</v>
       </c>
       <c r="L199" s="52" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="M199" s="52"/>
       <c r="N199" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P199" s="47" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="S199" s="47"/>
       <c r="T199" s="47"/>
@@ -35886,7 +35946,7 @@
         <v>996</v>
       </c>
       <c r="B201" s="55" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="C201" s="55" t="s">
         <v>95</v>
@@ -35927,7 +35987,7 @@
         <v>589</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
@@ -36051,10 +36111,10 @@
         <v>1250</v>
       </c>
       <c r="F204" s="64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G204" s="64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" s="63">
         <f t="shared" si="12"/>
@@ -36066,21 +36126,18 @@
       </c>
       <c r="J204" s="63">
         <f t="shared" si="13"/>
-        <v>1522</v>
+        <v>2283</v>
       </c>
       <c r="K204" s="63">
         <f t="shared" si="14"/>
-        <v>761</v>
+        <v>0</v>
       </c>
       <c r="L204" s="55" t="s">
-        <v>1297</v>
+        <v>1393</v>
       </c>
       <c r="M204" s="55"/>
       <c r="N204" s="47" t="s">
-        <v>589</v>
-      </c>
-      <c r="P204" s="47" t="s">
-        <v>1298</v>
+        <v>504</v>
       </c>
       <c r="S204" s="47"/>
       <c r="T204" s="47"/>
@@ -36226,14 +36283,14 @@
         <v>2346</v>
       </c>
       <c r="L207" s="52" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="M207" s="52"/>
       <c r="N207" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P207" s="47" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="S207" s="47"/>
       <c r="T207" s="47"/>
@@ -36377,7 +36434,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="55" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="M210" s="55"/>
       <c r="N210" s="47" t="s">
@@ -36428,7 +36485,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="52" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="M211" s="52"/>
       <c r="N211" s="47" t="s">
@@ -36476,14 +36533,14 @@
         <v>2775</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P212" s="47" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="S212" s="47"/>
       <c r="T212" s="47"/>
@@ -36527,7 +36584,7 @@
         <v>3340</v>
       </c>
       <c r="L213" s="52" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="M213" s="52"/>
       <c r="N213" s="47" t="s">
@@ -36578,7 +36635,7 @@
         <v>1984</v>
       </c>
       <c r="L214" s="55" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="M214" s="55"/>
       <c r="N214" s="47" t="s">
@@ -36678,7 +36735,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="55" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="M216" s="55"/>
       <c r="N216" s="47" t="s">
@@ -36780,7 +36837,7 @@
         <v>761</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
@@ -36897,7 +36954,7 @@
         <v>1031</v>
       </c>
       <c r="B221" s="52" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C221" s="52" t="s">
         <v>96</v>
@@ -36936,7 +36993,7 @@
         <v>677</v>
       </c>
       <c r="P221" s="86" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="S221" s="47"/>
       <c r="T221" s="47"/>
@@ -36946,7 +37003,7 @@
         <v>1032</v>
       </c>
       <c r="B222" s="55" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C222" s="55" t="s">
         <v>95</v>
@@ -36985,7 +37042,7 @@
         <v>677</v>
       </c>
       <c r="P222" s="86" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="S222" s="47"/>
       <c r="T222" s="47"/>
@@ -36995,7 +37052,7 @@
         <v>1033</v>
       </c>
       <c r="B223" s="52" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C223" s="52" t="s">
         <v>95</v>
@@ -37029,14 +37086,14 @@
         <v>942</v>
       </c>
       <c r="L223" s="52" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="M223" s="52"/>
       <c r="N223" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P223" s="86" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="S223" s="47"/>
       <c r="T223" s="47"/>
@@ -37046,7 +37103,7 @@
         <v>1034</v>
       </c>
       <c r="B224" s="55" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C224" s="55" t="s">
         <v>95</v>
@@ -37087,17 +37144,17 @@
         <v>504</v>
       </c>
       <c r="P224" s="86" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
     </row>
     <row r="225" spans="1:20" ht="17">
       <c r="A225" s="52" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B225" s="55" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C225" s="55" t="s">
         <v>95</v>
@@ -37131,24 +37188,24 @@
         <v>1338</v>
       </c>
       <c r="L225" s="55" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="M225" s="55"/>
       <c r="N225" s="47" t="s">
         <v>677</v>
       </c>
       <c r="P225" s="86" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
     </row>
     <row r="226" spans="1:20" ht="17">
       <c r="A226" s="55" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B226" s="52" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C226" s="52" t="s">
         <v>95</v>
@@ -37187,17 +37244,17 @@
         <v>677</v>
       </c>
       <c r="P226" s="86" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
     </row>
     <row r="227" spans="1:20" ht="17">
       <c r="A227" s="52" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B227" s="55" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C227" s="55" t="s">
         <v>95</v>
@@ -37231,24 +37288,24 @@
         <v>2775</v>
       </c>
       <c r="L227" s="55" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="M227" s="55"/>
       <c r="N227" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P227" s="86" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
     </row>
     <row r="228" spans="1:20" ht="16">
       <c r="A228" s="55" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B228" s="52" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C228" s="52" t="s">
         <v>95</v>
@@ -37282,7 +37339,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="52" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="M228" s="52"/>
       <c r="N228" s="47" t="s">
@@ -37294,10 +37351,10 @@
     </row>
     <row r="229" spans="1:20" ht="17">
       <c r="A229" s="52" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B229" s="55" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C229" s="55" t="s">
         <v>95</v>
@@ -37338,17 +37395,17 @@
         <v>589</v>
       </c>
       <c r="P229" s="86" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
     </row>
     <row r="230" spans="1:20" ht="17">
       <c r="A230" s="52" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B230" s="52" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C230" s="52" t="s">
         <v>95</v>
@@ -37394,10 +37451,10 @@
     </row>
     <row r="231" spans="1:20" ht="17">
       <c r="A231" s="55" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B231" s="55" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C231" s="55" t="s">
         <v>95</v>
@@ -37431,24 +37488,24 @@
         <v>0</v>
       </c>
       <c r="L231" s="55" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="M231" s="55"/>
       <c r="N231" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P231" s="86" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
     </row>
     <row r="232" spans="1:20" ht="17">
       <c r="A232" s="52" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B232" s="52" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C232" s="52" t="s">
         <v>95</v>
@@ -37482,24 +37539,24 @@
         <v>1048</v>
       </c>
       <c r="L232" s="52" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="M232" s="52"/>
       <c r="N232" s="47" t="s">
         <v>677</v>
       </c>
       <c r="P232" s="86" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="S232" s="47"/>
       <c r="T232" s="47"/>
     </row>
     <row r="233" spans="1:20" ht="17">
       <c r="A233" s="55" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B233" s="55" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C233" s="55" t="s">
         <v>95</v>
@@ -37533,21 +37590,21 @@
         <v>891</v>
       </c>
       <c r="L233" s="55" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="M233" s="55"/>
       <c r="N233" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P233" s="86" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
     </row>
     <row r="234" spans="1:20" ht="17">
       <c r="A234" s="52" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B234" s="52" t="s">
         <v>510</v>
@@ -37584,24 +37641,24 @@
         <v>1824</v>
       </c>
       <c r="L234" s="52" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="M234" s="52"/>
       <c r="N234" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
     </row>
     <row r="235" spans="1:20" ht="17">
       <c r="A235" s="52" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C235" s="55" t="s">
         <v>95</v>
@@ -37635,7 +37692,7 @@
         <v>734</v>
       </c>
       <c r="L235" s="55" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="M235" s="55"/>
       <c r="N235" s="47" t="s">
@@ -37649,10 +37706,10 @@
     </row>
     <row r="236" spans="1:20" ht="17">
       <c r="A236" s="55" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B236" s="52" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C236" s="52" t="s">
         <v>95</v>
@@ -37686,7 +37743,7 @@
         <v>436</v>
       </c>
       <c r="L236" s="52" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="M236" s="52"/>
       <c r="N236" s="47" t="s">
@@ -37700,10 +37757,10 @@
     </row>
     <row r="237" spans="1:20" ht="16">
       <c r="A237" s="55" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B237" s="55" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C237" s="55" t="s">
         <v>95</v>
@@ -37737,7 +37794,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="55" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="M237" s="55"/>
       <c r="N237" s="47" t="s">
@@ -37749,10 +37806,10 @@
     </row>
     <row r="238" spans="1:20" ht="17">
       <c r="A238" s="52" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B238" s="52" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C238" s="52" t="s">
         <v>95</v>
@@ -37767,11 +37824,11 @@
         <v>0</v>
       </c>
       <c r="G238" s="66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H238" s="65">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I238" s="65">
         <f>IF(D238&lt;&gt;"",D238,IFERROR(E238/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -37783,7 +37840,7 @@
       </c>
       <c r="K238" s="65">
         <f t="shared" si="20"/>
-        <v>1206</v>
+        <v>603</v>
       </c>
       <c r="L238" s="52"/>
       <c r="M238" s="52"/>
@@ -37791,17 +37848,17 @@
         <v>677</v>
       </c>
       <c r="P238" s="86" t="s">
-        <v>1237</v>
+        <v>1390</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
     </row>
     <row r="239" spans="1:20" ht="17">
       <c r="A239" s="55" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B239" s="55" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C239" s="55" t="s">
         <v>95</v>
@@ -37835,7 +37892,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="55" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="M239" s="55"/>
       <c r="N239" s="47" t="s">
@@ -37849,10 +37906,10 @@
     </row>
     <row r="240" spans="1:20" ht="17">
       <c r="A240" s="52" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B240" s="52" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C240" s="52" t="s">
         <v>95</v>
@@ -37886,24 +37943,24 @@
         <v>1124</v>
       </c>
       <c r="L240" s="52" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="M240" s="52"/>
       <c r="N240" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P240" s="86" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="S240" s="47"/>
       <c r="T240" s="47"/>
     </row>
     <row r="241" spans="1:246" ht="17">
       <c r="A241" s="55" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B241" s="55" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C241" s="55" t="s">
         <v>95</v>
@@ -37944,17 +38001,17 @@
         <v>677</v>
       </c>
       <c r="P241" s="86" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="S241" s="47"/>
       <c r="T241" s="47"/>
     </row>
     <row r="242" spans="1:246" ht="17">
       <c r="A242" s="52" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B242" s="52" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C242" s="52" t="s">
         <v>95</v>
@@ -37988,24 +38045,24 @@
         <v>0</v>
       </c>
       <c r="L242" s="52" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="M242" s="52"/>
       <c r="N242" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P242" s="86" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="S242" s="47"/>
       <c r="T242" s="47"/>
     </row>
     <row r="243" spans="1:246" ht="17">
       <c r="A243" s="55" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B243" s="55" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C243" s="55" t="s">
         <v>95</v>
@@ -38044,17 +38101,17 @@
         <v>677</v>
       </c>
       <c r="P243" s="86" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="S243" s="47"/>
       <c r="T243" s="47"/>
     </row>
     <row r="244" spans="1:246" ht="16">
       <c r="A244" s="52" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B244" s="52" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C244" s="52" t="s">
         <v>95</v>
@@ -38098,10 +38155,10 @@
     </row>
     <row r="245" spans="1:246" s="62" customFormat="1" ht="17">
       <c r="A245" s="87" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B245" s="87" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C245" s="87" t="s">
         <v>95</v>
@@ -38140,7 +38197,7 @@
         <v>504</v>
       </c>
       <c r="P245" s="91" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="U245" s="61"/>
       <c r="V245" s="61"/>
@@ -38371,10 +38428,10 @@
     </row>
     <row r="246" spans="1:246" s="62" customFormat="1" ht="16">
       <c r="A246" s="59" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B246" s="59" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C246" s="59" t="s">
         <v>95</v>
@@ -38385,25 +38442,25 @@
       <c r="E246" s="60">
         <v>999</v>
       </c>
-      <c r="F246" s="95">
+      <c r="F246" s="92">
         <v>0</v>
       </c>
-      <c r="G246" s="95">
+      <c r="G246" s="92">
         <v>0</v>
       </c>
-      <c r="H246" s="96">
+      <c r="H246" s="93">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="I246" s="96">
+      <c r="I246" s="93">
         <f>IF(D246&lt;&gt;"",D246,IFERROR(E246/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
         <v>628</v>
       </c>
-      <c r="J246" s="96">
+      <c r="J246" s="93">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K246" s="96">
+      <c r="K246" s="93">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
@@ -38644,10 +38701,10 @@
     </row>
     <row r="247" spans="1:246" ht="17">
       <c r="A247" s="55" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B247" s="55" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C247" s="55" t="s">
         <v>95</v>
@@ -38686,17 +38743,17 @@
         <v>677</v>
       </c>
       <c r="P247" s="86" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="S247" s="47"/>
       <c r="T247" s="47"/>
     </row>
     <row r="248" spans="1:246" ht="17">
       <c r="A248" s="52" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B248" s="52" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="C248" s="52" t="s">
         <v>95</v>
@@ -38735,17 +38792,17 @@
         <v>677</v>
       </c>
       <c r="P248" s="86" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="S248" s="47"/>
       <c r="T248" s="47"/>
     </row>
     <row r="249" spans="1:246" ht="17">
       <c r="A249" s="55" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="B249" s="55" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="C249" s="55" t="s">
         <v>95</v>
@@ -38784,17 +38841,17 @@
         <v>677</v>
       </c>
       <c r="P249" s="86" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="S249" s="47"/>
       <c r="T249" s="47"/>
     </row>
     <row r="250" spans="1:246" ht="16">
       <c r="A250" s="52" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="B250" s="52" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="C250" s="52" t="s">
         <v>96</v>
@@ -38831,7 +38888,7 @@
         <v>677</v>
       </c>
       <c r="O250" s="47" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="P250" s="86"/>
       <c r="S250" s="47"/>
@@ -38839,10 +38896,10 @@
     </row>
     <row r="251" spans="1:246" ht="16">
       <c r="A251" s="55" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="B251" s="55" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="C251" s="55" t="s">
         <v>96</v>
@@ -38879,7 +38936,7 @@
         <v>677</v>
       </c>
       <c r="O251" s="47" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="P251" s="86"/>
       <c r="S251" s="47"/>
@@ -38887,10 +38944,10 @@
     </row>
     <row r="252" spans="1:246" ht="16">
       <c r="A252" s="52" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="B252" s="52" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="C252" s="52" t="s">
         <v>96</v>
@@ -38927,7 +38984,7 @@
         <v>677</v>
       </c>
       <c r="O252" s="47" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="P252" s="86"/>
       <c r="S252" s="47"/>
@@ -38935,10 +38992,10 @@
     </row>
     <row r="253" spans="1:246" ht="16">
       <c r="A253" s="55" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="B253" s="55" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="C253" s="55" t="s">
         <v>96</v>
@@ -38975,7 +39032,7 @@
         <v>677</v>
       </c>
       <c r="O253" s="47" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="P253" s="86"/>
       <c r="S253" s="47"/>
@@ -38983,10 +39040,10 @@
     </row>
     <row r="254" spans="1:246" ht="16">
       <c r="A254" s="52" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="B254" s="52" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="C254" s="52" t="s">
         <v>95</v>
@@ -39020,7 +39077,7 @@
         <v>3564</v>
       </c>
       <c r="L254" s="52" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="M254" s="52"/>
       <c r="N254" s="47" t="s">
@@ -39032,10 +39089,10 @@
     </row>
     <row r="255" spans="1:246" ht="16">
       <c r="A255" s="55" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="B255" s="55" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="C255" s="55" t="s">
         <v>95</v>
@@ -39047,10 +39104,10 @@
         <v>1380</v>
       </c>
       <c r="F255" s="64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G255" s="64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H255" s="63">
         <f t="shared" si="18"/>
@@ -39062,18 +39119,18 @@
       </c>
       <c r="J255" s="63">
         <f t="shared" si="19"/>
-        <v>1782</v>
+        <v>2673</v>
       </c>
       <c r="K255" s="63">
         <f t="shared" si="20"/>
-        <v>891</v>
+        <v>0</v>
       </c>
       <c r="L255" s="55" t="s">
-        <v>1380</v>
+        <v>1397</v>
       </c>
       <c r="M255" s="55"/>
       <c r="N255" s="47" t="s">
-        <v>589</v>
+        <v>504</v>
       </c>
       <c r="P255" s="86"/>
       <c r="S255" s="47"/>
@@ -39081,10 +39138,10 @@
     </row>
     <row r="256" spans="1:246" ht="16">
       <c r="A256" s="52" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B256" s="52" t="s">
         <v>1343</v>
-      </c>
-      <c r="B256" s="52" t="s">
-        <v>1348</v>
       </c>
       <c r="C256" s="52" t="s">
         <v>95</v>
@@ -39126,12 +39183,12 @@
       <c r="S256" s="47"/>
       <c r="T256" s="47"/>
     </row>
-    <row r="257" spans="1:20" ht="16">
+    <row r="257" spans="1:246" ht="16">
       <c r="A257" s="55" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B257" s="55" t="s">
         <v>1344</v>
-      </c>
-      <c r="B257" s="55" t="s">
-        <v>1349</v>
       </c>
       <c r="C257" s="55" t="s">
         <v>95</v>
@@ -39173,12 +39230,12 @@
       <c r="S257" s="47"/>
       <c r="T257" s="47"/>
     </row>
-    <row r="258" spans="1:20" ht="16">
+    <row r="258" spans="1:246" ht="16">
       <c r="A258" s="52" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B258" s="52" t="s">
         <v>1345</v>
-      </c>
-      <c r="B258" s="52" t="s">
-        <v>1350</v>
       </c>
       <c r="C258" s="52" t="s">
         <v>95</v>
@@ -39220,12 +39277,12 @@
       <c r="S258" s="47"/>
       <c r="T258" s="47"/>
     </row>
-    <row r="259" spans="1:20" ht="17">
+    <row r="259" spans="1:246" ht="17">
       <c r="A259" s="55" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="B259" s="55" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="C259" s="55" t="s">
         <v>95</v>
@@ -39264,17 +39321,17 @@
         <v>677</v>
       </c>
       <c r="P259" s="86" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="S259" s="47"/>
       <c r="T259" s="47"/>
     </row>
-    <row r="260" spans="1:20" ht="17">
+    <row r="260" spans="1:246" ht="17">
       <c r="A260" s="52" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="B260" s="52" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="C260" s="52" t="s">
         <v>95</v>
@@ -39313,17 +39370,17 @@
         <v>677</v>
       </c>
       <c r="P260" s="86" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="S260" s="47"/>
       <c r="T260" s="47"/>
     </row>
-    <row r="261" spans="1:20" ht="17">
+    <row r="261" spans="1:246" ht="17">
       <c r="A261" s="55" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="B261" s="55" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="C261" s="55" t="s">
         <v>95</v>
@@ -39362,17 +39419,17 @@
         <v>677</v>
       </c>
       <c r="P261" s="86" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="S261" s="47"/>
       <c r="T261" s="47"/>
     </row>
-    <row r="262" spans="1:20" ht="17">
+    <row r="262" spans="1:246" ht="17">
       <c r="A262" s="52" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="B262" s="52" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="C262" s="52" t="s">
         <v>95</v>
@@ -39411,66 +39468,290 @@
         <v>677</v>
       </c>
       <c r="P262" s="86" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="S262" s="47"/>
       <c r="T262" s="47"/>
     </row>
-    <row r="263" spans="1:20" ht="17">
-      <c r="A263" s="55" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B263" s="55" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C263" s="55" t="s">
+    <row r="263" spans="1:246" s="62" customFormat="1" ht="17">
+      <c r="A263" s="87" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B263" s="87" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C263" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="D263" s="56">
+      <c r="D263" s="88">
         <v>887</v>
       </c>
-      <c r="E263" s="56">
+      <c r="E263" s="88">
         <v>1380</v>
       </c>
-      <c r="F263" s="64">
+      <c r="F263" s="89">
         <v>0</v>
       </c>
-      <c r="G263" s="64">
+      <c r="G263" s="89">
         <v>1</v>
       </c>
-      <c r="H263" s="63">
+      <c r="H263" s="90">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="I263" s="63">
+      <c r="I263" s="90">
         <f>IF(D263&lt;&gt;"",D263,IFERROR(E263/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
         <v>887</v>
       </c>
-      <c r="J263" s="63">
+      <c r="J263" s="90">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K263" s="63">
+      <c r="K263" s="90">
         <f t="shared" si="23"/>
         <v>887</v>
       </c>
-      <c r="L263" s="55"/>
-      <c r="M263" s="55"/>
-      <c r="N263" s="47" t="s">
+      <c r="L263" s="87"/>
+      <c r="M263" s="87"/>
+      <c r="N263" s="62" t="s">
         <v>677</v>
       </c>
-      <c r="P263" s="86" t="s">
-        <v>1363</v>
-      </c>
-      <c r="S263" s="47"/>
-      <c r="T263" s="47"/>
-    </row>
-    <row r="264" spans="1:20" ht="34">
+      <c r="P263" s="91" t="s">
+        <v>1358</v>
+      </c>
+      <c r="U263" s="61"/>
+      <c r="V263" s="61"/>
+      <c r="W263" s="61"/>
+      <c r="X263" s="61"/>
+      <c r="Y263" s="61"/>
+      <c r="Z263" s="61"/>
+      <c r="AA263" s="61"/>
+      <c r="AB263" s="61"/>
+      <c r="AC263" s="61"/>
+      <c r="AD263" s="61"/>
+      <c r="AE263" s="61"/>
+      <c r="AF263" s="61"/>
+      <c r="AG263" s="61"/>
+      <c r="AH263" s="61"/>
+      <c r="AI263" s="61"/>
+      <c r="AJ263" s="61"/>
+      <c r="AK263" s="61"/>
+      <c r="AL263" s="61"/>
+      <c r="AM263" s="61"/>
+      <c r="AN263" s="61"/>
+      <c r="AO263" s="61"/>
+      <c r="AP263" s="61"/>
+      <c r="AQ263" s="61"/>
+      <c r="AR263" s="61"/>
+      <c r="AS263" s="61"/>
+      <c r="AT263" s="61"/>
+      <c r="AU263" s="61"/>
+      <c r="AV263" s="61"/>
+      <c r="AW263" s="61"/>
+      <c r="AX263" s="61"/>
+      <c r="AY263" s="61"/>
+      <c r="AZ263" s="61"/>
+      <c r="BA263" s="61"/>
+      <c r="BB263" s="61"/>
+      <c r="BC263" s="61"/>
+      <c r="BD263" s="61"/>
+      <c r="BE263" s="61"/>
+      <c r="BF263" s="61"/>
+      <c r="BG263" s="61"/>
+      <c r="BH263" s="61"/>
+      <c r="BI263" s="61"/>
+      <c r="BJ263" s="61"/>
+      <c r="BK263" s="61"/>
+      <c r="BL263" s="61"/>
+      <c r="BM263" s="61"/>
+      <c r="BN263" s="61"/>
+      <c r="BO263" s="61"/>
+      <c r="BP263" s="61"/>
+      <c r="BQ263" s="61"/>
+      <c r="BR263" s="61"/>
+      <c r="BS263" s="61"/>
+      <c r="BT263" s="61"/>
+      <c r="BU263" s="61"/>
+      <c r="BV263" s="61"/>
+      <c r="BW263" s="61"/>
+      <c r="BX263" s="61"/>
+      <c r="BY263" s="61"/>
+      <c r="BZ263" s="61"/>
+      <c r="CA263" s="61"/>
+      <c r="CB263" s="61"/>
+      <c r="CC263" s="61"/>
+      <c r="CD263" s="61"/>
+      <c r="CE263" s="61"/>
+      <c r="CF263" s="61"/>
+      <c r="CG263" s="61"/>
+      <c r="CH263" s="61"/>
+      <c r="CI263" s="61"/>
+      <c r="CJ263" s="61"/>
+      <c r="CK263" s="61"/>
+      <c r="CL263" s="61"/>
+      <c r="CM263" s="61"/>
+      <c r="CN263" s="61"/>
+      <c r="CO263" s="61"/>
+      <c r="CP263" s="61"/>
+      <c r="CQ263" s="61"/>
+      <c r="CR263" s="61"/>
+      <c r="CS263" s="61"/>
+      <c r="CT263" s="61"/>
+      <c r="CU263" s="61"/>
+      <c r="CV263" s="61"/>
+      <c r="CW263" s="61"/>
+      <c r="CX263" s="61"/>
+      <c r="CY263" s="61"/>
+      <c r="CZ263" s="61"/>
+      <c r="DA263" s="61"/>
+      <c r="DB263" s="61"/>
+      <c r="DC263" s="61"/>
+      <c r="DD263" s="61"/>
+      <c r="DE263" s="61"/>
+      <c r="DF263" s="61"/>
+      <c r="DG263" s="61"/>
+      <c r="DH263" s="61"/>
+      <c r="DI263" s="61"/>
+      <c r="DJ263" s="61"/>
+      <c r="DK263" s="61"/>
+      <c r="DL263" s="61"/>
+      <c r="DM263" s="61"/>
+      <c r="DN263" s="61"/>
+      <c r="DO263" s="61"/>
+      <c r="DP263" s="61"/>
+      <c r="DQ263" s="61"/>
+      <c r="DR263" s="61"/>
+      <c r="DS263" s="61"/>
+      <c r="DT263" s="61"/>
+      <c r="DU263" s="61"/>
+      <c r="DV263" s="61"/>
+      <c r="DW263" s="61"/>
+      <c r="DX263" s="61"/>
+      <c r="DY263" s="61"/>
+      <c r="DZ263" s="61"/>
+      <c r="EA263" s="61"/>
+      <c r="EB263" s="61"/>
+      <c r="EC263" s="61"/>
+      <c r="ED263" s="61"/>
+      <c r="EE263" s="61"/>
+      <c r="EF263" s="61"/>
+      <c r="EG263" s="61"/>
+      <c r="EH263" s="61"/>
+      <c r="EI263" s="61"/>
+      <c r="EJ263" s="61"/>
+      <c r="EK263" s="61"/>
+      <c r="EL263" s="61"/>
+      <c r="EM263" s="61"/>
+      <c r="EN263" s="61"/>
+      <c r="EO263" s="61"/>
+      <c r="EP263" s="61"/>
+      <c r="EQ263" s="61"/>
+      <c r="ER263" s="61"/>
+      <c r="ES263" s="61"/>
+      <c r="ET263" s="61"/>
+      <c r="EU263" s="61"/>
+      <c r="EV263" s="61"/>
+      <c r="EW263" s="61"/>
+      <c r="EX263" s="61"/>
+      <c r="EY263" s="61"/>
+      <c r="EZ263" s="61"/>
+      <c r="FA263" s="61"/>
+      <c r="FB263" s="61"/>
+      <c r="FC263" s="61"/>
+      <c r="FD263" s="61"/>
+      <c r="FE263" s="61"/>
+      <c r="FF263" s="61"/>
+      <c r="FG263" s="61"/>
+      <c r="FH263" s="61"/>
+      <c r="FI263" s="61"/>
+      <c r="FJ263" s="61"/>
+      <c r="FK263" s="61"/>
+      <c r="FL263" s="61"/>
+      <c r="FM263" s="61"/>
+      <c r="FN263" s="61"/>
+      <c r="FO263" s="61"/>
+      <c r="FP263" s="61"/>
+      <c r="FQ263" s="61"/>
+      <c r="FR263" s="61"/>
+      <c r="FS263" s="61"/>
+      <c r="FT263" s="61"/>
+      <c r="FU263" s="61"/>
+      <c r="FV263" s="61"/>
+      <c r="FW263" s="61"/>
+      <c r="FX263" s="61"/>
+      <c r="FY263" s="61"/>
+      <c r="FZ263" s="61"/>
+      <c r="GA263" s="61"/>
+      <c r="GB263" s="61"/>
+      <c r="GC263" s="61"/>
+      <c r="GD263" s="61"/>
+      <c r="GE263" s="61"/>
+      <c r="GF263" s="61"/>
+      <c r="GG263" s="61"/>
+      <c r="GH263" s="61"/>
+      <c r="GI263" s="61"/>
+      <c r="GJ263" s="61"/>
+      <c r="GK263" s="61"/>
+      <c r="GL263" s="61"/>
+      <c r="GM263" s="61"/>
+      <c r="GN263" s="61"/>
+      <c r="GO263" s="61"/>
+      <c r="GP263" s="61"/>
+      <c r="GQ263" s="61"/>
+      <c r="GR263" s="61"/>
+      <c r="GS263" s="61"/>
+      <c r="GT263" s="61"/>
+      <c r="GU263" s="61"/>
+      <c r="GV263" s="61"/>
+      <c r="GW263" s="61"/>
+      <c r="GX263" s="61"/>
+      <c r="GY263" s="61"/>
+      <c r="GZ263" s="61"/>
+      <c r="HA263" s="61"/>
+      <c r="HB263" s="61"/>
+      <c r="HC263" s="61"/>
+      <c r="HD263" s="61"/>
+      <c r="HE263" s="61"/>
+      <c r="HF263" s="61"/>
+      <c r="HG263" s="61"/>
+      <c r="HH263" s="61"/>
+      <c r="HI263" s="61"/>
+      <c r="HJ263" s="61"/>
+      <c r="HK263" s="61"/>
+      <c r="HL263" s="61"/>
+      <c r="HM263" s="61"/>
+      <c r="HN263" s="61"/>
+      <c r="HO263" s="61"/>
+      <c r="HP263" s="61"/>
+      <c r="HQ263" s="61"/>
+      <c r="HR263" s="61"/>
+      <c r="HS263" s="61"/>
+      <c r="HT263" s="61"/>
+      <c r="HU263" s="61"/>
+      <c r="HV263" s="61"/>
+      <c r="HW263" s="61"/>
+      <c r="HX263" s="61"/>
+      <c r="HY263" s="61"/>
+      <c r="HZ263" s="61"/>
+      <c r="IA263" s="61"/>
+      <c r="IB263" s="61"/>
+      <c r="IC263" s="61"/>
+      <c r="ID263" s="61"/>
+      <c r="IE263" s="61"/>
+      <c r="IF263" s="61"/>
+      <c r="IG263" s="61"/>
+      <c r="IH263" s="61"/>
+      <c r="II263" s="61"/>
+      <c r="IJ263" s="61"/>
+      <c r="IK263" s="61"/>
+      <c r="IL263" s="61"/>
+    </row>
+    <row r="264" spans="1:246" ht="34">
       <c r="A264" s="52" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="B264" s="52" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="C264" s="52" t="s">
         <v>95</v>
@@ -39509,12 +39790,12 @@
         <v>677</v>
       </c>
       <c r="P264" s="86" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="S264" s="47"/>
       <c r="T264" s="47"/>
     </row>
-    <row r="265" spans="1:20" ht="16">
+    <row r="265" spans="1:246" ht="16">
       <c r="A265" s="55"/>
       <c r="B265" s="55"/>
       <c r="C265" s="55" t="s">
@@ -39554,7 +39835,7 @@
       <c r="S265" s="47"/>
       <c r="T265" s="47"/>
     </row>
-    <row r="266" spans="1:20" ht="16">
+    <row r="266" spans="1:246" ht="16">
       <c r="A266" s="52"/>
       <c r="B266" s="52"/>
       <c r="C266" s="52" t="s">
@@ -39594,7 +39875,7 @@
       <c r="S266" s="47"/>
       <c r="T266" s="47"/>
     </row>
-    <row r="267" spans="1:20" ht="16">
+    <row r="267" spans="1:246" ht="16">
       <c r="A267" s="55"/>
       <c r="B267" s="55"/>
       <c r="C267" s="55" t="s">
@@ -39634,7 +39915,7 @@
       <c r="S267" s="47"/>
       <c r="T267" s="47"/>
     </row>
-    <row r="268" spans="1:20" ht="16">
+    <row r="268" spans="1:246" ht="16">
       <c r="A268" s="52"/>
       <c r="B268" s="52"/>
       <c r="C268" s="52" t="s">
@@ -39674,7 +39955,7 @@
       <c r="S268" s="47"/>
       <c r="T268" s="47"/>
     </row>
-    <row r="269" spans="1:20" ht="16">
+    <row r="269" spans="1:246" ht="16">
       <c r="A269" s="55"/>
       <c r="B269" s="55"/>
       <c r="C269" s="55" t="s">
@@ -39714,7 +39995,7 @@
       <c r="S269" s="47"/>
       <c r="T269" s="47"/>
     </row>
-    <row r="270" spans="1:20" ht="16">
+    <row r="270" spans="1:246" ht="16">
       <c r="A270" s="52"/>
       <c r="B270" s="52"/>
       <c r="C270" s="52" t="s">
@@ -39754,7 +40035,7 @@
       <c r="S270" s="47"/>
       <c r="T270" s="47"/>
     </row>
-    <row r="271" spans="1:20" ht="16">
+    <row r="271" spans="1:246" ht="16">
       <c r="A271" s="55"/>
       <c r="B271" s="55"/>
       <c r="C271" s="55" t="s">
@@ -39794,7 +40075,7 @@
       <c r="S271" s="47"/>
       <c r="T271" s="47"/>
     </row>
-    <row r="272" spans="1:20" ht="16">
+    <row r="272" spans="1:246" ht="16">
       <c r="A272" s="52"/>
       <c r="B272" s="52"/>
       <c r="C272" s="52" t="s">
@@ -45331,10 +45612,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="95" t="s">
         <v>1035</v>
       </c>
-      <c r="B1" s="93"/>
+      <c r="B1" s="95"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1">
       <c r="A2" s="8" t="s">
@@ -45400,15 +45681,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>261321</v>
+        <v>260718</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>198839</v>
+        <v>198342.33333333334</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>62482</v>
+        <v>62375.666666666657</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45416,7 +45697,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>62482</v>
+        <v>62375.666666666657</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -45424,7 +45705,7 @@
       </c>
       <c r="H8" s="73">
         <f>F8-G8</f>
-        <v>44178.66</v>
+        <v>44072.32666666666</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -45433,15 +45714,15 @@
       </c>
       <c r="B9" s="11">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A9,Purchases!$C:$C),0)</f>
-        <v>302596</v>
+        <v>301709</v>
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>198839</v>
+        <v>198342.33333333334</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>103757</v>
+        <v>103366.66666666666</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45449,7 +45730,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>103757</v>
+        <v>103366.66666666666</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -45457,7 +45738,7 @@
       </c>
       <c r="H9" s="74">
         <f>F9-G9</f>
-        <v>62117.67</v>
+        <v>61727.336666666655</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -45470,11 +45751,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>198839</v>
+        <v>198342.33333333334</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-166239</v>
+        <v>-165742.33333333334</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45482,7 +45763,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-166239</v>
+        <v>-165742.33333333334</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -45490,18 +45771,18 @@
       </c>
       <c r="H10" s="73">
         <f>F10-G10</f>
-        <v>-106296.33</v>
+        <v>-105799.66333333334</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="96" t="s">
         <v>1044</v>
       </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
     </row>
     <row r="13" spans="1:8" s="72" customFormat="1" ht="13.5" customHeight="1">
       <c r="A13" s="71" t="s">
@@ -45907,7 +46188,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>493648</v>
+        <v>495678</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -45915,11 +46196,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>188588.0434</v>
+        <v>189481.55539999998</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>305059.95660000003</v>
+        <v>306196.44460000005</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -45927,7 +46208,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>167749.93060000002</v>
+        <v>168886.41860000003</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -45936,7 +46217,7 @@
       </c>
       <c r="B5" s="11">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A5,Sales!$I:$I,"Completed"),0)</f>
-        <v>58473</v>
+        <v>59123</v>
       </c>
       <c r="C5" s="11">
         <f>VLOOKUP($A5,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -45944,11 +46225,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>188474.91320000001</v>
+        <v>189367.88920000001</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-130001.91320000001</v>
+        <v>-130244.88920000001</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -45956,7 +46237,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-58414.871200000009</v>
+        <v>-58657.847200000004</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -45973,11 +46254,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>188588.0434</v>
+        <v>189481.55539999998</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-176058.0434</v>
+        <v>-176951.55539999998</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -45985,7 +46266,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-110335.05939999998</v>
+        <v>-111228.57139999997</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Sep26.xlsx
+++ b/docs/Chiraath-Summary-Sep26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9AF3DB-1A9F-7344-B49D-5F111706D3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981932A2-332F-5849-87C8-D2712785B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -4127,9 +4127,6 @@
     <t>418043 sarees kamana - Tissue silk saree with Woven Zari Bird Motifs</t>
   </si>
   <si>
-    <t>Teal Green, Mauve Purple, Deep Red / Maroon</t>
-  </si>
-  <si>
     <t>421299 Sarees Vigyan Silk - Printed Semi Silk Saree with Lotus Motifs</t>
   </si>
   <si>
@@ -4257,6 +4254,9 @@
   </si>
   <si>
     <t>Reetha Peethambaran, Anu Mathew (Canada), Komallavali</t>
+  </si>
+  <si>
+    <t>Mauve Purple, Deep Red / Maroon</t>
   </si>
 </sst>
 </file>
@@ -5273,7 +5273,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>81</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>62</c:v>
@@ -5606,7 +5606,7 @@
                   <c:v>67003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-193900.99333333335</c:v>
+                  <c:v>-194924.99333333335</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5945,7 +5945,7 @@
                   <c:v>45848</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-7168</c:v>
+                  <c:v>-8192</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6545,7 +6545,7 @@
                   <c:v>33250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16028</c:v>
+                  <c:v>17052</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -7006,7 +7006,7 @@
                   <c:v>476</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>146</c:v>
+                  <c:v>145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>595027</v>
+        <v>594003</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-26696</v>
+        <v>-25672</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>44072.32666666666</v>
+        <v>44413.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>61727.336666666655</v>
+        <v>61044.67</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-105799.66333333334</v>
+        <v>-105458.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -8345,11 +8345,11 @@
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>198342.33333333334</v>
+        <v>198001</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>62375.666666666657</v>
+        <v>62717</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8357,11 +8357,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>44072.32666666666</v>
+        <v>44413.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹44,072</v>
+        <v>Receive ₹44,414</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -8371,15 +8371,15 @@
       </c>
       <c r="B19" s="12">
         <f>PartnerShares!B9</f>
-        <v>301709</v>
+        <v>300685</v>
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>198342.33333333334</v>
+        <v>198001</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>103366.66666666666</v>
+        <v>102684</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8387,11 +8387,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>61727.336666666655</v>
+        <v>61044.67</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹61,727</v>
+        <v>Receive ₹61,045</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -8405,11 +8405,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>198342.33333333334</v>
+        <v>198001</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-165742.33333333334</v>
+        <v>-165401</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8417,11 +8417,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-105799.66333333334</v>
+        <v>-105458.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹105,800</v>
+        <v>Pay ₹105,458</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>595027</v>
+        <v>594003</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
@@ -8676,14 +8676,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-26696</v>
+        <v>-25672</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>-138269.79333333333</v>
+        <v>-139293.79333333333</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="B18" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A18)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>-7168</v>
+        <v>-8192</v>
       </c>
       <c r="C18" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="D18" s="21">
         <f t="shared" si="0"/>
-        <v>16028</v>
+        <v>17052</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$475=J48)*(INVENTORY!$D$2:$D$475)*(INVENTORY!$G$2:$G$475))</f>
-        <v>-193900.99333333335</v>
+        <v>-194924.99333333335</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10695,7 +10695,7 @@
         <v>-4202</v>
       </c>
       <c r="D115" s="39" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
@@ -10709,7 +10709,7 @@
         <v>-1620</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
@@ -10723,7 +10723,7 @@
         <v>-603</v>
       </c>
       <c r="D117" s="39" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" customHeight="1">
@@ -10734,10 +10734,10 @@
         <v>50</v>
       </c>
       <c r="C118" s="37">
-        <v>-887</v>
+        <v>-1911</v>
       </c>
       <c r="D118" s="36" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" customHeight="1">
@@ -19281,7 +19281,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>148</v>
@@ -19938,7 +19938,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="C292" s="85">
         <v>3600</v>
@@ -19948,7 +19948,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -20215,7 +20215,7 @@
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I303" s="44" t="s">
         <v>148</v>
@@ -20240,7 +20240,7 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>148</v>
@@ -20826,7 +20826,7 @@
         <v>46275</v>
       </c>
       <c r="B328" s="44" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C328" s="83">
         <v>1380</v>
@@ -20840,7 +20840,7 @@
       <c r="F328" s="44"/>
       <c r="G328" s="44"/>
       <c r="H328" s="44" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="I328" s="44" t="s">
         <v>148</v>
@@ -20861,7 +20861,7 @@
       <c r="F329" s="46"/>
       <c r="G329" s="46"/>
       <c r="H329" s="46" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="I329" s="45" t="s">
         <v>356</v>
@@ -20872,7 +20872,7 @@
         <v>46275</v>
       </c>
       <c r="B330" s="44" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C330" s="83">
         <v>1450</v>
@@ -20886,7 +20886,7 @@
       <c r="F330" s="44"/>
       <c r="G330" s="44"/>
       <c r="H330" s="44" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="I330" s="44" t="s">
         <v>148</v>
@@ -20897,7 +20897,7 @@
         <v>46275</v>
       </c>
       <c r="B331" s="45" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C331" s="85">
         <v>950</v>
@@ -20911,7 +20911,7 @@
       <c r="F331" s="46"/>
       <c r="G331" s="46"/>
       <c r="H331" s="46" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="I331" s="45" t="s">
         <v>148</v>
@@ -20936,7 +20936,7 @@
       <c r="F332" s="44"/>
       <c r="G332" s="44"/>
       <c r="H332" s="44" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="I332" s="44" t="s">
         <v>148</v>
@@ -20961,7 +20961,7 @@
       <c r="F333" s="46"/>
       <c r="G333" s="46"/>
       <c r="H333" s="46" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="I333" s="45" t="s">
         <v>148</v>
@@ -20978,7 +20978,7 @@
         <v>1380</v>
       </c>
       <c r="D334" s="44" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="E334" s="44" t="s">
         <v>49</v>
@@ -20986,7 +20986,7 @@
       <c r="F334" s="44"/>
       <c r="G334" s="44"/>
       <c r="H334" s="44" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="I334" s="44" t="s">
         <v>148</v>
@@ -28835,7 +28835,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="52" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="M78" s="52"/>
       <c r="N78" s="52" t="s">
@@ -29155,14 +29155,14 @@
         <v>450</v>
       </c>
       <c r="L84" s="52" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="M84" s="52"/>
       <c r="N84" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O84" s="52" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="P84" s="52"/>
       <c r="Q84" s="52"/>
@@ -29261,14 +29261,14 @@
         <v>1045</v>
       </c>
       <c r="L86" s="52" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="M86" s="52"/>
       <c r="N86" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O86" s="52" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="P86" s="52"/>
       <c r="Q86" s="52"/>
@@ -35634,7 +35634,7 @@
         <v>589</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
@@ -35827,14 +35827,14 @@
         <v>934</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
@@ -35946,7 +35946,7 @@
         <v>996</v>
       </c>
       <c r="B201" s="55" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C201" s="55" t="s">
         <v>95</v>
@@ -35987,7 +35987,7 @@
         <v>589</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
@@ -36133,7 +36133,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="55" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="M204" s="55"/>
       <c r="N204" s="47" t="s">
@@ -36533,7 +36533,7 @@
         <v>2775</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
@@ -36837,7 +36837,7 @@
         <v>761</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
@@ -37339,7 +37339,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="52" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="M228" s="52"/>
       <c r="N228" s="47" t="s">
@@ -37692,7 +37692,7 @@
         <v>734</v>
       </c>
       <c r="L235" s="55" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="M235" s="55"/>
       <c r="N235" s="47" t="s">
@@ -37848,7 +37848,7 @@
         <v>677</v>
       </c>
       <c r="P238" s="86" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
@@ -39126,7 +39126,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="55" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="M255" s="55"/>
       <c r="N255" s="47" t="s">
@@ -39282,7 +39282,7 @@
         <v>1347</v>
       </c>
       <c r="B259" s="55" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C259" s="55" t="s">
         <v>95</v>
@@ -39321,7 +39321,7 @@
         <v>677</v>
       </c>
       <c r="P259" s="86" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="S259" s="47"/>
       <c r="T259" s="47"/>
@@ -39331,7 +39331,7 @@
         <v>1348</v>
       </c>
       <c r="B260" s="52" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C260" s="52" t="s">
         <v>95</v>
@@ -39370,7 +39370,7 @@
         <v>677</v>
       </c>
       <c r="P260" s="86" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="S260" s="47"/>
       <c r="T260" s="47"/>
@@ -39380,7 +39380,7 @@
         <v>1349</v>
       </c>
       <c r="B261" s="55" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C261" s="55" t="s">
         <v>95</v>
@@ -39419,7 +39419,7 @@
         <v>677</v>
       </c>
       <c r="P261" s="86" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="S261" s="47"/>
       <c r="T261" s="47"/>
@@ -39444,11 +39444,11 @@
         <v>0</v>
       </c>
       <c r="G262" s="66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H262" s="65">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I262" s="65">
         <f>IF(D262&lt;&gt;"",D262,IFERROR(E262/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -39460,7 +39460,7 @@
       </c>
       <c r="K262" s="65">
         <f t="shared" si="23"/>
-        <v>3072</v>
+        <v>2048</v>
       </c>
       <c r="L262" s="52"/>
       <c r="M262" s="52"/>
@@ -39468,7 +39468,7 @@
         <v>677</v>
       </c>
       <c r="P262" s="86" t="s">
-        <v>1354</v>
+        <v>1397</v>
       </c>
       <c r="S262" s="47"/>
       <c r="T262" s="47"/>
@@ -39478,7 +39478,7 @@
         <v>1351</v>
       </c>
       <c r="B263" s="87" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C263" s="87" t="s">
         <v>95</v>
@@ -39517,7 +39517,7 @@
         <v>677</v>
       </c>
       <c r="P263" s="91" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="U263" s="61"/>
       <c r="V263" s="61"/>
@@ -39751,7 +39751,7 @@
         <v>1352</v>
       </c>
       <c r="B264" s="52" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C264" s="52" t="s">
         <v>95</v>
@@ -39790,7 +39790,7 @@
         <v>677</v>
       </c>
       <c r="P264" s="86" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="S264" s="47"/>
       <c r="T264" s="47"/>
@@ -45685,11 +45685,11 @@
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>198342.33333333334</v>
+        <v>198001</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>62375.666666666657</v>
+        <v>62717</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45697,7 +45697,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>62375.666666666657</v>
+        <v>62717</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -45705,7 +45705,7 @@
       </c>
       <c r="H8" s="73">
         <f>F8-G8</f>
-        <v>44072.32666666666</v>
+        <v>44413.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -45714,15 +45714,15 @@
       </c>
       <c r="B9" s="11">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A9,Purchases!$C:$C),0)</f>
-        <v>301709</v>
+        <v>300685</v>
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>198342.33333333334</v>
+        <v>198001</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>103366.66666666666</v>
+        <v>102684</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45730,7 +45730,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>103366.66666666666</v>
+        <v>102684</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -45738,7 +45738,7 @@
       </c>
       <c r="H9" s="74">
         <f>F9-G9</f>
-        <v>61727.336666666655</v>
+        <v>61044.67</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -45751,11 +45751,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>198342.33333333334</v>
+        <v>198001</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-165742.33333333334</v>
+        <v>-165401</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -45763,7 +45763,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-165742.33333333334</v>
+        <v>-165401</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -45771,7 +45771,7 @@
       </c>
       <c r="H10" s="73">
         <f>F10-G10</f>
-        <v>-105799.66333333334</v>
+        <v>-105458.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">

--- a/docs/Chiraath-Summary-Sep26.xlsx
+++ b/docs/Chiraath-Summary-Sep26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981932A2-332F-5849-87C8-D2712785B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E4BE83-2814-4547-B274-C644FA88F445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$272</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$334</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3551" uniqueCount="1398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="1402">
   <si>
     <t>Notes:</t>
   </si>
@@ -3880,9 +3880,6 @@
     <t>Prajisha (Construction Company)</t>
   </si>
   <si>
-    <t>CHR-87 Red Salwar with Elephant print, CHR-58 Wine Red Salwar, CHR-180 Coffee Brown Salwar(M) (2100 advance, 1350 balance)</t>
-  </si>
-  <si>
     <t>Shinoob School - 1500(XXL), Niroop - XL, Prajisha(1100) - M</t>
   </si>
   <si>
@@ -3988,31 +3985,19 @@
     <t>Peacock blue/Royal blue, Purple/Pink, Lime Green/Wine Purple</t>
   </si>
   <si>
-    <t>426363 Churidar Set</t>
-  </si>
-  <si>
     <t>L, XL, XXL</t>
   </si>
   <si>
     <t>CHR-251</t>
   </si>
   <si>
-    <t>425677 Churidar Set</t>
-  </si>
-  <si>
     <t>M, L, XL, XXL</t>
   </si>
   <si>
     <t>CHR-252</t>
   </si>
   <si>
-    <t>417278 Churidar Set</t>
-  </si>
-  <si>
     <t>CHR-253</t>
-  </si>
-  <si>
-    <t>424938 Churidar Set</t>
   </si>
   <si>
     <t>Soft Silk Saree Collection (Kuthanpully)</t>
@@ -4257,6 +4242,33 @@
   </si>
   <si>
     <t>Mauve Purple, Deep Red / Maroon</t>
+  </si>
+  <si>
+    <t>425677 Churidar Set - Cotton Salwar 3 piece set</t>
+  </si>
+  <si>
+    <t>417278 Churidar Set - Chanderi Salwar 3 piece set</t>
+  </si>
+  <si>
+    <t>424938 Churidar Set - Silk Salwar 3 piece set</t>
+  </si>
+  <si>
+    <t>Navy Blue</t>
+  </si>
+  <si>
+    <t>CHR-87 Red Salwar with Elephant print, CHR-58 Wine Red Salwar, CHR-180 Coffee Brown Salwar(M) (3100 advance, 350 balance)</t>
+  </si>
+  <si>
+    <t>Olive gold</t>
+  </si>
+  <si>
+    <t>426363 Churidar Set - Chanderi Salwar multicolor flora set</t>
+  </si>
+  <si>
+    <t>Dusty Rose</t>
+  </si>
+  <si>
+    <t>Chocolate Brown.</t>
   </si>
 </sst>
 </file>
@@ -6099,13 +6111,13 @@
                   <c:v>72915</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>65156</c:v>
+                  <c:v>66256</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>79098</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8860</c:v>
+                  <c:v>8960</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6539,13 +6551,13 @@
                   <c:v>-26128</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-37044</c:v>
+                  <c:v>-35944</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>33250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17052</c:v>
+                  <c:v>17152</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -8213,7 +8225,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>568331</v>
+        <v>568431</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -8230,7 +8242,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>581411</v>
+        <v>582611</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -8247,7 +8259,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-25672</v>
+        <v>-25572</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8463,11 +8475,11 @@
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>189481.55539999998</v>
+        <v>189514.89539999998</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>306196.44460000005</v>
+        <v>306163.10460000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8475,11 +8487,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>168886.41860000003</v>
+        <v>168853.07860000001</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹168,886</v>
+        <v>Pay ₹168,853</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8489,15 +8501,15 @@
       </c>
       <c r="B27" s="12">
         <f>'Cash Pool'!B5</f>
-        <v>59123</v>
+        <v>59223</v>
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>189367.88920000001</v>
+        <v>189401.20920000001</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-130244.88920000001</v>
+        <v>-130178.20920000001</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8505,11 +8517,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-58657.847200000004</v>
+        <v>-58591.167200000011</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹58,658</v>
+        <v>Receive ₹58,591</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8523,11 +8535,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>189481.55539999998</v>
+        <v>189514.89539999998</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-176951.55539999998</v>
+        <v>-176984.89539999998</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8535,11 +8547,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-111228.57139999997</v>
+        <v>-111261.91139999997</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹111,229</v>
+        <v>Receive ₹111,262</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8651,7 +8663,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8667,7 +8679,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>568331</v>
+        <v>568431</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8676,7 +8688,7 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-25672</v>
+        <v>-25572</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
@@ -8840,11 +8852,11 @@
       </c>
       <c r="C16" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>65156</v>
+        <v>66256</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
-        <v>-37044</v>
+        <v>-35944</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -8874,11 +8886,11 @@
       </c>
       <c r="C18" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>8860</v>
+        <v>8960</v>
       </c>
       <c r="D18" s="21">
         <f t="shared" si="0"/>
-        <v>17052</v>
+        <v>17152</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
@@ -10625,7 +10637,7 @@
         <v>3046</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15" customHeight="1">
@@ -10695,7 +10707,7 @@
         <v>-4202</v>
       </c>
       <c r="D115" s="39" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
@@ -10709,7 +10721,7 @@
         <v>-1620</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
@@ -10723,7 +10735,7 @@
         <v>-603</v>
       </c>
       <c r="D117" s="39" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" customHeight="1">
@@ -10737,7 +10749,7 @@
         <v>-1911</v>
       </c>
       <c r="D118" s="36" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" customHeight="1">
@@ -19281,7 +19293,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>148</v>
@@ -19345,14 +19357,14 @@
         <v>1271</v>
       </c>
       <c r="C268" s="83">
-        <v>2350</v>
+        <v>3450</v>
       </c>
       <c r="D268" s="44"/>
       <c r="E268" s="44"/>
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1272</v>
+        <v>1397</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>356</v>
@@ -19388,7 +19400,7 @@
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -19663,7 +19675,7 @@
         <v>46219</v>
       </c>
       <c r="B281" s="45" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="C281" s="85">
         <v>3600</v>
@@ -19677,7 +19689,7 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
@@ -19938,7 +19950,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="C292" s="85">
         <v>3600</v>
@@ -19948,7 +19960,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19969,7 +19981,7 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
@@ -19994,7 +20006,7 @@
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I294" s="45" t="s">
         <v>148</v>
@@ -20055,7 +20067,7 @@
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -20069,7 +20081,7 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
@@ -20155,7 +20167,7 @@
         <v>46238</v>
       </c>
       <c r="B301" s="44" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C301" s="83">
         <v>12650</v>
@@ -20169,7 +20181,7 @@
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
       <c r="H301" s="44" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="I301" s="44" t="s">
         <v>148</v>
@@ -20215,7 +20227,7 @@
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="I303" s="44" t="s">
         <v>148</v>
@@ -20240,7 +20252,7 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>148</v>
@@ -20301,7 +20313,7 @@
         <v>46243</v>
       </c>
       <c r="B307" s="44" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C307" s="83">
         <v>5750</v>
@@ -20315,7 +20327,7 @@
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
       <c r="H307" s="44" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="I307" s="44" t="s">
         <v>148</v>
@@ -20451,7 +20463,7 @@
         <v>46252</v>
       </c>
       <c r="B313" s="45" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C313" s="85">
         <v>5750</v>
@@ -20465,7 +20477,7 @@
       <c r="F313" s="46"/>
       <c r="G313" s="46"/>
       <c r="H313" s="46" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="I313" s="45" t="s">
         <v>148</v>
@@ -20476,7 +20488,7 @@
         <v>46252</v>
       </c>
       <c r="B314" s="44" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C314" s="83">
         <v>1380</v>
@@ -20490,7 +20502,7 @@
       <c r="F314" s="44"/>
       <c r="G314" s="44"/>
       <c r="H314" s="44" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="I314" s="44" t="s">
         <v>148</v>
@@ -20501,7 +20513,7 @@
         <v>46252</v>
       </c>
       <c r="B315" s="45" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C315" s="85">
         <v>5750</v>
@@ -20515,7 +20527,7 @@
       <c r="F315" s="46"/>
       <c r="G315" s="46"/>
       <c r="H315" s="46" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="I315" s="45" t="s">
         <v>148</v>
@@ -20526,7 +20538,7 @@
         <v>46252</v>
       </c>
       <c r="B316" s="44" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C316" s="83">
         <v>1340</v>
@@ -20540,7 +20552,7 @@
       <c r="F316" s="44"/>
       <c r="G316" s="44"/>
       <c r="H316" s="44" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="I316" s="44" t="s">
         <v>148</v>
@@ -20551,7 +20563,7 @@
         <v>46252</v>
       </c>
       <c r="B317" s="45" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C317" s="85">
         <v>1250</v>
@@ -20565,7 +20577,7 @@
       <c r="F317" s="46"/>
       <c r="G317" s="46"/>
       <c r="H317" s="46" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="I317" s="45" t="s">
         <v>148</v>
@@ -20576,7 +20588,7 @@
         <v>46257</v>
       </c>
       <c r="B318" s="44" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C318" s="83">
         <v>1780</v>
@@ -20590,7 +20602,7 @@
       <c r="F318" s="44"/>
       <c r="G318" s="44"/>
       <c r="H318" s="44" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="I318" s="44" t="s">
         <v>148</v>
@@ -20615,7 +20627,7 @@
       <c r="F319" s="46"/>
       <c r="G319" s="46"/>
       <c r="H319" s="46" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="I319" s="45" t="s">
         <v>148</v>
@@ -20640,7 +20652,7 @@
       <c r="F320" s="44"/>
       <c r="G320" s="44"/>
       <c r="H320" s="44" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="I320" s="44" t="s">
         <v>148</v>
@@ -20651,7 +20663,7 @@
         <v>46257</v>
       </c>
       <c r="B321" s="45" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C321" s="85">
         <v>1500</v>
@@ -20665,7 +20677,7 @@
       <c r="F321" s="46"/>
       <c r="G321" s="46"/>
       <c r="H321" s="46" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="I321" s="45" t="s">
         <v>148</v>
@@ -20676,7 +20688,7 @@
         <v>46258</v>
       </c>
       <c r="B322" s="44" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C322" s="83">
         <v>1250</v>
@@ -20690,7 +20702,7 @@
       <c r="F322" s="44"/>
       <c r="G322" s="44"/>
       <c r="H322" s="44" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="I322" s="44" t="s">
         <v>148</v>
@@ -20701,7 +20713,7 @@
         <v>46263</v>
       </c>
       <c r="B323" s="45" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="C323" s="85">
         <v>1380</v>
@@ -20715,7 +20727,7 @@
       <c r="F323" s="46"/>
       <c r="G323" s="46"/>
       <c r="H323" s="46" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="I323" s="45" t="s">
         <v>148</v>
@@ -20726,7 +20738,7 @@
         <v>46263</v>
       </c>
       <c r="B324" s="44" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="C324" s="83">
         <v>1380</v>
@@ -20740,7 +20752,7 @@
       <c r="F324" s="44"/>
       <c r="G324" s="44"/>
       <c r="H324" s="44" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="I324" s="44" t="s">
         <v>148</v>
@@ -20751,7 +20763,7 @@
         <v>46263</v>
       </c>
       <c r="B325" s="45" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="C325" s="85">
         <v>2500</v>
@@ -20765,7 +20777,7 @@
       <c r="F325" s="46"/>
       <c r="G325" s="46"/>
       <c r="H325" s="46" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="I325" s="45" t="s">
         <v>148</v>
@@ -20790,7 +20802,7 @@
       <c r="F326" s="44"/>
       <c r="G326" s="44"/>
       <c r="H326" s="44" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="I326" s="44" t="s">
         <v>148</v>
@@ -20801,7 +20813,7 @@
         <v>46257</v>
       </c>
       <c r="B327" s="45" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="C327" s="85">
         <v>750</v>
@@ -20815,7 +20827,7 @@
       <c r="F327" s="46"/>
       <c r="G327" s="46"/>
       <c r="H327" s="46" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="I327" s="45" t="s">
         <v>148</v>
@@ -20826,7 +20838,7 @@
         <v>46275</v>
       </c>
       <c r="B328" s="44" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="C328" s="83">
         <v>1380</v>
@@ -20840,7 +20852,7 @@
       <c r="F328" s="44"/>
       <c r="G328" s="44"/>
       <c r="H328" s="44" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="I328" s="44" t="s">
         <v>148</v>
@@ -20861,7 +20873,7 @@
       <c r="F329" s="46"/>
       <c r="G329" s="46"/>
       <c r="H329" s="46" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="I329" s="45" t="s">
         <v>356</v>
@@ -20872,7 +20884,7 @@
         <v>46275</v>
       </c>
       <c r="B330" s="44" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="C330" s="83">
         <v>1450</v>
@@ -20886,7 +20898,7 @@
       <c r="F330" s="44"/>
       <c r="G330" s="44"/>
       <c r="H330" s="44" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="I330" s="44" t="s">
         <v>148</v>
@@ -20897,7 +20909,7 @@
         <v>46275</v>
       </c>
       <c r="B331" s="45" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="C331" s="85">
         <v>950</v>
@@ -20911,7 +20923,7 @@
       <c r="F331" s="46"/>
       <c r="G331" s="46"/>
       <c r="H331" s="46" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="I331" s="45" t="s">
         <v>148</v>
@@ -20936,7 +20948,7 @@
       <c r="F332" s="44"/>
       <c r="G332" s="44"/>
       <c r="H332" s="44" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="I332" s="44" t="s">
         <v>148</v>
@@ -20950,7 +20962,7 @@
         <v>183</v>
       </c>
       <c r="C333" s="85">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="D333" s="45" t="s">
         <v>150</v>
@@ -20961,7 +20973,7 @@
       <c r="F333" s="46"/>
       <c r="G333" s="46"/>
       <c r="H333" s="46" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="I333" s="45" t="s">
         <v>148</v>
@@ -20978,7 +20990,7 @@
         <v>1380</v>
       </c>
       <c r="D334" s="44" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="E334" s="44" t="s">
         <v>49</v>
@@ -20986,7 +20998,7 @@
       <c r="F334" s="44"/>
       <c r="G334" s="44"/>
       <c r="H334" s="44" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="I334" s="44" t="s">
         <v>148</v>
@@ -21202,7 +21214,7 @@
       <c r="I353" s="45"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I329" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I334" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1257" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
@@ -21234,7 +21246,7 @@
     <col min="13" max="13" width="22.5" style="47" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.83203125" style="47" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.6640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62.6640625" style="47" customWidth="1"/>
+    <col min="16" max="16" width="62" style="47" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.83203125" style="47" customWidth="1"/>
     <col min="18" max="18" width="11.1640625" style="47" customWidth="1"/>
     <col min="19" max="20" width="10" style="48" customWidth="1"/>
@@ -28835,7 +28847,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="52" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="M78" s="52"/>
       <c r="N78" s="52" t="s">
@@ -29155,14 +29167,14 @@
         <v>450</v>
       </c>
       <c r="L84" s="52" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="M84" s="52"/>
       <c r="N84" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O84" s="52" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="P84" s="52"/>
       <c r="Q84" s="52"/>
@@ -29261,14 +29273,14 @@
         <v>1045</v>
       </c>
       <c r="L86" s="52" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="M86" s="52"/>
       <c r="N86" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O86" s="52" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="P86" s="52"/>
       <c r="Q86" s="52"/>
@@ -31075,7 +31087,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -34163,7 +34175,7 @@
         <v>606</v>
       </c>
       <c r="L166" s="52" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="M166" s="52"/>
       <c r="N166" s="52" t="s">
@@ -34171,7 +34183,7 @@
       </c>
       <c r="O166" s="52"/>
       <c r="P166" s="52" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q166" s="52"/>
       <c r="R166" s="52"/>
@@ -34959,7 +34971,7 @@
         <v>1019</v>
       </c>
       <c r="L181" s="55" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="M181" s="55"/>
       <c r="N181" s="55" t="s">
@@ -35272,7 +35284,7 @@
         <v>891</v>
       </c>
       <c r="L187" s="55" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="M187" s="55"/>
       <c r="N187" s="55" t="s">
@@ -35376,7 +35388,7 @@
         <v>891</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -35384,7 +35396,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -35627,14 +35639,14 @@
         <v>3950</v>
       </c>
       <c r="L194" s="52" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="M194" s="52"/>
       <c r="N194" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
@@ -35827,14 +35839,14 @@
         <v>934</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
@@ -35878,14 +35890,14 @@
         <v>1732</v>
       </c>
       <c r="L199" s="52" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M199" s="52"/>
       <c r="N199" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P199" s="47" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="S199" s="47"/>
       <c r="T199" s="47"/>
@@ -35946,7 +35958,7 @@
         <v>996</v>
       </c>
       <c r="B201" s="55" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="C201" s="55" t="s">
         <v>95</v>
@@ -35987,7 +35999,7 @@
         <v>589</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
@@ -36133,7 +36145,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="55" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="M204" s="55"/>
       <c r="N204" s="47" t="s">
@@ -36283,14 +36295,14 @@
         <v>2346</v>
       </c>
       <c r="L207" s="52" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="M207" s="52"/>
       <c r="N207" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P207" s="47" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="S207" s="47"/>
       <c r="T207" s="47"/>
@@ -36434,7 +36446,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="55" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="M210" s="55"/>
       <c r="N210" s="47" t="s">
@@ -36485,7 +36497,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="52" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="M211" s="52"/>
       <c r="N211" s="47" t="s">
@@ -36533,14 +36545,14 @@
         <v>2775</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P212" s="47" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="S212" s="47"/>
       <c r="T212" s="47"/>
@@ -36584,7 +36596,7 @@
         <v>3340</v>
       </c>
       <c r="L213" s="52" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="M213" s="52"/>
       <c r="N213" s="47" t="s">
@@ -36837,7 +36849,7 @@
         <v>761</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
@@ -37339,7 +37351,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="52" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="M228" s="52"/>
       <c r="N228" s="47" t="s">
@@ -37641,14 +37653,14 @@
         <v>1824</v>
       </c>
       <c r="L234" s="52" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="M234" s="52"/>
       <c r="N234" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
@@ -37692,7 +37704,7 @@
         <v>734</v>
       </c>
       <c r="L235" s="55" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="M235" s="55"/>
       <c r="N235" s="47" t="s">
@@ -37848,7 +37860,7 @@
         <v>677</v>
       </c>
       <c r="P238" s="86" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
@@ -38045,7 +38057,7 @@
         <v>0</v>
       </c>
       <c r="L242" s="52" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="M242" s="52"/>
       <c r="N242" s="47" t="s">
@@ -38753,7 +38765,7 @@
         <v>1223</v>
       </c>
       <c r="B248" s="52" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="C248" s="52" t="s">
         <v>95</v>
@@ -38792,17 +38804,17 @@
         <v>677</v>
       </c>
       <c r="P248" s="86" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="S248" s="47"/>
       <c r="T248" s="47"/>
     </row>
     <row r="249" spans="1:246" ht="17">
       <c r="A249" s="55" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B249" s="55" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="C249" s="55" t="s">
         <v>95</v>
@@ -38841,17 +38853,17 @@
         <v>677</v>
       </c>
       <c r="P249" s="86" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="S249" s="47"/>
       <c r="T249" s="47"/>
     </row>
-    <row r="250" spans="1:246" ht="16">
+    <row r="250" spans="1:246" ht="17">
       <c r="A250" s="52" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B250" s="52" t="s">
-        <v>1308</v>
+        <v>1399</v>
       </c>
       <c r="C250" s="52" t="s">
         <v>96</v>
@@ -38859,7 +38871,9 @@
       <c r="D250" s="53">
         <v>1090</v>
       </c>
-      <c r="E250" s="53"/>
+      <c r="E250" s="53">
+        <v>1650</v>
+      </c>
       <c r="F250" s="66">
         <v>0</v>
       </c>
@@ -38888,18 +38902,20 @@
         <v>677</v>
       </c>
       <c r="O250" s="47" t="s">
-        <v>1309</v>
-      </c>
-      <c r="P250" s="86"/>
+        <v>1307</v>
+      </c>
+      <c r="P250" s="86" t="s">
+        <v>1401</v>
+      </c>
       <c r="S250" s="47"/>
       <c r="T250" s="47"/>
     </row>
-    <row r="251" spans="1:246" ht="16">
+    <row r="251" spans="1:246" ht="17">
       <c r="A251" s="55" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B251" s="55" t="s">
-        <v>1311</v>
+        <v>1393</v>
       </c>
       <c r="C251" s="55" t="s">
         <v>96</v>
@@ -38907,7 +38923,9 @@
       <c r="D251" s="56">
         <v>1049</v>
       </c>
-      <c r="E251" s="56"/>
+      <c r="E251" s="56">
+        <v>1550</v>
+      </c>
       <c r="F251" s="64">
         <v>0</v>
       </c>
@@ -38936,18 +38954,20 @@
         <v>677</v>
       </c>
       <c r="O251" s="47" t="s">
-        <v>1312</v>
-      </c>
-      <c r="P251" s="86"/>
+        <v>1309</v>
+      </c>
+      <c r="P251" s="86" t="s">
+        <v>1396</v>
+      </c>
       <c r="S251" s="47"/>
       <c r="T251" s="47"/>
     </row>
-    <row r="252" spans="1:246" ht="16">
+    <row r="252" spans="1:246" ht="17">
       <c r="A252" s="52" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B252" s="52" t="s">
-        <v>1314</v>
+        <v>1394</v>
       </c>
       <c r="C252" s="52" t="s">
         <v>96</v>
@@ -38955,7 +38975,9 @@
       <c r="D252" s="53">
         <v>1049</v>
       </c>
-      <c r="E252" s="53"/>
+      <c r="E252" s="53">
+        <v>1550</v>
+      </c>
       <c r="F252" s="66">
         <v>0</v>
       </c>
@@ -38984,18 +39006,20 @@
         <v>677</v>
       </c>
       <c r="O252" s="47" t="s">
-        <v>1312</v>
-      </c>
-      <c r="P252" s="86"/>
+        <v>1309</v>
+      </c>
+      <c r="P252" s="86" t="s">
+        <v>1398</v>
+      </c>
       <c r="S252" s="47"/>
       <c r="T252" s="47"/>
     </row>
-    <row r="253" spans="1:246" ht="16">
+    <row r="253" spans="1:246" ht="17">
       <c r="A253" s="55" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="B253" s="55" t="s">
-        <v>1316</v>
+        <v>1395</v>
       </c>
       <c r="C253" s="55" t="s">
         <v>96</v>
@@ -39003,7 +39027,9 @@
       <c r="D253" s="56">
         <v>1322</v>
       </c>
-      <c r="E253" s="56"/>
+      <c r="E253" s="56">
+        <v>1900</v>
+      </c>
       <c r="F253" s="64">
         <v>0</v>
       </c>
@@ -39032,18 +39058,20 @@
         <v>677</v>
       </c>
       <c r="O253" s="47" t="s">
-        <v>1309</v>
-      </c>
-      <c r="P253" s="86"/>
+        <v>1307</v>
+      </c>
+      <c r="P253" s="86" t="s">
+        <v>1400</v>
+      </c>
       <c r="S253" s="47"/>
       <c r="T253" s="47"/>
     </row>
     <row r="254" spans="1:246" ht="16">
       <c r="A254" s="52" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="B254" s="52" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="C254" s="52" t="s">
         <v>95</v>
@@ -39077,7 +39105,7 @@
         <v>3564</v>
       </c>
       <c r="L254" s="52" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="M254" s="52"/>
       <c r="N254" s="47" t="s">
@@ -39089,10 +39117,10 @@
     </row>
     <row r="255" spans="1:246" ht="16">
       <c r="A255" s="55" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="B255" s="55" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="C255" s="55" t="s">
         <v>95</v>
@@ -39126,7 +39154,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="55" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="M255" s="55"/>
       <c r="N255" s="47" t="s">
@@ -39138,10 +39166,10 @@
     </row>
     <row r="256" spans="1:246" ht="16">
       <c r="A256" s="52" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B256" s="52" t="s">
         <v>1338</v>
-      </c>
-      <c r="B256" s="52" t="s">
-        <v>1343</v>
       </c>
       <c r="C256" s="52" t="s">
         <v>95</v>
@@ -39185,10 +39213,10 @@
     </row>
     <row r="257" spans="1:246" ht="16">
       <c r="A257" s="55" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B257" s="55" t="s">
         <v>1339</v>
-      </c>
-      <c r="B257" s="55" t="s">
-        <v>1344</v>
       </c>
       <c r="C257" s="55" t="s">
         <v>95</v>
@@ -39232,10 +39260,10 @@
     </row>
     <row r="258" spans="1:246" ht="16">
       <c r="A258" s="52" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B258" s="52" t="s">
         <v>1340</v>
-      </c>
-      <c r="B258" s="52" t="s">
-        <v>1345</v>
       </c>
       <c r="C258" s="52" t="s">
         <v>95</v>
@@ -39279,10 +39307,10 @@
     </row>
     <row r="259" spans="1:246" ht="17">
       <c r="A259" s="55" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="B259" s="55" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="C259" s="55" t="s">
         <v>95</v>
@@ -39321,17 +39349,17 @@
         <v>677</v>
       </c>
       <c r="P259" s="86" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="S259" s="47"/>
       <c r="T259" s="47"/>
     </row>
     <row r="260" spans="1:246" ht="17">
       <c r="A260" s="52" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="B260" s="52" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="C260" s="52" t="s">
         <v>95</v>
@@ -39370,17 +39398,17 @@
         <v>677</v>
       </c>
       <c r="P260" s="86" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="S260" s="47"/>
       <c r="T260" s="47"/>
     </row>
     <row r="261" spans="1:246" ht="17">
       <c r="A261" s="55" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B261" s="55" t="s">
         <v>1349</v>
-      </c>
-      <c r="B261" s="55" t="s">
-        <v>1354</v>
       </c>
       <c r="C261" s="55" t="s">
         <v>95</v>
@@ -39419,17 +39447,17 @@
         <v>677</v>
       </c>
       <c r="P261" s="86" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="S261" s="47"/>
       <c r="T261" s="47"/>
     </row>
     <row r="262" spans="1:246" ht="17">
       <c r="A262" s="52" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="B262" s="52" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="C262" s="52" t="s">
         <v>95</v>
@@ -39468,17 +39496,17 @@
         <v>677</v>
       </c>
       <c r="P262" s="86" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="S262" s="47"/>
       <c r="T262" s="47"/>
     </row>
     <row r="263" spans="1:246" s="62" customFormat="1" ht="17">
       <c r="A263" s="87" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B263" s="87" t="s">
         <v>1351</v>
-      </c>
-      <c r="B263" s="87" t="s">
-        <v>1356</v>
       </c>
       <c r="C263" s="87" t="s">
         <v>95</v>
@@ -39517,7 +39545,7 @@
         <v>677</v>
       </c>
       <c r="P263" s="91" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="U263" s="61"/>
       <c r="V263" s="61"/>
@@ -39748,10 +39776,10 @@
     </row>
     <row r="264" spans="1:246" ht="34">
       <c r="A264" s="52" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="B264" s="52" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="C264" s="52" t="s">
         <v>95</v>
@@ -39790,7 +39818,7 @@
         <v>677</v>
       </c>
       <c r="P264" s="86" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="S264" s="47"/>
       <c r="T264" s="47"/>
@@ -46196,11 +46224,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>189481.55539999998</v>
+        <v>189514.89539999998</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>306196.44460000005</v>
+        <v>306163.10460000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -46208,7 +46236,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>168886.41860000003</v>
+        <v>168853.07860000001</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -46217,7 +46245,7 @@
       </c>
       <c r="B5" s="11">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A5,Sales!$I:$I,"Completed"),0)</f>
-        <v>59123</v>
+        <v>59223</v>
       </c>
       <c r="C5" s="11">
         <f>VLOOKUP($A5,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -46225,11 +46253,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>189367.88920000001</v>
+        <v>189401.20920000001</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-130244.88920000001</v>
+        <v>-130178.20920000001</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -46237,7 +46265,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-58657.847200000004</v>
+        <v>-58591.167200000011</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -46254,11 +46282,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>189481.55539999998</v>
+        <v>189514.89539999998</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-176951.55539999998</v>
+        <v>-176984.89539999998</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -46266,7 +46294,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-111228.57139999997</v>
+        <v>-111261.91139999997</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
